--- a/DSBDAL/Assignment2/CreatedData.xlsx
+++ b/DSBDAL/Assignment2/CreatedData.xlsx
@@ -315,25 +315,25 @@
         <f t="shared" ref="A2:A139" si="2">ROW()-ROW($A$1)</f>
         <v>1</v>
       </c>
-      <c r="B2" s="3">
+      <c r="B2" s="3" t="str">
         <f t="shared" ref="B2:D2" si="1">IF(RAND()&lt;0.2,"NA",RANDBETWEEN(60,80))</f>
-        <v>71</v>
-      </c>
-      <c r="C2" s="3">
+        <v>NA</v>
+      </c>
+      <c r="C2" s="3" t="str">
         <f t="shared" si="1"/>
-        <v>67</v>
-      </c>
-      <c r="D2" s="3" t="str">
+        <v>NA</v>
+      </c>
+      <c r="D2" s="3">
         <f t="shared" si="1"/>
-        <v>NA</v>
+        <v>69</v>
       </c>
       <c r="E2" s="2">
         <f t="shared" ref="E2:E139" si="4">IF(RAND()&lt;0.05,CHOOSE(RANDBETWEEN(1,2),500,5),RANDBETWEEN(75,90))</f>
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="F2" s="2">
         <f t="shared" ref="F2:F139" si="5">RANDBETWEEN(2018,2021)</f>
-        <v>2018</v>
+        <v>2019</v>
       </c>
     </row>
     <row r="3">
@@ -343,11 +343,11 @@
       </c>
       <c r="B3" s="3">
         <f t="shared" ref="B3:D3" si="3">IF(RAND()&lt;0.2,"NA",RANDBETWEEN(60,80))</f>
-        <v>76</v>
-      </c>
-      <c r="C3" s="3" t="str">
+        <v>64</v>
+      </c>
+      <c r="C3" s="3">
         <f t="shared" si="3"/>
-        <v>NA</v>
+        <v>63</v>
       </c>
       <c r="D3" s="3" t="str">
         <f t="shared" si="3"/>
@@ -355,11 +355,11 @@
       </c>
       <c r="E3" s="2">
         <f t="shared" si="4"/>
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="F3" s="2">
         <f t="shared" si="5"/>
-        <v>2021</v>
+        <v>2019</v>
       </c>
     </row>
     <row r="4">
@@ -369,23 +369,23 @@
       </c>
       <c r="B4" s="3">
         <f t="shared" ref="B4:D4" si="6">IF(RAND()&lt;0.2,"NA",RANDBETWEEN(60,80))</f>
-        <v>74</v>
+        <v>61</v>
       </c>
       <c r="C4" s="3">
         <f t="shared" si="6"/>
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="D4" s="3">
         <f t="shared" si="6"/>
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="E4" s="2">
         <f t="shared" si="4"/>
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="F4" s="2">
         <f t="shared" si="5"/>
-        <v>2020</v>
+        <v>2018</v>
       </c>
     </row>
     <row r="5">
@@ -393,25 +393,25 @@
         <f t="shared" si="2"/>
         <v>4</v>
       </c>
-      <c r="B5" s="3">
+      <c r="B5" s="3" t="str">
         <f t="shared" ref="B5:D5" si="7">IF(RAND()&lt;0.2,"NA",RANDBETWEEN(60,80))</f>
-        <v>70</v>
+        <v>NA</v>
       </c>
       <c r="C5" s="3">
         <f t="shared" si="7"/>
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="D5" s="3">
         <f t="shared" si="7"/>
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="E5" s="2">
         <f t="shared" si="4"/>
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="F5" s="2">
         <f t="shared" si="5"/>
-        <v>2020</v>
+        <v>2021</v>
       </c>
     </row>
     <row r="6">
@@ -419,25 +419,25 @@
         <f t="shared" si="2"/>
         <v>5</v>
       </c>
-      <c r="B6" s="3" t="str">
+      <c r="B6" s="3">
         <f t="shared" ref="B6:D6" si="8">IF(RAND()&lt;0.2,"NA",RANDBETWEEN(60,80))</f>
-        <v>NA</v>
+        <v>77</v>
       </c>
       <c r="C6" s="3">
         <f t="shared" si="8"/>
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="D6" s="3">
         <f t="shared" si="8"/>
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="E6" s="2">
         <f t="shared" si="4"/>
-        <v>82</v>
+        <v>89</v>
       </c>
       <c r="F6" s="2">
         <f t="shared" si="5"/>
-        <v>2020</v>
+        <v>2021</v>
       </c>
     </row>
     <row r="7">
@@ -447,19 +447,19 @@
       </c>
       <c r="B7" s="3">
         <f t="shared" ref="B7:D7" si="9">IF(RAND()&lt;0.2,"NA",RANDBETWEEN(60,80))</f>
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="C7" s="3">
         <f t="shared" si="9"/>
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="D7" s="3">
         <f t="shared" si="9"/>
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="E7" s="2">
         <f t="shared" si="4"/>
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="F7" s="2">
         <f t="shared" si="5"/>
@@ -473,15 +473,15 @@
       </c>
       <c r="B8" s="3">
         <f t="shared" ref="B8:D8" si="10">IF(RAND()&lt;0.2,"NA",RANDBETWEEN(60,80))</f>
-        <v>70</v>
+        <v>64</v>
       </c>
       <c r="C8" s="3">
         <f t="shared" si="10"/>
-        <v>76</v>
+        <v>71</v>
       </c>
       <c r="D8" s="3">
         <f t="shared" si="10"/>
-        <v>72</v>
+        <v>61</v>
       </c>
       <c r="E8" s="2">
         <f t="shared" si="4"/>
@@ -497,25 +497,25 @@
         <f t="shared" si="2"/>
         <v>8</v>
       </c>
-      <c r="B9" s="3">
+      <c r="B9" s="3" t="str">
         <f t="shared" ref="B9:D9" si="11">IF(RAND()&lt;0.2,"NA",RANDBETWEEN(60,80))</f>
-        <v>74</v>
-      </c>
-      <c r="C9" s="3">
+        <v>NA</v>
+      </c>
+      <c r="C9" s="3" t="str">
         <f t="shared" si="11"/>
-        <v>71</v>
+        <v>NA</v>
       </c>
       <c r="D9" s="3">
         <f t="shared" si="11"/>
-        <v>64</v>
+        <v>78</v>
       </c>
       <c r="E9" s="2">
         <f t="shared" si="4"/>
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="F9" s="2">
         <f t="shared" si="5"/>
-        <v>2021</v>
+        <v>2019</v>
       </c>
     </row>
     <row r="10">
@@ -525,23 +525,23 @@
       </c>
       <c r="B10" s="3">
         <f t="shared" ref="B10:D10" si="12">IF(RAND()&lt;0.2,"NA",RANDBETWEEN(60,80))</f>
-        <v>61</v>
-      </c>
-      <c r="C10" s="3" t="str">
+        <v>64</v>
+      </c>
+      <c r="C10" s="3">
         <f t="shared" si="12"/>
-        <v>NA</v>
+        <v>78</v>
       </c>
       <c r="D10" s="3">
         <f t="shared" si="12"/>
-        <v>65</v>
+        <v>77</v>
       </c>
       <c r="E10" s="2">
         <f t="shared" si="4"/>
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="F10" s="2">
         <f t="shared" si="5"/>
-        <v>2019</v>
+        <v>2021</v>
       </c>
     </row>
     <row r="11">
@@ -551,23 +551,23 @@
       </c>
       <c r="B11" s="3">
         <f t="shared" ref="B11:D11" si="13">IF(RAND()&lt;0.2,"NA",RANDBETWEEN(60,80))</f>
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="C11" s="3">
         <f t="shared" si="13"/>
-        <v>60</v>
-      </c>
-      <c r="D11" s="3" t="str">
+        <v>66</v>
+      </c>
+      <c r="D11" s="3">
         <f t="shared" si="13"/>
-        <v>NA</v>
+        <v>67</v>
       </c>
       <c r="E11" s="2">
         <f t="shared" si="4"/>
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="F11" s="2">
         <f t="shared" si="5"/>
-        <v>2019</v>
+        <v>2018</v>
       </c>
     </row>
     <row r="12">
@@ -577,11 +577,11 @@
       </c>
       <c r="B12" s="3">
         <f t="shared" ref="B12:D12" si="14">IF(RAND()&lt;0.2,"NA",RANDBETWEEN(60,80))</f>
-        <v>71</v>
+        <v>80</v>
       </c>
       <c r="C12" s="3">
         <f t="shared" si="14"/>
-        <v>63</v>
+        <v>79</v>
       </c>
       <c r="D12" s="3">
         <f t="shared" si="14"/>
@@ -589,11 +589,11 @@
       </c>
       <c r="E12" s="2">
         <f t="shared" si="4"/>
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="F12" s="2">
         <f t="shared" si="5"/>
-        <v>2021</v>
+        <v>2019</v>
       </c>
     </row>
     <row r="13">
@@ -603,23 +603,23 @@
       </c>
       <c r="B13" s="3">
         <f t="shared" ref="B13:D13" si="15">IF(RAND()&lt;0.2,"NA",RANDBETWEEN(60,80))</f>
-        <v>73</v>
-      </c>
-      <c r="C13" s="3" t="str">
+        <v>72</v>
+      </c>
+      <c r="C13" s="3">
         <f t="shared" si="15"/>
-        <v>NA</v>
+        <v>80</v>
       </c>
       <c r="D13" s="3">
         <f t="shared" si="15"/>
-        <v>75</v>
+        <v>62</v>
       </c>
       <c r="E13" s="2">
         <f t="shared" si="4"/>
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="F13" s="2">
         <f t="shared" si="5"/>
-        <v>2018</v>
+        <v>2021</v>
       </c>
     </row>
     <row r="14">
@@ -629,19 +629,19 @@
       </c>
       <c r="B14" s="3">
         <f t="shared" ref="B14:D14" si="16">IF(RAND()&lt;0.2,"NA",RANDBETWEEN(60,80))</f>
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="C14" s="3">
         <f t="shared" si="16"/>
-        <v>73</v>
-      </c>
-      <c r="D14" s="3" t="str">
+        <v>78</v>
+      </c>
+      <c r="D14" s="3">
         <f t="shared" si="16"/>
-        <v>NA</v>
+        <v>70</v>
       </c>
       <c r="E14" s="2">
         <f t="shared" si="4"/>
-        <v>84</v>
+        <v>78</v>
       </c>
       <c r="F14" s="2">
         <f t="shared" si="5"/>
@@ -655,23 +655,23 @@
       </c>
       <c r="B15" s="3">
         <f t="shared" ref="B15:D15" si="17">IF(RAND()&lt;0.2,"NA",RANDBETWEEN(60,80))</f>
-        <v>71</v>
-      </c>
-      <c r="C15" s="3" t="str">
+        <v>76</v>
+      </c>
+      <c r="C15" s="3">
         <f t="shared" si="17"/>
-        <v>NA</v>
+        <v>64</v>
       </c>
       <c r="D15" s="3">
         <f t="shared" si="17"/>
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="E15" s="2">
         <f t="shared" si="4"/>
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F15" s="2">
         <f t="shared" si="5"/>
-        <v>2020</v>
+        <v>2018</v>
       </c>
     </row>
     <row r="16">
@@ -679,25 +679,25 @@
         <f t="shared" si="2"/>
         <v>15</v>
       </c>
-      <c r="B16" s="3">
+      <c r="B16" s="3" t="str">
         <f t="shared" ref="B16:D16" si="18">IF(RAND()&lt;0.2,"NA",RANDBETWEEN(60,80))</f>
-        <v>71</v>
-      </c>
-      <c r="C16" s="3" t="str">
+        <v>NA</v>
+      </c>
+      <c r="C16" s="3">
         <f t="shared" si="18"/>
-        <v>NA</v>
-      </c>
-      <c r="D16" s="3">
+        <v>72</v>
+      </c>
+      <c r="D16" s="3" t="str">
         <f t="shared" si="18"/>
-        <v>62</v>
+        <v>NA</v>
       </c>
       <c r="E16" s="2">
         <f t="shared" si="4"/>
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="F16" s="2">
         <f t="shared" si="5"/>
-        <v>2020</v>
+        <v>2018</v>
       </c>
     </row>
     <row r="17">
@@ -705,25 +705,25 @@
         <f t="shared" si="2"/>
         <v>16</v>
       </c>
-      <c r="B17" s="3">
+      <c r="B17" s="3" t="str">
         <f t="shared" ref="B17:D17" si="19">IF(RAND()&lt;0.2,"NA",RANDBETWEEN(60,80))</f>
-        <v>75</v>
-      </c>
-      <c r="C17" s="3" t="str">
+        <v>NA</v>
+      </c>
+      <c r="C17" s="3">
         <f t="shared" si="19"/>
-        <v>NA</v>
-      </c>
-      <c r="D17" s="3">
+        <v>62</v>
+      </c>
+      <c r="D17" s="3" t="str">
         <f t="shared" si="19"/>
-        <v>78</v>
+        <v>NA</v>
       </c>
       <c r="E17" s="2">
         <f t="shared" si="4"/>
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="F17" s="2">
         <f t="shared" si="5"/>
-        <v>2021</v>
+        <v>2019</v>
       </c>
     </row>
     <row r="18">
@@ -733,23 +733,23 @@
       </c>
       <c r="B18" s="3">
         <f t="shared" ref="B18:D18" si="20">IF(RAND()&lt;0.2,"NA",RANDBETWEEN(60,80))</f>
-        <v>68</v>
+        <v>75</v>
       </c>
       <c r="C18" s="3">
         <f t="shared" si="20"/>
-        <v>66</v>
+        <v>75</v>
       </c>
       <c r="D18" s="3">
         <f t="shared" si="20"/>
-        <v>66</v>
+        <v>77</v>
       </c>
       <c r="E18" s="2">
         <f t="shared" si="4"/>
-        <v>75</v>
+        <v>5</v>
       </c>
       <c r="F18" s="2">
         <f t="shared" si="5"/>
-        <v>2020</v>
+        <v>2018</v>
       </c>
     </row>
     <row r="19">
@@ -757,21 +757,21 @@
         <f t="shared" si="2"/>
         <v>18</v>
       </c>
-      <c r="B19" s="3" t="str">
+      <c r="B19" s="3">
         <f t="shared" ref="B19:D19" si="21">IF(RAND()&lt;0.2,"NA",RANDBETWEEN(60,80))</f>
-        <v>NA</v>
+        <v>80</v>
       </c>
       <c r="C19" s="3">
         <f t="shared" si="21"/>
-        <v>72</v>
-      </c>
-      <c r="D19" s="3">
+        <v>70</v>
+      </c>
+      <c r="D19" s="3" t="str">
         <f t="shared" si="21"/>
-        <v>75</v>
+        <v>NA</v>
       </c>
       <c r="E19" s="2">
         <f t="shared" si="4"/>
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="F19" s="2">
         <f t="shared" si="5"/>
@@ -785,7 +785,7 @@
       </c>
       <c r="B20" s="3">
         <f t="shared" ref="B20:D20" si="22">IF(RAND()&lt;0.2,"NA",RANDBETWEEN(60,80))</f>
-        <v>60</v>
+        <v>75</v>
       </c>
       <c r="C20" s="3" t="str">
         <f t="shared" si="22"/>
@@ -793,15 +793,15 @@
       </c>
       <c r="D20" s="3">
         <f t="shared" si="22"/>
+        <v>71</v>
+      </c>
+      <c r="E20" s="2">
+        <f t="shared" si="4"/>
         <v>78</v>
       </c>
-      <c r="E20" s="2">
-        <f t="shared" si="4"/>
-        <v>80</v>
-      </c>
       <c r="F20" s="2">
         <f t="shared" si="5"/>
-        <v>2020</v>
+        <v>2021</v>
       </c>
     </row>
     <row r="21">
@@ -815,19 +815,19 @@
       </c>
       <c r="C21" s="3">
         <f t="shared" si="23"/>
-        <v>63</v>
+        <v>77</v>
       </c>
       <c r="D21" s="3">
         <f t="shared" si="23"/>
-        <v>60</v>
+        <v>75</v>
       </c>
       <c r="E21" s="2">
         <f t="shared" si="4"/>
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="F21" s="2">
         <f t="shared" si="5"/>
-        <v>2019</v>
+        <v>2018</v>
       </c>
     </row>
     <row r="22">
@@ -837,23 +837,23 @@
       </c>
       <c r="B22" s="3">
         <f t="shared" ref="B22:D22" si="24">IF(RAND()&lt;0.2,"NA",RANDBETWEEN(60,80))</f>
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="C22" s="3" t="str">
         <f t="shared" si="24"/>
         <v>NA</v>
       </c>
-      <c r="D22" s="3" t="str">
+      <c r="D22" s="3">
         <f t="shared" si="24"/>
-        <v>NA</v>
+        <v>62</v>
       </c>
       <c r="E22" s="2">
         <f t="shared" si="4"/>
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="F22" s="2">
         <f t="shared" si="5"/>
-        <v>2020</v>
+        <v>2018</v>
       </c>
     </row>
     <row r="23">
@@ -861,13 +861,13 @@
         <f t="shared" si="2"/>
         <v>22</v>
       </c>
-      <c r="B23" s="3">
+      <c r="B23" s="3" t="str">
         <f t="shared" ref="B23:D23" si="25">IF(RAND()&lt;0.2,"NA",RANDBETWEEN(60,80))</f>
-        <v>80</v>
-      </c>
-      <c r="C23" s="3" t="str">
+        <v>NA</v>
+      </c>
+      <c r="C23" s="3">
         <f t="shared" si="25"/>
-        <v>NA</v>
+        <v>67</v>
       </c>
       <c r="D23" s="3" t="str">
         <f t="shared" si="25"/>
@@ -875,11 +875,11 @@
       </c>
       <c r="E23" s="2">
         <f t="shared" si="4"/>
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="F23" s="2">
         <f t="shared" si="5"/>
-        <v>2019</v>
+        <v>2021</v>
       </c>
     </row>
     <row r="24">
@@ -887,25 +887,25 @@
         <f t="shared" si="2"/>
         <v>23</v>
       </c>
-      <c r="B24" s="3">
+      <c r="B24" s="3" t="str">
         <f t="shared" ref="B24:D24" si="26">IF(RAND()&lt;0.2,"NA",RANDBETWEEN(60,80))</f>
-        <v>66</v>
+        <v>NA</v>
       </c>
       <c r="C24" s="3">
         <f t="shared" si="26"/>
-        <v>75</v>
+        <v>63</v>
       </c>
       <c r="D24" s="3">
         <f t="shared" si="26"/>
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="E24" s="2">
         <f t="shared" si="4"/>
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="F24" s="2">
         <f t="shared" si="5"/>
-        <v>2020</v>
+        <v>2019</v>
       </c>
     </row>
     <row r="25">
@@ -915,23 +915,23 @@
       </c>
       <c r="B25" s="3">
         <f t="shared" ref="B25:D25" si="27">IF(RAND()&lt;0.2,"NA",RANDBETWEEN(60,80))</f>
-        <v>72</v>
-      </c>
-      <c r="C25" s="3">
+        <v>76</v>
+      </c>
+      <c r="C25" s="3" t="str">
         <f t="shared" si="27"/>
-        <v>69</v>
+        <v>NA</v>
       </c>
       <c r="D25" s="3">
         <f t="shared" si="27"/>
-        <v>72</v>
+        <v>66</v>
       </c>
       <c r="E25" s="2">
         <f t="shared" si="4"/>
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="F25" s="2">
         <f t="shared" si="5"/>
-        <v>2019</v>
+        <v>2020</v>
       </c>
     </row>
     <row r="26">
@@ -941,11 +941,11 @@
       </c>
       <c r="B26" s="3">
         <f t="shared" ref="B26:D26" si="28">IF(RAND()&lt;0.2,"NA",RANDBETWEEN(60,80))</f>
-        <v>72</v>
-      </c>
-      <c r="C26" s="3">
+        <v>66</v>
+      </c>
+      <c r="C26" s="3" t="str">
         <f t="shared" si="28"/>
-        <v>63</v>
+        <v>NA</v>
       </c>
       <c r="D26" s="3" t="str">
         <f t="shared" si="28"/>
@@ -953,11 +953,11 @@
       </c>
       <c r="E26" s="2">
         <f t="shared" si="4"/>
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="F26" s="2">
         <f t="shared" si="5"/>
-        <v>2018</v>
+        <v>2019</v>
       </c>
     </row>
     <row r="27">
@@ -967,23 +967,23 @@
       </c>
       <c r="B27" s="3">
         <f t="shared" ref="B27:D27" si="29">IF(RAND()&lt;0.2,"NA",RANDBETWEEN(60,80))</f>
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="C27" s="3">
         <f t="shared" si="29"/>
-        <v>80</v>
+        <v>62</v>
       </c>
       <c r="D27" s="3">
         <f t="shared" si="29"/>
-        <v>71</v>
+        <v>80</v>
       </c>
       <c r="E27" s="2">
         <f t="shared" si="4"/>
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="F27" s="2">
         <f t="shared" si="5"/>
-        <v>2019</v>
+        <v>2021</v>
       </c>
     </row>
     <row r="28">
@@ -991,25 +991,25 @@
         <f t="shared" si="2"/>
         <v>27</v>
       </c>
-      <c r="B28" s="3">
+      <c r="B28" s="3" t="str">
         <f t="shared" ref="B28:D28" si="30">IF(RAND()&lt;0.2,"NA",RANDBETWEEN(60,80))</f>
-        <v>73</v>
+        <v>NA</v>
       </c>
       <c r="C28" s="3">
         <f t="shared" si="30"/>
-        <v>62</v>
-      </c>
-      <c r="D28" s="3">
+        <v>75</v>
+      </c>
+      <c r="D28" s="3" t="str">
         <f t="shared" si="30"/>
-        <v>74</v>
+        <v>NA</v>
       </c>
       <c r="E28" s="2">
         <f t="shared" si="4"/>
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="F28" s="2">
         <f t="shared" si="5"/>
-        <v>2019</v>
+        <v>2018</v>
       </c>
     </row>
     <row r="29">
@@ -1019,19 +1019,19 @@
       </c>
       <c r="B29" s="3">
         <f t="shared" ref="B29:D29" si="31">IF(RAND()&lt;0.2,"NA",RANDBETWEEN(60,80))</f>
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="C29" s="3">
         <f t="shared" si="31"/>
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="D29" s="3">
         <f t="shared" si="31"/>
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="E29" s="2">
         <f t="shared" si="4"/>
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="F29" s="2">
         <f t="shared" si="5"/>
@@ -1049,15 +1049,15 @@
       </c>
       <c r="C30" s="3">
         <f t="shared" si="32"/>
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="D30" s="3">
         <f t="shared" si="32"/>
-        <v>64</v>
+        <v>76</v>
       </c>
       <c r="E30" s="2">
         <f t="shared" si="4"/>
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F30" s="2">
         <f t="shared" si="5"/>
@@ -1075,19 +1075,19 @@
       </c>
       <c r="C31" s="3">
         <f t="shared" si="33"/>
+        <v>74</v>
+      </c>
+      <c r="D31" s="3">
+        <f t="shared" si="33"/>
         <v>80</v>
       </c>
-      <c r="D31" s="3" t="str">
-        <f t="shared" si="33"/>
-        <v>NA</v>
-      </c>
       <c r="E31" s="2">
         <f t="shared" si="4"/>
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="F31" s="2">
         <f t="shared" si="5"/>
-        <v>2020</v>
+        <v>2019</v>
       </c>
     </row>
     <row r="32">
@@ -1095,25 +1095,25 @@
         <f t="shared" si="2"/>
         <v>31</v>
       </c>
-      <c r="B32" s="3">
+      <c r="B32" s="3" t="str">
         <f t="shared" ref="B32:D32" si="34">IF(RAND()&lt;0.2,"NA",RANDBETWEEN(60,80))</f>
-        <v>67</v>
-      </c>
-      <c r="C32" s="3">
+        <v>NA</v>
+      </c>
+      <c r="C32" s="3" t="str">
         <f t="shared" si="34"/>
-        <v>64</v>
+        <v>NA</v>
       </c>
       <c r="D32" s="3">
         <f t="shared" si="34"/>
-        <v>69</v>
+        <v>60</v>
       </c>
       <c r="E32" s="2">
         <f t="shared" si="4"/>
-        <v>77</v>
+        <v>500</v>
       </c>
       <c r="F32" s="2">
         <f t="shared" si="5"/>
-        <v>2018</v>
+        <v>2019</v>
       </c>
     </row>
     <row r="33">
@@ -1121,25 +1121,25 @@
         <f t="shared" si="2"/>
         <v>32</v>
       </c>
-      <c r="B33" s="3" t="str">
+      <c r="B33" s="3">
         <f t="shared" ref="B33:D33" si="35">IF(RAND()&lt;0.2,"NA",RANDBETWEEN(60,80))</f>
-        <v>NA</v>
+        <v>69</v>
       </c>
       <c r="C33" s="3">
         <f t="shared" si="35"/>
-        <v>75</v>
-      </c>
-      <c r="D33" s="3" t="str">
+        <v>74</v>
+      </c>
+      <c r="D33" s="3">
         <f t="shared" si="35"/>
-        <v>NA</v>
+        <v>69</v>
       </c>
       <c r="E33" s="2">
         <f t="shared" si="4"/>
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="F33" s="2">
         <f t="shared" si="5"/>
-        <v>2018</v>
+        <v>2021</v>
       </c>
     </row>
     <row r="34">
@@ -1149,23 +1149,23 @@
       </c>
       <c r="B34" s="3">
         <f t="shared" ref="B34:D34" si="36">IF(RAND()&lt;0.2,"NA",RANDBETWEEN(60,80))</f>
-        <v>75</v>
+        <v>62</v>
       </c>
       <c r="C34" s="3">
         <f t="shared" si="36"/>
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="D34" s="3">
         <f t="shared" si="36"/>
-        <v>80</v>
+        <v>65</v>
       </c>
       <c r="E34" s="2">
         <f t="shared" si="4"/>
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="F34" s="2">
         <f t="shared" si="5"/>
-        <v>2021</v>
+        <v>2019</v>
       </c>
     </row>
     <row r="35">
@@ -1175,11 +1175,11 @@
       </c>
       <c r="B35" s="3">
         <f t="shared" ref="B35:D35" si="37">IF(RAND()&lt;0.2,"NA",RANDBETWEEN(60,80))</f>
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C35" s="3">
         <f t="shared" si="37"/>
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="D35" s="3">
         <f t="shared" si="37"/>
@@ -1187,11 +1187,11 @@
       </c>
       <c r="E35" s="2">
         <f t="shared" si="4"/>
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="F35" s="2">
         <f t="shared" si="5"/>
-        <v>2018</v>
+        <v>2019</v>
       </c>
     </row>
     <row r="36">
@@ -1199,25 +1199,25 @@
         <f t="shared" si="2"/>
         <v>35</v>
       </c>
-      <c r="B36" s="3" t="str">
+      <c r="B36" s="3">
         <f t="shared" ref="B36:D36" si="38">IF(RAND()&lt;0.2,"NA",RANDBETWEEN(60,80))</f>
-        <v>NA</v>
+        <v>76</v>
       </c>
       <c r="C36" s="3">
         <f t="shared" si="38"/>
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="D36" s="3">
         <f t="shared" si="38"/>
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="E36" s="2">
         <f t="shared" si="4"/>
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="F36" s="2">
         <f t="shared" si="5"/>
-        <v>2021</v>
+        <v>2018</v>
       </c>
     </row>
     <row r="37">
@@ -1227,23 +1227,23 @@
       </c>
       <c r="B37" s="3">
         <f t="shared" ref="B37:D37" si="39">IF(RAND()&lt;0.2,"NA",RANDBETWEEN(60,80))</f>
-        <v>64</v>
-      </c>
-      <c r="C37" s="3" t="str">
+        <v>63</v>
+      </c>
+      <c r="C37" s="3">
         <f t="shared" si="39"/>
-        <v>NA</v>
+        <v>69</v>
       </c>
       <c r="D37" s="3">
         <f t="shared" si="39"/>
-        <v>69</v>
+        <v>80</v>
       </c>
       <c r="E37" s="2">
         <f t="shared" si="4"/>
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="F37" s="2">
         <f t="shared" si="5"/>
-        <v>2020</v>
+        <v>2019</v>
       </c>
     </row>
     <row r="38">
@@ -1253,11 +1253,11 @@
       </c>
       <c r="B38" s="3">
         <f t="shared" ref="B38:D38" si="40">IF(RAND()&lt;0.2,"NA",RANDBETWEEN(60,80))</f>
-        <v>65</v>
-      </c>
-      <c r="C38" s="3" t="str">
+        <v>74</v>
+      </c>
+      <c r="C38" s="3">
         <f t="shared" si="40"/>
-        <v>NA</v>
+        <v>63</v>
       </c>
       <c r="D38" s="3" t="str">
         <f t="shared" si="40"/>
@@ -1265,7 +1265,7 @@
       </c>
       <c r="E38" s="2">
         <f t="shared" si="4"/>
-        <v>5</v>
+        <v>85</v>
       </c>
       <c r="F38" s="2">
         <f t="shared" si="5"/>
@@ -1279,23 +1279,23 @@
       </c>
       <c r="B39" s="3">
         <f t="shared" ref="B39:D39" si="41">IF(RAND()&lt;0.2,"NA",RANDBETWEEN(60,80))</f>
-        <v>78</v>
+        <v>64</v>
       </c>
       <c r="C39" s="3">
         <f t="shared" si="41"/>
-        <v>67</v>
-      </c>
-      <c r="D39" s="3" t="str">
+        <v>68</v>
+      </c>
+      <c r="D39" s="3">
         <f t="shared" si="41"/>
-        <v>NA</v>
+        <v>68</v>
       </c>
       <c r="E39" s="2">
         <f t="shared" si="4"/>
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="F39" s="2">
         <f t="shared" si="5"/>
-        <v>2018</v>
+        <v>2019</v>
       </c>
     </row>
     <row r="40">
@@ -1305,23 +1305,23 @@
       </c>
       <c r="B40" s="3">
         <f t="shared" ref="B40:D40" si="42">IF(RAND()&lt;0.2,"NA",RANDBETWEEN(60,80))</f>
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="C40" s="3">
         <f t="shared" si="42"/>
-        <v>61</v>
+        <v>77</v>
       </c>
       <c r="D40" s="3">
         <f t="shared" si="42"/>
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="E40" s="2">
         <f t="shared" si="4"/>
-        <v>5</v>
+        <v>79</v>
       </c>
       <c r="F40" s="2">
         <f t="shared" si="5"/>
-        <v>2018</v>
+        <v>2021</v>
       </c>
     </row>
     <row r="41">
@@ -1331,23 +1331,23 @@
       </c>
       <c r="B41" s="3">
         <f t="shared" ref="B41:D41" si="43">IF(RAND()&lt;0.2,"NA",RANDBETWEEN(60,80))</f>
-        <v>72</v>
+        <v>79</v>
       </c>
       <c r="C41" s="3">
         <f t="shared" si="43"/>
-        <v>63</v>
-      </c>
-      <c r="D41" s="3">
+        <v>65</v>
+      </c>
+      <c r="D41" s="3" t="str">
         <f t="shared" si="43"/>
-        <v>73</v>
+        <v>NA</v>
       </c>
       <c r="E41" s="2">
         <f t="shared" si="4"/>
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="F41" s="2">
         <f t="shared" si="5"/>
-        <v>2019</v>
+        <v>2020</v>
       </c>
     </row>
     <row r="42">
@@ -1357,23 +1357,23 @@
       </c>
       <c r="B42" s="3">
         <f t="shared" ref="B42:D42" si="44">IF(RAND()&lt;0.2,"NA",RANDBETWEEN(60,80))</f>
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="C42" s="3" t="str">
         <f t="shared" si="44"/>
         <v>NA</v>
       </c>
-      <c r="D42" s="3" t="str">
+      <c r="D42" s="3">
         <f t="shared" si="44"/>
-        <v>NA</v>
+        <v>64</v>
       </c>
       <c r="E42" s="2">
         <f t="shared" si="4"/>
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="F42" s="2">
         <f t="shared" si="5"/>
-        <v>2020</v>
+        <v>2019</v>
       </c>
     </row>
     <row r="43">
@@ -1381,21 +1381,21 @@
         <f t="shared" si="2"/>
         <v>42</v>
       </c>
-      <c r="B43" s="3" t="str">
+      <c r="B43" s="3">
         <f t="shared" ref="B43:D43" si="45">IF(RAND()&lt;0.2,"NA",RANDBETWEEN(60,80))</f>
-        <v>NA</v>
-      </c>
-      <c r="C43" s="3">
+        <v>76</v>
+      </c>
+      <c r="C43" s="3" t="str">
         <f t="shared" si="45"/>
-        <v>75</v>
+        <v>NA</v>
       </c>
       <c r="D43" s="3">
         <f t="shared" si="45"/>
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="E43" s="2">
         <f t="shared" si="4"/>
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="F43" s="2">
         <f t="shared" si="5"/>
@@ -1409,23 +1409,23 @@
       </c>
       <c r="B44" s="3">
         <f t="shared" ref="B44:D44" si="46">IF(RAND()&lt;0.2,"NA",RANDBETWEEN(60,80))</f>
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="C44" s="3">
         <f t="shared" si="46"/>
-        <v>61</v>
+        <v>76</v>
       </c>
       <c r="D44" s="3">
         <f t="shared" si="46"/>
-        <v>62</v>
+        <v>72</v>
       </c>
       <c r="E44" s="2">
         <f t="shared" si="4"/>
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="F44" s="2">
         <f t="shared" si="5"/>
-        <v>2019</v>
+        <v>2018</v>
       </c>
     </row>
     <row r="45">
@@ -1435,19 +1435,19 @@
       </c>
       <c r="B45" s="3">
         <f t="shared" ref="B45:D45" si="47">IF(RAND()&lt;0.2,"NA",RANDBETWEEN(60,80))</f>
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C45" s="3">
         <f t="shared" si="47"/>
-        <v>68</v>
+        <v>79</v>
       </c>
       <c r="D45" s="3">
         <f t="shared" si="47"/>
-        <v>74</v>
+        <v>64</v>
       </c>
       <c r="E45" s="2">
         <f t="shared" si="4"/>
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="F45" s="2">
         <f t="shared" si="5"/>
@@ -1459,25 +1459,25 @@
         <f t="shared" si="2"/>
         <v>45</v>
       </c>
-      <c r="B46" s="3" t="str">
+      <c r="B46" s="3">
         <f t="shared" ref="B46:D46" si="48">IF(RAND()&lt;0.2,"NA",RANDBETWEEN(60,80))</f>
-        <v>NA</v>
+        <v>66</v>
       </c>
       <c r="C46" s="3">
         <f t="shared" si="48"/>
-        <v>66</v>
-      </c>
-      <c r="D46" s="3">
+        <v>80</v>
+      </c>
+      <c r="D46" s="3" t="str">
         <f t="shared" si="48"/>
-        <v>60</v>
+        <v>NA</v>
       </c>
       <c r="E46" s="2">
         <f t="shared" si="4"/>
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="F46" s="2">
         <f t="shared" si="5"/>
-        <v>2018</v>
+        <v>2021</v>
       </c>
     </row>
     <row r="47">
@@ -1485,13 +1485,13 @@
         <f t="shared" si="2"/>
         <v>46</v>
       </c>
-      <c r="B47" s="3" t="str">
+      <c r="B47" s="3">
         <f t="shared" ref="B47:D47" si="49">IF(RAND()&lt;0.2,"NA",RANDBETWEEN(60,80))</f>
-        <v>NA</v>
+        <v>74</v>
       </c>
       <c r="C47" s="3">
         <f t="shared" si="49"/>
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="D47" s="3" t="str">
         <f t="shared" si="49"/>
@@ -1499,11 +1499,11 @@
       </c>
       <c r="E47" s="2">
         <f t="shared" si="4"/>
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="F47" s="2">
         <f t="shared" si="5"/>
-        <v>2018</v>
+        <v>2021</v>
       </c>
     </row>
     <row r="48">
@@ -1511,21 +1511,21 @@
         <f t="shared" si="2"/>
         <v>47</v>
       </c>
-      <c r="B48" s="3">
+      <c r="B48" s="3" t="str">
         <f t="shared" ref="B48:D48" si="50">IF(RAND()&lt;0.2,"NA",RANDBETWEEN(60,80))</f>
-        <v>76</v>
-      </c>
-      <c r="C48" s="3" t="str">
+        <v>NA</v>
+      </c>
+      <c r="C48" s="3">
         <f t="shared" si="50"/>
-        <v>NA</v>
+        <v>61</v>
       </c>
       <c r="D48" s="3">
         <f t="shared" si="50"/>
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="E48" s="2">
         <f t="shared" si="4"/>
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="F48" s="2">
         <f t="shared" si="5"/>
@@ -1539,23 +1539,23 @@
       </c>
       <c r="B49" s="3">
         <f t="shared" ref="B49:D49" si="51">IF(RAND()&lt;0.2,"NA",RANDBETWEEN(60,80))</f>
-        <v>63</v>
-      </c>
-      <c r="C49" s="3">
+        <v>64</v>
+      </c>
+      <c r="C49" s="3" t="str">
         <f t="shared" si="51"/>
-        <v>64</v>
+        <v>NA</v>
       </c>
       <c r="D49" s="3">
         <f t="shared" si="51"/>
-        <v>74</v>
+        <v>69</v>
       </c>
       <c r="E49" s="2">
         <f t="shared" si="4"/>
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="F49" s="2">
         <f t="shared" si="5"/>
-        <v>2021</v>
+        <v>2020</v>
       </c>
     </row>
     <row r="50">
@@ -1565,11 +1565,11 @@
       </c>
       <c r="B50" s="3">
         <f t="shared" ref="B50:D50" si="52">IF(RAND()&lt;0.2,"NA",RANDBETWEEN(60,80))</f>
-        <v>63</v>
+        <v>77</v>
       </c>
       <c r="C50" s="3">
         <f t="shared" si="52"/>
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="D50" s="3" t="str">
         <f t="shared" si="52"/>
@@ -1577,7 +1577,7 @@
       </c>
       <c r="E50" s="2">
         <f t="shared" si="4"/>
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="F50" s="2">
         <f t="shared" si="5"/>
@@ -1589,25 +1589,25 @@
         <f t="shared" si="2"/>
         <v>50</v>
       </c>
-      <c r="B51" s="3" t="str">
+      <c r="B51" s="3">
         <f t="shared" ref="B51:D51" si="53">IF(RAND()&lt;0.2,"NA",RANDBETWEEN(60,80))</f>
-        <v>NA</v>
+        <v>63</v>
       </c>
       <c r="C51" s="3">
         <f t="shared" si="53"/>
-        <v>65</v>
+        <v>78</v>
       </c>
       <c r="D51" s="3">
         <f t="shared" si="53"/>
-        <v>78</v>
+        <v>63</v>
       </c>
       <c r="E51" s="2">
         <f t="shared" si="4"/>
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="F51" s="2">
         <f t="shared" si="5"/>
-        <v>2020</v>
+        <v>2021</v>
       </c>
     </row>
     <row r="52">
@@ -1617,11 +1617,11 @@
       </c>
       <c r="B52" s="3">
         <f t="shared" ref="B52:D52" si="54">IF(RAND()&lt;0.2,"NA",RANDBETWEEN(60,80))</f>
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="C52" s="3">
         <f t="shared" si="54"/>
-        <v>62</v>
+        <v>68</v>
       </c>
       <c r="D52" s="3" t="str">
         <f t="shared" si="54"/>
@@ -1629,7 +1629,7 @@
       </c>
       <c r="E52" s="2">
         <f t="shared" si="4"/>
-        <v>500</v>
+        <v>90</v>
       </c>
       <c r="F52" s="2">
         <f t="shared" si="5"/>
@@ -1641,25 +1641,25 @@
         <f t="shared" si="2"/>
         <v>52</v>
       </c>
-      <c r="B53" s="3" t="str">
+      <c r="B53" s="3">
         <f t="shared" ref="B53:D53" si="55">IF(RAND()&lt;0.2,"NA",RANDBETWEEN(60,80))</f>
-        <v>NA</v>
+        <v>63</v>
       </c>
       <c r="C53" s="3">
         <f t="shared" si="55"/>
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="D53" s="3">
         <f t="shared" si="55"/>
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E53" s="2">
         <f t="shared" si="4"/>
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="F53" s="2">
         <f t="shared" si="5"/>
-        <v>2021</v>
+        <v>2019</v>
       </c>
     </row>
     <row r="54">
@@ -1667,25 +1667,25 @@
         <f t="shared" si="2"/>
         <v>53</v>
       </c>
-      <c r="B54" s="3" t="str">
+      <c r="B54" s="3">
         <f t="shared" ref="B54:D54" si="56">IF(RAND()&lt;0.2,"NA",RANDBETWEEN(60,80))</f>
-        <v>NA</v>
-      </c>
-      <c r="C54" s="3">
+        <v>79</v>
+      </c>
+      <c r="C54" s="3" t="str">
         <f t="shared" si="56"/>
-        <v>70</v>
+        <v>NA</v>
       </c>
       <c r="D54" s="3">
         <f t="shared" si="56"/>
-        <v>60</v>
+        <v>67</v>
       </c>
       <c r="E54" s="2">
         <f t="shared" si="4"/>
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="F54" s="2">
         <f t="shared" si="5"/>
-        <v>2018</v>
+        <v>2019</v>
       </c>
     </row>
     <row r="55">
@@ -1695,23 +1695,23 @@
       </c>
       <c r="B55" s="3">
         <f t="shared" ref="B55:D55" si="57">IF(RAND()&lt;0.2,"NA",RANDBETWEEN(60,80))</f>
-        <v>80</v>
+        <v>73</v>
       </c>
       <c r="C55" s="3">
         <f t="shared" si="57"/>
-        <v>65</v>
-      </c>
-      <c r="D55" s="3">
+        <v>79</v>
+      </c>
+      <c r="D55" s="3" t="str">
         <f t="shared" si="57"/>
-        <v>60</v>
+        <v>NA</v>
       </c>
       <c r="E55" s="2">
         <f t="shared" si="4"/>
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="F55" s="2">
         <f t="shared" si="5"/>
-        <v>2021</v>
+        <v>2020</v>
       </c>
     </row>
     <row r="56">
@@ -1721,7 +1721,7 @@
       </c>
       <c r="B56" s="3">
         <f t="shared" ref="B56:D56" si="58">IF(RAND()&lt;0.2,"NA",RANDBETWEEN(60,80))</f>
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C56" s="3" t="str">
         <f t="shared" si="58"/>
@@ -1729,15 +1729,15 @@
       </c>
       <c r="D56" s="3">
         <f t="shared" si="58"/>
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="E56" s="2">
         <f t="shared" si="4"/>
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="F56" s="2">
         <f t="shared" si="5"/>
-        <v>2020</v>
+        <v>2019</v>
       </c>
     </row>
     <row r="57">
@@ -1745,25 +1745,25 @@
         <f t="shared" si="2"/>
         <v>56</v>
       </c>
-      <c r="B57" s="3">
+      <c r="B57" s="3" t="str">
         <f t="shared" ref="B57:D57" si="59">IF(RAND()&lt;0.2,"NA",RANDBETWEEN(60,80))</f>
-        <v>61</v>
+        <v>NA</v>
       </c>
       <c r="C57" s="3">
         <f t="shared" si="59"/>
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D57" s="3">
         <f t="shared" si="59"/>
-        <v>77</v>
+        <v>60</v>
       </c>
       <c r="E57" s="2">
         <f t="shared" si="4"/>
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="F57" s="2">
         <f t="shared" si="5"/>
-        <v>2021</v>
+        <v>2020</v>
       </c>
     </row>
     <row r="58">
@@ -1771,25 +1771,25 @@
         <f t="shared" si="2"/>
         <v>57</v>
       </c>
-      <c r="B58" s="3">
+      <c r="B58" s="3" t="str">
         <f t="shared" ref="B58:D58" si="60">IF(RAND()&lt;0.2,"NA",RANDBETWEEN(60,80))</f>
-        <v>75</v>
+        <v>NA</v>
       </c>
       <c r="C58" s="3">
         <f t="shared" si="60"/>
-        <v>67</v>
+        <v>62</v>
       </c>
       <c r="D58" s="3">
         <f t="shared" si="60"/>
-        <v>62</v>
+        <v>74</v>
       </c>
       <c r="E58" s="2">
         <f t="shared" si="4"/>
-        <v>86</v>
+        <v>75</v>
       </c>
       <c r="F58" s="2">
         <f t="shared" si="5"/>
-        <v>2018</v>
+        <v>2020</v>
       </c>
     </row>
     <row r="59">
@@ -1797,25 +1797,25 @@
         <f t="shared" si="2"/>
         <v>58</v>
       </c>
-      <c r="B59" s="3">
+      <c r="B59" s="3" t="str">
         <f t="shared" ref="B59:D59" si="61">IF(RAND()&lt;0.2,"NA",RANDBETWEEN(60,80))</f>
-        <v>74</v>
-      </c>
-      <c r="C59" s="3" t="str">
+        <v>NA</v>
+      </c>
+      <c r="C59" s="3">
         <f t="shared" si="61"/>
-        <v>NA</v>
+        <v>76</v>
       </c>
       <c r="D59" s="3">
         <f t="shared" si="61"/>
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="E59" s="2">
         <f t="shared" si="4"/>
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="F59" s="2">
         <f t="shared" si="5"/>
-        <v>2019</v>
+        <v>2018</v>
       </c>
     </row>
     <row r="60">
@@ -1825,19 +1825,19 @@
       </c>
       <c r="B60" s="3">
         <f t="shared" ref="B60:D60" si="62">IF(RAND()&lt;0.2,"NA",RANDBETWEEN(60,80))</f>
-        <v>76</v>
-      </c>
-      <c r="C60" s="3" t="str">
+        <v>63</v>
+      </c>
+      <c r="C60" s="3">
         <f t="shared" si="62"/>
-        <v>NA</v>
-      </c>
-      <c r="D60" s="3" t="str">
+        <v>72</v>
+      </c>
+      <c r="D60" s="3">
         <f t="shared" si="62"/>
-        <v>NA</v>
+        <v>74</v>
       </c>
       <c r="E60" s="2">
         <f t="shared" si="4"/>
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="F60" s="2">
         <f t="shared" si="5"/>
@@ -1851,23 +1851,23 @@
       </c>
       <c r="B61" s="3">
         <f t="shared" ref="B61:D61" si="63">IF(RAND()&lt;0.2,"NA",RANDBETWEEN(60,80))</f>
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C61" s="3">
         <f t="shared" si="63"/>
-        <v>73</v>
+        <v>60</v>
       </c>
       <c r="D61" s="3">
         <f t="shared" si="63"/>
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="E61" s="2">
         <f t="shared" si="4"/>
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="F61" s="2">
         <f t="shared" si="5"/>
-        <v>2018</v>
+        <v>2021</v>
       </c>
     </row>
     <row r="62">
@@ -1875,25 +1875,25 @@
         <f t="shared" si="2"/>
         <v>61</v>
       </c>
-      <c r="B62" s="3" t="str">
+      <c r="B62" s="3">
         <f t="shared" ref="B62:D62" si="64">IF(RAND()&lt;0.2,"NA",RANDBETWEEN(60,80))</f>
-        <v>NA</v>
+        <v>62</v>
       </c>
       <c r="C62" s="3">
         <f t="shared" si="64"/>
-        <v>79</v>
-      </c>
-      <c r="D62" s="3">
+        <v>75</v>
+      </c>
+      <c r="D62" s="3" t="str">
         <f t="shared" si="64"/>
-        <v>76</v>
+        <v>NA</v>
       </c>
       <c r="E62" s="2">
         <f t="shared" si="4"/>
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="F62" s="2">
         <f t="shared" si="5"/>
-        <v>2019</v>
+        <v>2020</v>
       </c>
     </row>
     <row r="63">
@@ -1903,23 +1903,23 @@
       </c>
       <c r="B63" s="3">
         <f t="shared" ref="B63:D63" si="65">IF(RAND()&lt;0.2,"NA",RANDBETWEEN(60,80))</f>
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="C63" s="3">
         <f t="shared" si="65"/>
-        <v>76</v>
+        <v>67</v>
       </c>
       <c r="D63" s="3">
         <f t="shared" si="65"/>
-        <v>80</v>
+        <v>66</v>
       </c>
       <c r="E63" s="2">
         <f t="shared" si="4"/>
-        <v>84</v>
+        <v>500</v>
       </c>
       <c r="F63" s="2">
         <f t="shared" si="5"/>
-        <v>2020</v>
+        <v>2019</v>
       </c>
     </row>
     <row r="64">
@@ -1929,23 +1929,23 @@
       </c>
       <c r="B64" s="3">
         <f t="shared" ref="B64:D64" si="66">IF(RAND()&lt;0.2,"NA",RANDBETWEEN(60,80))</f>
-        <v>71</v>
-      </c>
-      <c r="C64" s="3" t="str">
-        <f t="shared" si="66"/>
-        <v>NA</v>
-      </c>
-      <c r="D64" s="3">
+        <v>67</v>
+      </c>
+      <c r="C64" s="3">
         <f t="shared" si="66"/>
         <v>63</v>
       </c>
+      <c r="D64" s="3" t="str">
+        <f t="shared" si="66"/>
+        <v>NA</v>
+      </c>
       <c r="E64" s="2">
         <f t="shared" si="4"/>
-        <v>80</v>
+        <v>500</v>
       </c>
       <c r="F64" s="2">
         <f t="shared" si="5"/>
-        <v>2019</v>
+        <v>2021</v>
       </c>
     </row>
     <row r="65">
@@ -1953,25 +1953,25 @@
         <f t="shared" si="2"/>
         <v>64</v>
       </c>
-      <c r="B65" s="3">
+      <c r="B65" s="3" t="str">
         <f t="shared" ref="B65:D65" si="67">IF(RAND()&lt;0.2,"NA",RANDBETWEEN(60,80))</f>
-        <v>77</v>
+        <v>NA</v>
       </c>
       <c r="C65" s="3" t="str">
         <f t="shared" si="67"/>
         <v>NA</v>
       </c>
-      <c r="D65" s="3" t="str">
+      <c r="D65" s="3">
         <f t="shared" si="67"/>
-        <v>NA</v>
+        <v>80</v>
       </c>
       <c r="E65" s="2">
         <f t="shared" si="4"/>
-        <v>86</v>
+        <v>80</v>
       </c>
       <c r="F65" s="2">
         <f t="shared" si="5"/>
-        <v>2020</v>
+        <v>2021</v>
       </c>
     </row>
     <row r="66">
@@ -1981,23 +1981,23 @@
       </c>
       <c r="B66" s="3">
         <f t="shared" ref="B66:D66" si="68">IF(RAND()&lt;0.2,"NA",RANDBETWEEN(60,80))</f>
-        <v>75</v>
-      </c>
-      <c r="C66" s="3" t="str">
+        <v>71</v>
+      </c>
+      <c r="C66" s="3">
         <f t="shared" si="68"/>
-        <v>NA</v>
+        <v>71</v>
       </c>
       <c r="D66" s="3">
         <f t="shared" si="68"/>
-        <v>77</v>
+        <v>63</v>
       </c>
       <c r="E66" s="2">
         <f t="shared" si="4"/>
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="F66" s="2">
         <f t="shared" si="5"/>
-        <v>2019</v>
+        <v>2020</v>
       </c>
     </row>
     <row r="67">
@@ -2011,19 +2011,19 @@
       </c>
       <c r="C67" s="3">
         <f t="shared" si="69"/>
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="D67" s="3">
         <f t="shared" si="69"/>
-        <v>76</v>
+        <v>64</v>
       </c>
       <c r="E67" s="2">
         <f t="shared" si="4"/>
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F67" s="2">
         <f t="shared" si="5"/>
-        <v>2018</v>
+        <v>2021</v>
       </c>
     </row>
     <row r="68">
@@ -2033,23 +2033,23 @@
       </c>
       <c r="B68" s="3">
         <f t="shared" ref="B68:D68" si="70">IF(RAND()&lt;0.2,"NA",RANDBETWEEN(60,80))</f>
-        <v>70</v>
+        <v>78</v>
       </c>
       <c r="C68" s="3">
         <f t="shared" si="70"/>
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D68" s="3">
         <f t="shared" si="70"/>
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="E68" s="2">
         <f t="shared" si="4"/>
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="F68" s="2">
         <f t="shared" si="5"/>
-        <v>2019</v>
+        <v>2021</v>
       </c>
     </row>
     <row r="69">
@@ -2057,25 +2057,25 @@
         <f t="shared" si="2"/>
         <v>68</v>
       </c>
-      <c r="B69" s="3">
+      <c r="B69" s="3" t="str">
         <f t="shared" ref="B69:D69" si="71">IF(RAND()&lt;0.2,"NA",RANDBETWEEN(60,80))</f>
-        <v>71</v>
+        <v>NA</v>
       </c>
       <c r="C69" s="3">
         <f t="shared" si="71"/>
-        <v>63</v>
+        <v>69</v>
       </c>
       <c r="D69" s="3">
         <f t="shared" si="71"/>
-        <v>64</v>
+        <v>70</v>
       </c>
       <c r="E69" s="2">
         <f t="shared" si="4"/>
-        <v>87</v>
+        <v>82</v>
       </c>
       <c r="F69" s="2">
         <f t="shared" si="5"/>
-        <v>2019</v>
+        <v>2021</v>
       </c>
     </row>
     <row r="70">
@@ -2085,23 +2085,23 @@
       </c>
       <c r="B70" s="3">
         <f t="shared" ref="B70:D70" si="72">IF(RAND()&lt;0.2,"NA",RANDBETWEEN(60,80))</f>
-        <v>63</v>
-      </c>
-      <c r="C70" s="3">
+        <v>75</v>
+      </c>
+      <c r="C70" s="3" t="str">
         <f t="shared" si="72"/>
-        <v>77</v>
+        <v>NA</v>
       </c>
       <c r="D70" s="3">
         <f t="shared" si="72"/>
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="E70" s="2">
         <f t="shared" si="4"/>
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="F70" s="2">
         <f t="shared" si="5"/>
-        <v>2021</v>
+        <v>2019</v>
       </c>
     </row>
     <row r="71">
@@ -2111,11 +2111,11 @@
       </c>
       <c r="B71" s="3">
         <f t="shared" ref="B71:D71" si="73">IF(RAND()&lt;0.2,"NA",RANDBETWEEN(60,80))</f>
-        <v>73</v>
+        <v>64</v>
       </c>
       <c r="C71" s="3">
         <f t="shared" si="73"/>
-        <v>66</v>
+        <v>79</v>
       </c>
       <c r="D71" s="3">
         <f t="shared" si="73"/>
@@ -2123,7 +2123,7 @@
       </c>
       <c r="E71" s="2">
         <f t="shared" si="4"/>
-        <v>82</v>
+        <v>500</v>
       </c>
       <c r="F71" s="2">
         <f t="shared" si="5"/>
@@ -2135,25 +2135,25 @@
         <f t="shared" si="2"/>
         <v>71</v>
       </c>
-      <c r="B72" s="3">
+      <c r="B72" s="3" t="str">
         <f t="shared" ref="B72:D72" si="74">IF(RAND()&lt;0.2,"NA",RANDBETWEEN(60,80))</f>
-        <v>76</v>
+        <v>NA</v>
       </c>
       <c r="C72" s="3">
         <f t="shared" si="74"/>
+        <v>67</v>
+      </c>
+      <c r="D72" s="3" t="str">
+        <f t="shared" si="74"/>
+        <v>NA</v>
+      </c>
+      <c r="E72" s="2">
+        <f t="shared" si="4"/>
         <v>75</v>
       </c>
-      <c r="D72" s="3">
-        <f t="shared" si="74"/>
-        <v>63</v>
-      </c>
-      <c r="E72" s="2">
-        <f t="shared" si="4"/>
-        <v>89</v>
-      </c>
       <c r="F72" s="2">
         <f t="shared" si="5"/>
-        <v>2020</v>
+        <v>2018</v>
       </c>
     </row>
     <row r="73">
@@ -2167,19 +2167,19 @@
       </c>
       <c r="C73" s="3">
         <f t="shared" si="75"/>
-        <v>68</v>
-      </c>
-      <c r="D73" s="3" t="str">
+        <v>61</v>
+      </c>
+      <c r="D73" s="3">
         <f t="shared" si="75"/>
-        <v>NA</v>
+        <v>79</v>
       </c>
       <c r="E73" s="2">
         <f t="shared" si="4"/>
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="F73" s="2">
         <f t="shared" si="5"/>
-        <v>2018</v>
+        <v>2019</v>
       </c>
     </row>
     <row r="74">
@@ -2189,23 +2189,23 @@
       </c>
       <c r="B74" s="3">
         <f t="shared" ref="B74:D74" si="76">IF(RAND()&lt;0.2,"NA",RANDBETWEEN(60,80))</f>
-        <v>61</v>
+        <v>76</v>
       </c>
       <c r="C74" s="3">
         <f t="shared" si="76"/>
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="D74" s="3">
         <f t="shared" si="76"/>
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E74" s="2">
         <f t="shared" si="4"/>
-        <v>75</v>
+        <v>88</v>
       </c>
       <c r="F74" s="2">
         <f t="shared" si="5"/>
-        <v>2018</v>
+        <v>2019</v>
       </c>
     </row>
     <row r="75">
@@ -2213,25 +2213,25 @@
         <f t="shared" si="2"/>
         <v>74</v>
       </c>
-      <c r="B75" s="3">
+      <c r="B75" s="3" t="str">
         <f t="shared" ref="B75:D75" si="77">IF(RAND()&lt;0.2,"NA",RANDBETWEEN(60,80))</f>
-        <v>67</v>
+        <v>NA</v>
       </c>
       <c r="C75" s="3">
         <f t="shared" si="77"/>
-        <v>67</v>
+        <v>79</v>
       </c>
       <c r="D75" s="3">
         <f t="shared" si="77"/>
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="E75" s="2">
         <f t="shared" si="4"/>
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="F75" s="2">
         <f t="shared" si="5"/>
-        <v>2021</v>
+        <v>2020</v>
       </c>
     </row>
     <row r="76">
@@ -2245,19 +2245,19 @@
       </c>
       <c r="C76" s="3">
         <f t="shared" si="78"/>
-        <v>68</v>
-      </c>
-      <c r="D76" s="3">
+        <v>71</v>
+      </c>
+      <c r="D76" s="3" t="str">
         <f t="shared" si="78"/>
-        <v>68</v>
+        <v>NA</v>
       </c>
       <c r="E76" s="2">
         <f t="shared" si="4"/>
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="F76" s="2">
         <f t="shared" si="5"/>
-        <v>2021</v>
+        <v>2018</v>
       </c>
     </row>
     <row r="77">
@@ -2267,23 +2267,23 @@
       </c>
       <c r="B77" s="3">
         <f t="shared" ref="B77:D77" si="79">IF(RAND()&lt;0.2,"NA",RANDBETWEEN(60,80))</f>
-        <v>65</v>
+        <v>77</v>
       </c>
       <c r="C77" s="3">
         <f t="shared" si="79"/>
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="D77" s="3">
         <f t="shared" si="79"/>
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="E77" s="2">
         <f t="shared" si="4"/>
-        <v>88</v>
+        <v>76</v>
       </c>
       <c r="F77" s="2">
         <f t="shared" si="5"/>
-        <v>2018</v>
+        <v>2019</v>
       </c>
     </row>
     <row r="78">
@@ -2291,21 +2291,21 @@
         <f t="shared" si="2"/>
         <v>77</v>
       </c>
-      <c r="B78" s="3">
+      <c r="B78" s="3" t="str">
         <f t="shared" ref="B78:D78" si="80">IF(RAND()&lt;0.2,"NA",RANDBETWEEN(60,80))</f>
-        <v>78</v>
-      </c>
-      <c r="C78" s="3">
+        <v>NA</v>
+      </c>
+      <c r="C78" s="3" t="str">
         <f t="shared" si="80"/>
-        <v>73</v>
-      </c>
-      <c r="D78" s="3">
+        <v>NA</v>
+      </c>
+      <c r="D78" s="3" t="str">
         <f t="shared" si="80"/>
-        <v>64</v>
+        <v>NA</v>
       </c>
       <c r="E78" s="2">
         <f t="shared" si="4"/>
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="F78" s="2">
         <f t="shared" si="5"/>
@@ -2319,11 +2319,11 @@
       </c>
       <c r="B79" s="3">
         <f t="shared" ref="B79:D79" si="81">IF(RAND()&lt;0.2,"NA",RANDBETWEEN(60,80))</f>
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="C79" s="3">
         <f t="shared" si="81"/>
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D79" s="3">
         <f t="shared" si="81"/>
@@ -2331,7 +2331,7 @@
       </c>
       <c r="E79" s="2">
         <f t="shared" si="4"/>
-        <v>86</v>
+        <v>80</v>
       </c>
       <c r="F79" s="2">
         <f t="shared" si="5"/>
@@ -2343,21 +2343,21 @@
         <f t="shared" si="2"/>
         <v>79</v>
       </c>
-      <c r="B80" s="3" t="str">
+      <c r="B80" s="3">
         <f t="shared" ref="B80:D80" si="82">IF(RAND()&lt;0.2,"NA",RANDBETWEEN(60,80))</f>
-        <v>NA</v>
+        <v>77</v>
       </c>
       <c r="C80" s="3" t="str">
         <f t="shared" si="82"/>
         <v>NA</v>
       </c>
-      <c r="D80" s="3" t="str">
+      <c r="D80" s="3">
         <f t="shared" si="82"/>
-        <v>NA</v>
+        <v>71</v>
       </c>
       <c r="E80" s="2">
         <f t="shared" si="4"/>
-        <v>87</v>
+        <v>77</v>
       </c>
       <c r="F80" s="2">
         <f t="shared" si="5"/>
@@ -2371,23 +2371,23 @@
       </c>
       <c r="B81" s="3">
         <f t="shared" ref="B81:D81" si="83">IF(RAND()&lt;0.2,"NA",RANDBETWEEN(60,80))</f>
-        <v>63</v>
+        <v>71</v>
       </c>
       <c r="C81" s="3">
         <f t="shared" si="83"/>
-        <v>65</v>
+        <v>76</v>
       </c>
       <c r="D81" s="3">
         <f t="shared" si="83"/>
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="E81" s="2">
         <f t="shared" si="4"/>
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="F81" s="2">
         <f t="shared" si="5"/>
-        <v>2019</v>
+        <v>2018</v>
       </c>
     </row>
     <row r="82">
@@ -2395,25 +2395,25 @@
         <f t="shared" si="2"/>
         <v>81</v>
       </c>
-      <c r="B82" s="3" t="str">
+      <c r="B82" s="3">
         <f t="shared" ref="B82:D82" si="84">IF(RAND()&lt;0.2,"NA",RANDBETWEEN(60,80))</f>
-        <v>NA</v>
+        <v>78</v>
       </c>
       <c r="C82" s="3">
         <f t="shared" si="84"/>
-        <v>63</v>
-      </c>
-      <c r="D82" s="3">
+        <v>72</v>
+      </c>
+      <c r="D82" s="3" t="str">
         <f t="shared" si="84"/>
-        <v>67</v>
+        <v>NA</v>
       </c>
       <c r="E82" s="2">
         <f t="shared" si="4"/>
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="F82" s="2">
         <f t="shared" si="5"/>
-        <v>2019</v>
+        <v>2020</v>
       </c>
     </row>
     <row r="83">
@@ -2423,19 +2423,19 @@
       </c>
       <c r="B83" s="3">
         <f t="shared" ref="B83:D83" si="85">IF(RAND()&lt;0.2,"NA",RANDBETWEEN(60,80))</f>
-        <v>72</v>
-      </c>
-      <c r="C83" s="3">
+        <v>61</v>
+      </c>
+      <c r="C83" s="3" t="str">
         <f t="shared" si="85"/>
-        <v>64</v>
+        <v>NA</v>
       </c>
       <c r="D83" s="3">
         <f t="shared" si="85"/>
-        <v>74</v>
+        <v>61</v>
       </c>
       <c r="E83" s="2">
         <f t="shared" si="4"/>
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="F83" s="2">
         <f t="shared" si="5"/>
@@ -2449,23 +2449,23 @@
       </c>
       <c r="B84" s="3">
         <f t="shared" ref="B84:D84" si="86">IF(RAND()&lt;0.2,"NA",RANDBETWEEN(60,80))</f>
-        <v>74</v>
-      </c>
-      <c r="C84" s="3" t="str">
+        <v>66</v>
+      </c>
+      <c r="C84" s="3">
         <f t="shared" si="86"/>
-        <v>NA</v>
+        <v>72</v>
       </c>
       <c r="D84" s="3">
         <f t="shared" si="86"/>
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E84" s="2">
         <f t="shared" si="4"/>
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="F84" s="2">
         <f t="shared" si="5"/>
-        <v>2018</v>
+        <v>2020</v>
       </c>
     </row>
     <row r="85">
@@ -2475,23 +2475,23 @@
       </c>
       <c r="B85" s="3">
         <f t="shared" ref="B85:D85" si="87">IF(RAND()&lt;0.2,"NA",RANDBETWEEN(60,80))</f>
-        <v>72</v>
-      </c>
-      <c r="C85" s="3" t="str">
+        <v>61</v>
+      </c>
+      <c r="C85" s="3">
         <f t="shared" si="87"/>
-        <v>NA</v>
+        <v>77</v>
       </c>
       <c r="D85" s="3">
         <f t="shared" si="87"/>
-        <v>67</v>
+        <v>75</v>
       </c>
       <c r="E85" s="2">
         <f t="shared" si="4"/>
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="F85" s="2">
         <f t="shared" si="5"/>
-        <v>2018</v>
+        <v>2019</v>
       </c>
     </row>
     <row r="86">
@@ -2501,23 +2501,23 @@
       </c>
       <c r="B86" s="3">
         <f t="shared" ref="B86:D86" si="88">IF(RAND()&lt;0.2,"NA",RANDBETWEEN(60,80))</f>
-        <v>78</v>
-      </c>
-      <c r="C86" s="3">
+        <v>61</v>
+      </c>
+      <c r="C86" s="3" t="str">
         <f t="shared" si="88"/>
-        <v>63</v>
+        <v>NA</v>
       </c>
       <c r="D86" s="3">
         <f t="shared" si="88"/>
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="E86" s="2">
         <f t="shared" si="4"/>
-        <v>86</v>
+        <v>79</v>
       </c>
       <c r="F86" s="2">
         <f t="shared" si="5"/>
-        <v>2018</v>
+        <v>2019</v>
       </c>
     </row>
     <row r="87">
@@ -2527,19 +2527,19 @@
       </c>
       <c r="B87" s="3">
         <f t="shared" ref="B87:D87" si="89">IF(RAND()&lt;0.2,"NA",RANDBETWEEN(60,80))</f>
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="C87" s="3">
         <f t="shared" si="89"/>
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="D87" s="3">
         <f t="shared" si="89"/>
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E87" s="2">
         <f t="shared" si="4"/>
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="F87" s="2">
         <f t="shared" si="5"/>
@@ -2551,9 +2551,9 @@
         <f t="shared" si="2"/>
         <v>87</v>
       </c>
-      <c r="B88" s="3">
+      <c r="B88" s="3" t="str">
         <f t="shared" ref="B88:D88" si="90">IF(RAND()&lt;0.2,"NA",RANDBETWEEN(60,80))</f>
-        <v>66</v>
+        <v>NA</v>
       </c>
       <c r="C88" s="3">
         <f t="shared" si="90"/>
@@ -2561,15 +2561,15 @@
       </c>
       <c r="D88" s="3">
         <f t="shared" si="90"/>
-        <v>62</v>
+        <v>77</v>
       </c>
       <c r="E88" s="2">
         <f t="shared" si="4"/>
-        <v>89</v>
+        <v>75</v>
       </c>
       <c r="F88" s="2">
         <f t="shared" si="5"/>
-        <v>2019</v>
+        <v>2020</v>
       </c>
     </row>
     <row r="89">
@@ -2579,23 +2579,23 @@
       </c>
       <c r="B89" s="3">
         <f t="shared" ref="B89:D89" si="91">IF(RAND()&lt;0.2,"NA",RANDBETWEEN(60,80))</f>
-        <v>69</v>
+        <v>61</v>
       </c>
       <c r="C89" s="3">
         <f t="shared" si="91"/>
-        <v>61</v>
-      </c>
-      <c r="D89" s="3" t="str">
+        <v>79</v>
+      </c>
+      <c r="D89" s="3">
         <f t="shared" si="91"/>
-        <v>NA</v>
+        <v>64</v>
       </c>
       <c r="E89" s="2">
         <f t="shared" si="4"/>
-        <v>86</v>
+        <v>75</v>
       </c>
       <c r="F89" s="2">
         <f t="shared" si="5"/>
-        <v>2020</v>
+        <v>2019</v>
       </c>
     </row>
     <row r="90">
@@ -2605,23 +2605,23 @@
       </c>
       <c r="B90" s="3">
         <f t="shared" ref="B90:D90" si="92">IF(RAND()&lt;0.2,"NA",RANDBETWEEN(60,80))</f>
-        <v>76</v>
+        <v>61</v>
       </c>
       <c r="C90" s="3">
         <f t="shared" si="92"/>
-        <v>70</v>
+        <v>77</v>
       </c>
       <c r="D90" s="3">
         <f t="shared" si="92"/>
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="E90" s="2">
         <f t="shared" si="4"/>
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="F90" s="2">
         <f t="shared" si="5"/>
-        <v>2020</v>
+        <v>2018</v>
       </c>
     </row>
     <row r="91">
@@ -2631,19 +2631,19 @@
       </c>
       <c r="B91" s="3">
         <f t="shared" ref="B91:D91" si="93">IF(RAND()&lt;0.2,"NA",RANDBETWEEN(60,80))</f>
-        <v>79</v>
-      </c>
-      <c r="C91" s="3" t="str">
+        <v>80</v>
+      </c>
+      <c r="C91" s="3">
         <f t="shared" si="93"/>
-        <v>NA</v>
-      </c>
-      <c r="D91" s="3">
+        <v>73</v>
+      </c>
+      <c r="D91" s="3" t="str">
         <f t="shared" si="93"/>
-        <v>65</v>
+        <v>NA</v>
       </c>
       <c r="E91" s="2">
         <f t="shared" si="4"/>
-        <v>89</v>
+        <v>82</v>
       </c>
       <c r="F91" s="2">
         <f t="shared" si="5"/>
@@ -2661,19 +2661,19 @@
       </c>
       <c r="C92" s="3">
         <f t="shared" si="94"/>
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="D92" s="3">
         <f t="shared" si="94"/>
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="E92" s="2">
         <f t="shared" si="4"/>
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="F92" s="2">
         <f t="shared" si="5"/>
-        <v>2019</v>
+        <v>2021</v>
       </c>
     </row>
     <row r="93">
@@ -2681,25 +2681,25 @@
         <f t="shared" si="2"/>
         <v>92</v>
       </c>
-      <c r="B93" s="3" t="str">
+      <c r="B93" s="3">
         <f t="shared" ref="B93:D93" si="95">IF(RAND()&lt;0.2,"NA",RANDBETWEEN(60,80))</f>
-        <v>NA</v>
+        <v>60</v>
       </c>
       <c r="C93" s="3">
         <f t="shared" si="95"/>
-        <v>68</v>
+        <v>60</v>
       </c>
       <c r="D93" s="3">
         <f t="shared" si="95"/>
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="E93" s="2">
         <f t="shared" si="4"/>
-        <v>84</v>
+        <v>500</v>
       </c>
       <c r="F93" s="2">
         <f t="shared" si="5"/>
-        <v>2021</v>
+        <v>2019</v>
       </c>
     </row>
     <row r="94">
@@ -2707,25 +2707,25 @@
         <f t="shared" si="2"/>
         <v>93</v>
       </c>
-      <c r="B94" s="3" t="str">
+      <c r="B94" s="3">
         <f t="shared" ref="B94:D94" si="96">IF(RAND()&lt;0.2,"NA",RANDBETWEEN(60,80))</f>
-        <v>NA</v>
+        <v>63</v>
       </c>
       <c r="C94" s="3">
         <f t="shared" si="96"/>
-        <v>66</v>
-      </c>
-      <c r="D94" s="3">
+        <v>73</v>
+      </c>
+      <c r="D94" s="3" t="str">
         <f t="shared" si="96"/>
-        <v>71</v>
+        <v>NA</v>
       </c>
       <c r="E94" s="2">
         <f t="shared" si="4"/>
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="F94" s="2">
         <f t="shared" si="5"/>
-        <v>2021</v>
+        <v>2019</v>
       </c>
     </row>
     <row r="95">
@@ -2735,23 +2735,23 @@
       </c>
       <c r="B95" s="3">
         <f t="shared" ref="B95:D95" si="97">IF(RAND()&lt;0.2,"NA",RANDBETWEEN(60,80))</f>
-        <v>68</v>
+        <v>80</v>
       </c>
       <c r="C95" s="3">
         <f t="shared" si="97"/>
-        <v>64</v>
-      </c>
-      <c r="D95" s="3">
+        <v>65</v>
+      </c>
+      <c r="D95" s="3" t="str">
         <f t="shared" si="97"/>
-        <v>65</v>
+        <v>NA</v>
       </c>
       <c r="E95" s="2">
         <f t="shared" si="4"/>
-        <v>79</v>
+        <v>500</v>
       </c>
       <c r="F95" s="2">
         <f t="shared" si="5"/>
-        <v>2018</v>
+        <v>2019</v>
       </c>
     </row>
     <row r="96">
@@ -2759,25 +2759,25 @@
         <f t="shared" si="2"/>
         <v>95</v>
       </c>
-      <c r="B96" s="3" t="str">
+      <c r="B96" s="3">
         <f t="shared" ref="B96:D96" si="98">IF(RAND()&lt;0.2,"NA",RANDBETWEEN(60,80))</f>
-        <v>NA</v>
+        <v>61</v>
       </c>
       <c r="C96" s="3">
         <f t="shared" si="98"/>
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="D96" s="3">
         <f t="shared" si="98"/>
-        <v>60</v>
+        <v>77</v>
       </c>
       <c r="E96" s="2">
         <f t="shared" si="4"/>
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="F96" s="2">
         <f t="shared" si="5"/>
-        <v>2019</v>
+        <v>2020</v>
       </c>
     </row>
     <row r="97">
@@ -2787,23 +2787,23 @@
       </c>
       <c r="B97" s="3">
         <f t="shared" ref="B97:D97" si="99">IF(RAND()&lt;0.2,"NA",RANDBETWEEN(60,80))</f>
-        <v>63</v>
+        <v>78</v>
       </c>
       <c r="C97" s="3">
         <f t="shared" si="99"/>
-        <v>69</v>
-      </c>
-      <c r="D97" s="3" t="str">
+        <v>63</v>
+      </c>
+      <c r="D97" s="3">
         <f t="shared" si="99"/>
-        <v>NA</v>
+        <v>66</v>
       </c>
       <c r="E97" s="2">
         <f t="shared" si="4"/>
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="F97" s="2">
         <f t="shared" si="5"/>
-        <v>2019</v>
+        <v>2018</v>
       </c>
     </row>
     <row r="98">
@@ -2813,19 +2813,19 @@
       </c>
       <c r="B98" s="3">
         <f t="shared" ref="B98:D98" si="100">IF(RAND()&lt;0.2,"NA",RANDBETWEEN(60,80))</f>
-        <v>61</v>
+        <v>74</v>
       </c>
       <c r="C98" s="3">
         <f t="shared" si="100"/>
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="D98" s="3">
         <f t="shared" si="100"/>
-        <v>60</v>
+        <v>67</v>
       </c>
       <c r="E98" s="2">
         <f t="shared" si="4"/>
-        <v>500</v>
+        <v>88</v>
       </c>
       <c r="F98" s="2">
         <f t="shared" si="5"/>
@@ -2837,21 +2837,21 @@
         <f t="shared" si="2"/>
         <v>98</v>
       </c>
-      <c r="B99" s="3" t="str">
+      <c r="B99" s="3">
         <f t="shared" ref="B99:D99" si="101">IF(RAND()&lt;0.2,"NA",RANDBETWEEN(60,80))</f>
-        <v>NA</v>
+        <v>76</v>
       </c>
       <c r="C99" s="3">
         <f t="shared" si="101"/>
-        <v>75</v>
-      </c>
-      <c r="D99" s="3" t="str">
+        <v>68</v>
+      </c>
+      <c r="D99" s="3">
         <f t="shared" si="101"/>
-        <v>NA</v>
+        <v>74</v>
       </c>
       <c r="E99" s="2">
         <f t="shared" si="4"/>
-        <v>89</v>
+        <v>76</v>
       </c>
       <c r="F99" s="2">
         <f t="shared" si="5"/>
@@ -2863,17 +2863,17 @@
         <f t="shared" si="2"/>
         <v>99</v>
       </c>
-      <c r="B100" s="3">
+      <c r="B100" s="3" t="str">
         <f t="shared" ref="B100:D100" si="102">IF(RAND()&lt;0.2,"NA",RANDBETWEEN(60,80))</f>
-        <v>64</v>
-      </c>
-      <c r="C100" s="3" t="str">
+        <v>NA</v>
+      </c>
+      <c r="C100" s="3">
         <f t="shared" si="102"/>
-        <v>NA</v>
-      </c>
-      <c r="D100" s="3">
+        <v>60</v>
+      </c>
+      <c r="D100" s="3" t="str">
         <f t="shared" si="102"/>
-        <v>63</v>
+        <v>NA</v>
       </c>
       <c r="E100" s="2">
         <f t="shared" si="4"/>
@@ -2881,7 +2881,7 @@
       </c>
       <c r="F100" s="2">
         <f t="shared" si="5"/>
-        <v>2018</v>
+        <v>2019</v>
       </c>
     </row>
     <row r="101">
@@ -2891,19 +2891,19 @@
       </c>
       <c r="B101" s="3">
         <f t="shared" ref="B101:D101" si="103">IF(RAND()&lt;0.2,"NA",RANDBETWEEN(60,80))</f>
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="C101" s="3">
         <f t="shared" si="103"/>
-        <v>73</v>
+        <v>66</v>
       </c>
       <c r="D101" s="3">
         <f t="shared" si="103"/>
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="E101" s="2">
         <f t="shared" si="4"/>
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="F101" s="2">
         <f t="shared" si="5"/>
@@ -2917,19 +2917,19 @@
       </c>
       <c r="B102" s="3">
         <f t="shared" ref="B102:D102" si="104">IF(RAND()&lt;0.2,"NA",RANDBETWEEN(60,80))</f>
-        <v>61</v>
+        <v>73</v>
       </c>
       <c r="C102" s="3">
         <f t="shared" si="104"/>
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="D102" s="3">
         <f t="shared" si="104"/>
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="E102" s="2">
         <f t="shared" si="4"/>
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="F102" s="2">
         <f t="shared" si="5"/>
@@ -2943,23 +2943,23 @@
       </c>
       <c r="B103" s="3">
         <f t="shared" ref="B103:D103" si="105">IF(RAND()&lt;0.2,"NA",RANDBETWEEN(60,80))</f>
-        <v>78</v>
+        <v>63</v>
       </c>
       <c r="C103" s="3">
         <f t="shared" si="105"/>
-        <v>69</v>
-      </c>
-      <c r="D103" s="3" t="str">
+        <v>79</v>
+      </c>
+      <c r="D103" s="3">
         <f t="shared" si="105"/>
-        <v>NA</v>
+        <v>62</v>
       </c>
       <c r="E103" s="2">
         <f t="shared" si="4"/>
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="F103" s="2">
         <f t="shared" si="5"/>
-        <v>2019</v>
+        <v>2018</v>
       </c>
     </row>
     <row r="104">
@@ -2969,23 +2969,23 @@
       </c>
       <c r="B104" s="3">
         <f t="shared" ref="B104:D104" si="106">IF(RAND()&lt;0.2,"NA",RANDBETWEEN(60,80))</f>
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="C104" s="3">
         <f t="shared" si="106"/>
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D104" s="3">
         <f t="shared" si="106"/>
-        <v>79</v>
+        <v>64</v>
       </c>
       <c r="E104" s="2">
         <f t="shared" si="4"/>
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="F104" s="2">
         <f t="shared" si="5"/>
-        <v>2020</v>
+        <v>2021</v>
       </c>
     </row>
     <row r="105">
@@ -2995,7 +2995,7 @@
       </c>
       <c r="B105" s="3">
         <f t="shared" ref="B105:D105" si="107">IF(RAND()&lt;0.2,"NA",RANDBETWEEN(60,80))</f>
-        <v>73</v>
+        <v>80</v>
       </c>
       <c r="C105" s="3">
         <f t="shared" si="107"/>
@@ -3003,15 +3003,15 @@
       </c>
       <c r="D105" s="3">
         <f t="shared" si="107"/>
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="E105" s="2">
         <f t="shared" si="4"/>
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="F105" s="2">
         <f t="shared" si="5"/>
-        <v>2019</v>
+        <v>2018</v>
       </c>
     </row>
     <row r="106">
@@ -3021,23 +3021,23 @@
       </c>
       <c r="B106" s="3">
         <f t="shared" ref="B106:D106" si="108">IF(RAND()&lt;0.2,"NA",RANDBETWEEN(60,80))</f>
-        <v>78</v>
-      </c>
-      <c r="C106" s="3" t="str">
+        <v>67</v>
+      </c>
+      <c r="C106" s="3">
         <f t="shared" si="108"/>
-        <v>NA</v>
-      </c>
-      <c r="D106" s="3" t="str">
+        <v>61</v>
+      </c>
+      <c r="D106" s="3">
         <f t="shared" si="108"/>
-        <v>NA</v>
+        <v>60</v>
       </c>
       <c r="E106" s="2">
         <f t="shared" si="4"/>
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="F106" s="2">
         <f t="shared" si="5"/>
-        <v>2021</v>
+        <v>2018</v>
       </c>
     </row>
     <row r="107">
@@ -3047,23 +3047,23 @@
       </c>
       <c r="B107" s="3">
         <f t="shared" ref="B107:D107" si="109">IF(RAND()&lt;0.2,"NA",RANDBETWEEN(60,80))</f>
-        <v>75</v>
+        <v>64</v>
       </c>
       <c r="C107" s="3">
         <f t="shared" si="109"/>
-        <v>64</v>
+        <v>80</v>
       </c>
       <c r="D107" s="3">
         <f t="shared" si="109"/>
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="E107" s="2">
         <f t="shared" si="4"/>
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="F107" s="2">
         <f t="shared" si="5"/>
-        <v>2019</v>
+        <v>2018</v>
       </c>
     </row>
     <row r="108">
@@ -3073,19 +3073,19 @@
       </c>
       <c r="B108" s="3">
         <f t="shared" ref="B108:D108" si="110">IF(RAND()&lt;0.2,"NA",RANDBETWEEN(60,80))</f>
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="C108" s="3">
         <f t="shared" si="110"/>
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="D108" s="3">
         <f t="shared" si="110"/>
-        <v>60</v>
+        <v>75</v>
       </c>
       <c r="E108" s="2">
         <f t="shared" si="4"/>
-        <v>89</v>
+        <v>83</v>
       </c>
       <c r="F108" s="2">
         <f t="shared" si="5"/>
@@ -3099,23 +3099,23 @@
       </c>
       <c r="B109" s="3">
         <f t="shared" ref="B109:D109" si="111">IF(RAND()&lt;0.2,"NA",RANDBETWEEN(60,80))</f>
-        <v>80</v>
-      </c>
-      <c r="C109" s="3" t="str">
+        <v>71</v>
+      </c>
+      <c r="C109" s="3">
         <f t="shared" si="111"/>
-        <v>NA</v>
-      </c>
-      <c r="D109" s="3" t="str">
+        <v>66</v>
+      </c>
+      <c r="D109" s="3">
         <f t="shared" si="111"/>
-        <v>NA</v>
+        <v>64</v>
       </c>
       <c r="E109" s="2">
         <f t="shared" si="4"/>
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="F109" s="2">
         <f t="shared" si="5"/>
-        <v>2020</v>
+        <v>2018</v>
       </c>
     </row>
     <row r="110">
@@ -3125,23 +3125,23 @@
       </c>
       <c r="B110" s="3">
         <f t="shared" ref="B110:D110" si="112">IF(RAND()&lt;0.2,"NA",RANDBETWEEN(60,80))</f>
-        <v>69</v>
+        <v>79</v>
       </c>
       <c r="C110" s="3">
         <f t="shared" si="112"/>
-        <v>77</v>
+        <v>60</v>
       </c>
       <c r="D110" s="3">
         <f t="shared" si="112"/>
-        <v>60</v>
+        <v>75</v>
       </c>
       <c r="E110" s="2">
         <f t="shared" si="4"/>
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="F110" s="2">
         <f t="shared" si="5"/>
-        <v>2020</v>
+        <v>2019</v>
       </c>
     </row>
     <row r="111">
@@ -3151,19 +3151,19 @@
       </c>
       <c r="B111" s="3">
         <f t="shared" ref="B111:D111" si="113">IF(RAND()&lt;0.2,"NA",RANDBETWEEN(60,80))</f>
-        <v>71</v>
-      </c>
-      <c r="C111" s="3" t="str">
+        <v>72</v>
+      </c>
+      <c r="C111" s="3">
         <f t="shared" si="113"/>
-        <v>NA</v>
-      </c>
-      <c r="D111" s="3" t="str">
+        <v>64</v>
+      </c>
+      <c r="D111" s="3">
         <f t="shared" si="113"/>
-        <v>NA</v>
+        <v>64</v>
       </c>
       <c r="E111" s="2">
         <f t="shared" si="4"/>
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="F111" s="2">
         <f t="shared" si="5"/>
@@ -3177,23 +3177,23 @@
       </c>
       <c r="B112" s="3">
         <f t="shared" ref="B112:D112" si="114">IF(RAND()&lt;0.2,"NA",RANDBETWEEN(60,80))</f>
-        <v>74</v>
-      </c>
-      <c r="C112" s="3">
+        <v>80</v>
+      </c>
+      <c r="C112" s="3" t="str">
         <f t="shared" si="114"/>
-        <v>62</v>
+        <v>NA</v>
       </c>
       <c r="D112" s="3">
         <f t="shared" si="114"/>
-        <v>63</v>
+        <v>76</v>
       </c>
       <c r="E112" s="2">
         <f t="shared" si="4"/>
-        <v>78</v>
+        <v>500</v>
       </c>
       <c r="F112" s="2">
         <f t="shared" si="5"/>
-        <v>2021</v>
+        <v>2018</v>
       </c>
     </row>
     <row r="113">
@@ -3203,23 +3203,23 @@
       </c>
       <c r="B113" s="3">
         <f t="shared" ref="B113:D113" si="115">IF(RAND()&lt;0.2,"NA",RANDBETWEEN(60,80))</f>
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="C113" s="3">
         <f t="shared" si="115"/>
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="D113" s="3">
         <f t="shared" si="115"/>
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="E113" s="2">
         <f t="shared" si="4"/>
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="F113" s="2">
         <f t="shared" si="5"/>
-        <v>2018</v>
+        <v>2021</v>
       </c>
     </row>
     <row r="114">
@@ -3227,25 +3227,25 @@
         <f t="shared" si="2"/>
         <v>113</v>
       </c>
-      <c r="B114" s="3">
+      <c r="B114" s="3" t="str">
         <f t="shared" ref="B114:D114" si="116">IF(RAND()&lt;0.2,"NA",RANDBETWEEN(60,80))</f>
-        <v>67</v>
+        <v>NA</v>
       </c>
       <c r="C114" s="3">
         <f t="shared" si="116"/>
-        <v>66</v>
-      </c>
-      <c r="D114" s="3">
+        <v>61</v>
+      </c>
+      <c r="D114" s="3" t="str">
         <f t="shared" si="116"/>
-        <v>66</v>
+        <v>NA</v>
       </c>
       <c r="E114" s="2">
         <f t="shared" si="4"/>
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="F114" s="2">
         <f t="shared" si="5"/>
-        <v>2018</v>
+        <v>2020</v>
       </c>
     </row>
     <row r="115">
@@ -3253,25 +3253,25 @@
         <f t="shared" si="2"/>
         <v>114</v>
       </c>
-      <c r="B115" s="3" t="str">
+      <c r="B115" s="3">
         <f t="shared" ref="B115:D115" si="117">IF(RAND()&lt;0.2,"NA",RANDBETWEEN(60,80))</f>
-        <v>NA</v>
-      </c>
-      <c r="C115" s="3" t="str">
+        <v>75</v>
+      </c>
+      <c r="C115" s="3">
         <f t="shared" si="117"/>
-        <v>NA</v>
-      </c>
-      <c r="D115" s="3">
+        <v>61</v>
+      </c>
+      <c r="D115" s="3" t="str">
         <f t="shared" si="117"/>
-        <v>72</v>
+        <v>NA</v>
       </c>
       <c r="E115" s="2">
         <f t="shared" si="4"/>
-        <v>500</v>
+        <v>79</v>
       </c>
       <c r="F115" s="2">
         <f t="shared" si="5"/>
-        <v>2019</v>
+        <v>2018</v>
       </c>
     </row>
     <row r="116">
@@ -3281,19 +3281,19 @@
       </c>
       <c r="B116" s="3">
         <f t="shared" ref="B116:D116" si="118">IF(RAND()&lt;0.2,"NA",RANDBETWEEN(60,80))</f>
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="C116" s="3">
         <f t="shared" si="118"/>
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="D116" s="3">
         <f t="shared" si="118"/>
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="E116" s="2">
         <f t="shared" si="4"/>
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="F116" s="2">
         <f t="shared" si="5"/>
@@ -3305,17 +3305,17 @@
         <f t="shared" si="2"/>
         <v>116</v>
       </c>
-      <c r="B117" s="3">
+      <c r="B117" s="3" t="str">
         <f t="shared" ref="B117:D117" si="119">IF(RAND()&lt;0.2,"NA",RANDBETWEEN(60,80))</f>
-        <v>72</v>
+        <v>NA</v>
       </c>
       <c r="C117" s="3">
         <f t="shared" si="119"/>
-        <v>68</v>
+        <v>80</v>
       </c>
       <c r="D117" s="3">
         <f t="shared" si="119"/>
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="E117" s="2">
         <f t="shared" si="4"/>
@@ -3323,7 +3323,7 @@
       </c>
       <c r="F117" s="2">
         <f t="shared" si="5"/>
-        <v>2021</v>
+        <v>2019</v>
       </c>
     </row>
     <row r="118">
@@ -3333,23 +3333,23 @@
       </c>
       <c r="B118" s="3">
         <f t="shared" ref="B118:D118" si="120">IF(RAND()&lt;0.2,"NA",RANDBETWEEN(60,80))</f>
-        <v>80</v>
+        <v>66</v>
       </c>
       <c r="C118" s="3">
         <f t="shared" si="120"/>
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="D118" s="3">
         <f t="shared" si="120"/>
-        <v>74</v>
+        <v>62</v>
       </c>
       <c r="E118" s="2">
         <f t="shared" si="4"/>
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="F118" s="2">
         <f t="shared" si="5"/>
-        <v>2021</v>
+        <v>2019</v>
       </c>
     </row>
     <row r="119">
@@ -3359,19 +3359,19 @@
       </c>
       <c r="B119" s="3">
         <f t="shared" ref="B119:D119" si="121">IF(RAND()&lt;0.2,"NA",RANDBETWEEN(60,80))</f>
-        <v>66</v>
+        <v>77</v>
       </c>
       <c r="C119" s="3">
         <f t="shared" si="121"/>
-        <v>71</v>
-      </c>
-      <c r="D119" s="3">
+        <v>61</v>
+      </c>
+      <c r="D119" s="3" t="str">
         <f t="shared" si="121"/>
-        <v>73</v>
+        <v>NA</v>
       </c>
       <c r="E119" s="2">
         <f t="shared" si="4"/>
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="F119" s="2">
         <f t="shared" si="5"/>
@@ -3385,23 +3385,23 @@
       </c>
       <c r="B120" s="3">
         <f t="shared" ref="B120:D120" si="122">IF(RAND()&lt;0.2,"NA",RANDBETWEEN(60,80))</f>
-        <v>66</v>
+        <v>77</v>
       </c>
       <c r="C120" s="3">
         <f t="shared" si="122"/>
-        <v>73</v>
+        <v>61</v>
       </c>
       <c r="D120" s="3">
         <f t="shared" si="122"/>
-        <v>62</v>
+        <v>68</v>
       </c>
       <c r="E120" s="2">
         <f t="shared" si="4"/>
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="F120" s="2">
         <f t="shared" si="5"/>
-        <v>2020</v>
+        <v>2019</v>
       </c>
     </row>
     <row r="121">
@@ -3411,23 +3411,23 @@
       </c>
       <c r="B121" s="3">
         <f t="shared" ref="B121:D121" si="123">IF(RAND()&lt;0.2,"NA",RANDBETWEEN(60,80))</f>
-        <v>76</v>
+        <v>63</v>
       </c>
       <c r="C121" s="3">
         <f t="shared" si="123"/>
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="D121" s="3">
         <f t="shared" si="123"/>
-        <v>63</v>
+        <v>73</v>
       </c>
       <c r="E121" s="2">
         <f t="shared" si="4"/>
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="F121" s="2">
         <f t="shared" si="5"/>
-        <v>2021</v>
+        <v>2019</v>
       </c>
     </row>
     <row r="122">
@@ -3435,25 +3435,25 @@
         <f t="shared" si="2"/>
         <v>121</v>
       </c>
-      <c r="B122" s="3">
+      <c r="B122" s="3" t="str">
         <f t="shared" ref="B122:D122" si="124">IF(RAND()&lt;0.2,"NA",RANDBETWEEN(60,80))</f>
-        <v>71</v>
+        <v>NA</v>
       </c>
       <c r="C122" s="3">
         <f t="shared" si="124"/>
-        <v>78</v>
+        <v>62</v>
       </c>
       <c r="D122" s="3">
         <f t="shared" si="124"/>
-        <v>72</v>
+        <v>62</v>
       </c>
       <c r="E122" s="2">
         <f t="shared" si="4"/>
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="F122" s="2">
         <f t="shared" si="5"/>
-        <v>2021</v>
+        <v>2018</v>
       </c>
     </row>
     <row r="123">
@@ -3461,17 +3461,17 @@
         <f t="shared" si="2"/>
         <v>122</v>
       </c>
-      <c r="B123" s="3">
+      <c r="B123" s="3" t="str">
         <f t="shared" ref="B123:D123" si="125">IF(RAND()&lt;0.2,"NA",RANDBETWEEN(60,80))</f>
-        <v>74</v>
+        <v>NA</v>
       </c>
       <c r="C123" s="3">
         <f t="shared" si="125"/>
-        <v>76</v>
-      </c>
-      <c r="D123" s="3" t="str">
+        <v>73</v>
+      </c>
+      <c r="D123" s="3">
         <f t="shared" si="125"/>
-        <v>NA</v>
+        <v>71</v>
       </c>
       <c r="E123" s="2">
         <f t="shared" si="4"/>
@@ -3479,7 +3479,7 @@
       </c>
       <c r="F123" s="2">
         <f t="shared" si="5"/>
-        <v>2018</v>
+        <v>2021</v>
       </c>
     </row>
     <row r="124">
@@ -3487,25 +3487,25 @@
         <f t="shared" si="2"/>
         <v>123</v>
       </c>
-      <c r="B124" s="3" t="str">
+      <c r="B124" s="3">
         <f t="shared" ref="B124:D124" si="126">IF(RAND()&lt;0.2,"NA",RANDBETWEEN(60,80))</f>
-        <v>NA</v>
+        <v>65</v>
       </c>
       <c r="C124" s="3">
         <f t="shared" si="126"/>
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="D124" s="3">
         <f t="shared" si="126"/>
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="E124" s="2">
         <f t="shared" si="4"/>
-        <v>75</v>
+        <v>90</v>
       </c>
       <c r="F124" s="2">
         <f t="shared" si="5"/>
-        <v>2021</v>
+        <v>2019</v>
       </c>
     </row>
     <row r="125">
@@ -3513,21 +3513,21 @@
         <f t="shared" si="2"/>
         <v>124</v>
       </c>
-      <c r="B125" s="3" t="str">
+      <c r="B125" s="3">
         <f t="shared" ref="B125:D125" si="127">IF(RAND()&lt;0.2,"NA",RANDBETWEEN(60,80))</f>
-        <v>NA</v>
+        <v>61</v>
       </c>
       <c r="C125" s="3">
         <f t="shared" si="127"/>
-        <v>77</v>
-      </c>
-      <c r="D125" s="3">
+        <v>74</v>
+      </c>
+      <c r="D125" s="3" t="str">
         <f t="shared" si="127"/>
-        <v>60</v>
+        <v>NA</v>
       </c>
       <c r="E125" s="2">
         <f t="shared" si="4"/>
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="F125" s="2">
         <f t="shared" si="5"/>
@@ -3541,23 +3541,23 @@
       </c>
       <c r="B126" s="3">
         <f t="shared" ref="B126:D126" si="128">IF(RAND()&lt;0.2,"NA",RANDBETWEEN(60,80))</f>
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="C126" s="3">
         <f t="shared" si="128"/>
-        <v>79</v>
-      </c>
-      <c r="D126" s="3" t="str">
+        <v>72</v>
+      </c>
+      <c r="D126" s="3">
         <f t="shared" si="128"/>
-        <v>NA</v>
+        <v>77</v>
       </c>
       <c r="E126" s="2">
         <f t="shared" si="4"/>
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="F126" s="2">
         <f t="shared" si="5"/>
-        <v>2020</v>
+        <v>2019</v>
       </c>
     </row>
     <row r="127">
@@ -3565,25 +3565,25 @@
         <f t="shared" si="2"/>
         <v>126</v>
       </c>
-      <c r="B127" s="3" t="str">
+      <c r="B127" s="3">
         <f t="shared" ref="B127:D127" si="129">IF(RAND()&lt;0.2,"NA",RANDBETWEEN(60,80))</f>
-        <v>NA</v>
-      </c>
-      <c r="C127" s="3">
+        <v>78</v>
+      </c>
+      <c r="C127" s="3" t="str">
         <f t="shared" si="129"/>
-        <v>61</v>
+        <v>NA</v>
       </c>
       <c r="D127" s="3">
         <f t="shared" si="129"/>
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="E127" s="2">
         <f t="shared" si="4"/>
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="F127" s="2">
         <f t="shared" si="5"/>
-        <v>2021</v>
+        <v>2019</v>
       </c>
     </row>
     <row r="128">
@@ -3591,25 +3591,25 @@
         <f t="shared" si="2"/>
         <v>127</v>
       </c>
-      <c r="B128" s="3">
+      <c r="B128" s="3" t="str">
         <f t="shared" ref="B128:D128" si="130">IF(RAND()&lt;0.2,"NA",RANDBETWEEN(60,80))</f>
-        <v>77</v>
-      </c>
-      <c r="C128" s="3" t="str">
+        <v>NA</v>
+      </c>
+      <c r="C128" s="3">
         <f t="shared" si="130"/>
-        <v>NA</v>
-      </c>
-      <c r="D128" s="3">
+        <v>71</v>
+      </c>
+      <c r="D128" s="3" t="str">
         <f t="shared" si="130"/>
-        <v>61</v>
+        <v>NA</v>
       </c>
       <c r="E128" s="2">
         <f t="shared" si="4"/>
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="F128" s="2">
         <f t="shared" si="5"/>
-        <v>2018</v>
+        <v>2019</v>
       </c>
     </row>
     <row r="129">
@@ -3617,25 +3617,25 @@
         <f t="shared" si="2"/>
         <v>128</v>
       </c>
-      <c r="B129" s="3">
+      <c r="B129" s="3" t="str">
         <f t="shared" ref="B129:D129" si="131">IF(RAND()&lt;0.2,"NA",RANDBETWEEN(60,80))</f>
-        <v>73</v>
-      </c>
-      <c r="C129" s="3">
+        <v>NA</v>
+      </c>
+      <c r="C129" s="3" t="str">
         <f t="shared" si="131"/>
-        <v>74</v>
+        <v>NA</v>
       </c>
       <c r="D129" s="3">
         <f t="shared" si="131"/>
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="E129" s="2">
         <f t="shared" si="4"/>
-        <v>90</v>
+        <v>82</v>
       </c>
       <c r="F129" s="2">
         <f t="shared" si="5"/>
-        <v>2021</v>
+        <v>2019</v>
       </c>
     </row>
     <row r="130">
@@ -3645,23 +3645,23 @@
       </c>
       <c r="B130" s="3">
         <f t="shared" ref="B130:D130" si="132">IF(RAND()&lt;0.2,"NA",RANDBETWEEN(60,80))</f>
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="C130" s="3">
         <f t="shared" si="132"/>
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="D130" s="3">
         <f t="shared" si="132"/>
-        <v>67</v>
+        <v>79</v>
       </c>
       <c r="E130" s="2">
         <f t="shared" si="4"/>
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="F130" s="2">
         <f t="shared" si="5"/>
-        <v>2020</v>
+        <v>2019</v>
       </c>
     </row>
     <row r="131">
@@ -3671,23 +3671,23 @@
       </c>
       <c r="B131" s="3">
         <f t="shared" ref="B131:D131" si="133">IF(RAND()&lt;0.2,"NA",RANDBETWEEN(60,80))</f>
-        <v>77</v>
+        <v>60</v>
       </c>
       <c r="C131" s="3">
         <f t="shared" si="133"/>
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="D131" s="3">
         <f t="shared" si="133"/>
-        <v>68</v>
+        <v>76</v>
       </c>
       <c r="E131" s="2">
         <f t="shared" si="4"/>
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="F131" s="2">
         <f t="shared" si="5"/>
-        <v>2020</v>
+        <v>2021</v>
       </c>
     </row>
     <row r="132">
@@ -3697,23 +3697,23 @@
       </c>
       <c r="B132" s="3">
         <f t="shared" ref="B132:D132" si="134">IF(RAND()&lt;0.2,"NA",RANDBETWEEN(60,80))</f>
-        <v>72</v>
-      </c>
-      <c r="C132" s="3">
+        <v>77</v>
+      </c>
+      <c r="C132" s="3" t="str">
         <f t="shared" si="134"/>
-        <v>79</v>
+        <v>NA</v>
       </c>
       <c r="D132" s="3">
         <f t="shared" si="134"/>
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="E132" s="2">
         <f t="shared" si="4"/>
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="F132" s="2">
         <f t="shared" si="5"/>
-        <v>2021</v>
+        <v>2018</v>
       </c>
     </row>
     <row r="133">
@@ -3723,23 +3723,23 @@
       </c>
       <c r="B133" s="3">
         <f t="shared" ref="B133:D133" si="135">IF(RAND()&lt;0.2,"NA",RANDBETWEEN(60,80))</f>
-        <v>75</v>
-      </c>
-      <c r="C133" s="3" t="str">
+        <v>70</v>
+      </c>
+      <c r="C133" s="3">
         <f t="shared" si="135"/>
-        <v>NA</v>
-      </c>
-      <c r="D133" s="3">
+        <v>71</v>
+      </c>
+      <c r="D133" s="3" t="str">
         <f t="shared" si="135"/>
-        <v>78</v>
+        <v>NA</v>
       </c>
       <c r="E133" s="2">
         <f t="shared" si="4"/>
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="F133" s="2">
         <f t="shared" si="5"/>
-        <v>2021</v>
+        <v>2019</v>
       </c>
     </row>
     <row r="134">
@@ -3747,25 +3747,25 @@
         <f t="shared" si="2"/>
         <v>133</v>
       </c>
-      <c r="B134" s="3" t="str">
+      <c r="B134" s="3">
         <f t="shared" ref="B134:D134" si="136">IF(RAND()&lt;0.2,"NA",RANDBETWEEN(60,80))</f>
-        <v>NA</v>
+        <v>78</v>
       </c>
       <c r="C134" s="3">
         <f t="shared" si="136"/>
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="D134" s="3">
         <f t="shared" si="136"/>
-        <v>62</v>
+        <v>75</v>
       </c>
       <c r="E134" s="2">
         <f t="shared" si="4"/>
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="F134" s="2">
         <f t="shared" si="5"/>
-        <v>2018</v>
+        <v>2020</v>
       </c>
     </row>
     <row r="135">
@@ -3775,23 +3775,23 @@
       </c>
       <c r="B135" s="3">
         <f t="shared" ref="B135:D135" si="137">IF(RAND()&lt;0.2,"NA",RANDBETWEEN(60,80))</f>
-        <v>64</v>
+        <v>78</v>
       </c>
       <c r="C135" s="3">
         <f t="shared" si="137"/>
-        <v>75</v>
-      </c>
-      <c r="D135" s="3" t="str">
+        <v>74</v>
+      </c>
+      <c r="D135" s="3">
         <f t="shared" si="137"/>
-        <v>NA</v>
+        <v>62</v>
       </c>
       <c r="E135" s="2">
         <f t="shared" si="4"/>
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="F135" s="2">
         <f t="shared" si="5"/>
-        <v>2021</v>
+        <v>2018</v>
       </c>
     </row>
     <row r="136">
@@ -3801,23 +3801,23 @@
       </c>
       <c r="B136" s="3">
         <f t="shared" ref="B136:D136" si="138">IF(RAND()&lt;0.2,"NA",RANDBETWEEN(60,80))</f>
-        <v>63</v>
+        <v>71</v>
       </c>
       <c r="C136" s="3">
         <f t="shared" si="138"/>
-        <v>78</v>
-      </c>
-      <c r="D136" s="3">
+        <v>77</v>
+      </c>
+      <c r="D136" s="3" t="str">
         <f t="shared" si="138"/>
-        <v>74</v>
+        <v>NA</v>
       </c>
       <c r="E136" s="2">
         <f t="shared" si="4"/>
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="F136" s="2">
         <f t="shared" si="5"/>
-        <v>2020</v>
+        <v>2018</v>
       </c>
     </row>
     <row r="137">
@@ -3825,25 +3825,25 @@
         <f t="shared" si="2"/>
         <v>136</v>
       </c>
-      <c r="B137" s="3" t="str">
+      <c r="B137" s="3">
         <f t="shared" ref="B137:D137" si="139">IF(RAND()&lt;0.2,"NA",RANDBETWEEN(60,80))</f>
-        <v>NA</v>
+        <v>66</v>
       </c>
       <c r="C137" s="3">
         <f t="shared" si="139"/>
-        <v>70</v>
+        <v>78</v>
       </c>
       <c r="D137" s="3">
         <f t="shared" si="139"/>
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="E137" s="2">
         <f t="shared" si="4"/>
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="F137" s="2">
         <f t="shared" si="5"/>
-        <v>2019</v>
+        <v>2020</v>
       </c>
     </row>
     <row r="138">
@@ -3853,23 +3853,23 @@
       </c>
       <c r="B138" s="3">
         <f t="shared" ref="B138:D138" si="140">IF(RAND()&lt;0.2,"NA",RANDBETWEEN(60,80))</f>
-        <v>73</v>
-      </c>
-      <c r="C138" s="3">
+        <v>70</v>
+      </c>
+      <c r="C138" s="3" t="str">
         <f t="shared" si="140"/>
-        <v>80</v>
+        <v>NA</v>
       </c>
       <c r="D138" s="3">
         <f t="shared" si="140"/>
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="E138" s="2">
         <f t="shared" si="4"/>
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="F138" s="2">
         <f t="shared" si="5"/>
-        <v>2020</v>
+        <v>2021</v>
       </c>
     </row>
     <row r="139">
@@ -3877,21 +3877,21 @@
         <f t="shared" si="2"/>
         <v>138</v>
       </c>
-      <c r="B139" s="3">
+      <c r="B139" s="3" t="str">
         <f t="shared" ref="B139:D139" si="141">IF(RAND()&lt;0.2,"NA",RANDBETWEEN(60,80))</f>
-        <v>77</v>
-      </c>
-      <c r="C139" s="3" t="str">
+        <v>NA</v>
+      </c>
+      <c r="C139" s="3">
         <f t="shared" si="141"/>
-        <v>NA</v>
+        <v>70</v>
       </c>
       <c r="D139" s="3">
         <f t="shared" si="141"/>
-        <v>74</v>
+        <v>69</v>
       </c>
       <c r="E139" s="2">
         <f t="shared" si="4"/>
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="F139" s="2">
         <f t="shared" si="5"/>

--- a/DSBDAL/Assignment2/CreatedData.xlsx
+++ b/DSBDAL/Assignment2/CreatedData.xlsx
@@ -315,21 +315,21 @@
         <f t="shared" ref="A2:A139" si="2">ROW()-ROW($A$1)</f>
         <v>1</v>
       </c>
-      <c r="B2" s="3" t="str">
+      <c r="B2" s="3">
         <f t="shared" ref="B2:D2" si="1">IF(RAND()&lt;0.2,"NA",RANDBETWEEN(60,80))</f>
-        <v>NA</v>
-      </c>
-      <c r="C2" s="3" t="str">
+        <v>67</v>
+      </c>
+      <c r="C2" s="3">
         <f t="shared" si="1"/>
-        <v>NA</v>
+        <v>61</v>
       </c>
       <c r="D2" s="3">
         <f t="shared" si="1"/>
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="E2" s="2">
         <f t="shared" ref="E2:E139" si="4">IF(RAND()&lt;0.05,CHOOSE(RANDBETWEEN(1,2),500,5),RANDBETWEEN(75,90))</f>
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="F2" s="2">
         <f t="shared" ref="F2:F139" si="5">RANDBETWEEN(2018,2021)</f>
@@ -343,11 +343,11 @@
       </c>
       <c r="B3" s="3">
         <f t="shared" ref="B3:D3" si="3">IF(RAND()&lt;0.2,"NA",RANDBETWEEN(60,80))</f>
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="C3" s="3">
         <f t="shared" si="3"/>
-        <v>63</v>
+        <v>73</v>
       </c>
       <c r="D3" s="3" t="str">
         <f t="shared" si="3"/>
@@ -355,11 +355,11 @@
       </c>
       <c r="E3" s="2">
         <f t="shared" si="4"/>
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="F3" s="2">
         <f t="shared" si="5"/>
-        <v>2019</v>
+        <v>2021</v>
       </c>
     </row>
     <row r="4">
@@ -369,23 +369,23 @@
       </c>
       <c r="B4" s="3">
         <f t="shared" ref="B4:D4" si="6">IF(RAND()&lt;0.2,"NA",RANDBETWEEN(60,80))</f>
-        <v>61</v>
-      </c>
-      <c r="C4" s="3">
+        <v>71</v>
+      </c>
+      <c r="C4" s="3" t="str">
         <f t="shared" si="6"/>
-        <v>60</v>
+        <v>NA</v>
       </c>
       <c r="D4" s="3">
         <f t="shared" si="6"/>
-        <v>74</v>
+        <v>65</v>
       </c>
       <c r="E4" s="2">
         <f t="shared" si="4"/>
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="F4" s="2">
         <f t="shared" si="5"/>
-        <v>2018</v>
+        <v>2020</v>
       </c>
     </row>
     <row r="5">
@@ -393,25 +393,25 @@
         <f t="shared" si="2"/>
         <v>4</v>
       </c>
-      <c r="B5" s="3" t="str">
+      <c r="B5" s="3">
         <f t="shared" ref="B5:D5" si="7">IF(RAND()&lt;0.2,"NA",RANDBETWEEN(60,80))</f>
-        <v>NA</v>
+        <v>79</v>
       </c>
       <c r="C5" s="3">
         <f t="shared" si="7"/>
-        <v>67</v>
+        <v>78</v>
       </c>
       <c r="D5" s="3">
         <f t="shared" si="7"/>
-        <v>78</v>
+        <v>64</v>
       </c>
       <c r="E5" s="2">
         <f t="shared" si="4"/>
-        <v>76</v>
+        <v>90</v>
       </c>
       <c r="F5" s="2">
         <f t="shared" si="5"/>
-        <v>2021</v>
+        <v>2019</v>
       </c>
     </row>
     <row r="6">
@@ -421,19 +421,19 @@
       </c>
       <c r="B6" s="3">
         <f t="shared" ref="B6:D6" si="8">IF(RAND()&lt;0.2,"NA",RANDBETWEEN(60,80))</f>
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="C6" s="3">
         <f t="shared" si="8"/>
-        <v>72</v>
-      </c>
-      <c r="D6" s="3">
+        <v>64</v>
+      </c>
+      <c r="D6" s="3" t="str">
         <f t="shared" si="8"/>
-        <v>78</v>
+        <v>NA</v>
       </c>
       <c r="E6" s="2">
         <f t="shared" si="4"/>
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="F6" s="2">
         <f t="shared" si="5"/>
@@ -447,23 +447,23 @@
       </c>
       <c r="B7" s="3">
         <f t="shared" ref="B7:D7" si="9">IF(RAND()&lt;0.2,"NA",RANDBETWEEN(60,80))</f>
-        <v>76</v>
+        <v>64</v>
       </c>
       <c r="C7" s="3">
         <f t="shared" si="9"/>
-        <v>71</v>
+        <v>62</v>
       </c>
       <c r="D7" s="3">
         <f t="shared" si="9"/>
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="E7" s="2">
         <f t="shared" si="4"/>
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="F7" s="2">
         <f t="shared" si="5"/>
-        <v>2019</v>
+        <v>2018</v>
       </c>
     </row>
     <row r="8">
@@ -473,19 +473,19 @@
       </c>
       <c r="B8" s="3">
         <f t="shared" ref="B8:D8" si="10">IF(RAND()&lt;0.2,"NA",RANDBETWEEN(60,80))</f>
-        <v>64</v>
+        <v>78</v>
       </c>
       <c r="C8" s="3">
         <f t="shared" si="10"/>
-        <v>71</v>
+        <v>60</v>
       </c>
       <c r="D8" s="3">
         <f t="shared" si="10"/>
-        <v>61</v>
+        <v>66</v>
       </c>
       <c r="E8" s="2">
         <f t="shared" si="4"/>
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="F8" s="2">
         <f t="shared" si="5"/>
@@ -501,21 +501,21 @@
         <f t="shared" ref="B9:D9" si="11">IF(RAND()&lt;0.2,"NA",RANDBETWEEN(60,80))</f>
         <v>NA</v>
       </c>
-      <c r="C9" s="3" t="str">
+      <c r="C9" s="3">
         <f t="shared" si="11"/>
-        <v>NA</v>
+        <v>67</v>
       </c>
       <c r="D9" s="3">
         <f t="shared" si="11"/>
-        <v>78</v>
+        <v>62</v>
       </c>
       <c r="E9" s="2">
         <f t="shared" si="4"/>
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="F9" s="2">
         <f t="shared" si="5"/>
-        <v>2019</v>
+        <v>2018</v>
       </c>
     </row>
     <row r="10">
@@ -525,23 +525,23 @@
       </c>
       <c r="B10" s="3">
         <f t="shared" ref="B10:D10" si="12">IF(RAND()&lt;0.2,"NA",RANDBETWEEN(60,80))</f>
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="C10" s="3">
         <f t="shared" si="12"/>
-        <v>78</v>
-      </c>
-      <c r="D10" s="3">
+        <v>75</v>
+      </c>
+      <c r="D10" s="3" t="str">
         <f t="shared" si="12"/>
-        <v>77</v>
+        <v>NA</v>
       </c>
       <c r="E10" s="2">
         <f t="shared" si="4"/>
-        <v>75</v>
+        <v>84</v>
       </c>
       <c r="F10" s="2">
         <f t="shared" si="5"/>
-        <v>2021</v>
+        <v>2018</v>
       </c>
     </row>
     <row r="11">
@@ -549,21 +549,21 @@
         <f t="shared" si="2"/>
         <v>10</v>
       </c>
-      <c r="B11" s="3">
+      <c r="B11" s="3" t="str">
         <f t="shared" ref="B11:D11" si="13">IF(RAND()&lt;0.2,"NA",RANDBETWEEN(60,80))</f>
-        <v>71</v>
+        <v>NA</v>
       </c>
       <c r="C11" s="3">
         <f t="shared" si="13"/>
-        <v>66</v>
-      </c>
-      <c r="D11" s="3">
+        <v>62</v>
+      </c>
+      <c r="D11" s="3" t="str">
         <f t="shared" si="13"/>
-        <v>67</v>
+        <v>NA</v>
       </c>
       <c r="E11" s="2">
         <f t="shared" si="4"/>
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="F11" s="2">
         <f t="shared" si="5"/>
@@ -577,23 +577,23 @@
       </c>
       <c r="B12" s="3">
         <f t="shared" ref="B12:D12" si="14">IF(RAND()&lt;0.2,"NA",RANDBETWEEN(60,80))</f>
-        <v>80</v>
+        <v>62</v>
       </c>
       <c r="C12" s="3">
         <f t="shared" si="14"/>
-        <v>79</v>
-      </c>
-      <c r="D12" s="3">
+        <v>63</v>
+      </c>
+      <c r="D12" s="3" t="str">
         <f t="shared" si="14"/>
-        <v>61</v>
+        <v>NA</v>
       </c>
       <c r="E12" s="2">
         <f t="shared" si="4"/>
-        <v>88</v>
+        <v>76</v>
       </c>
       <c r="F12" s="2">
         <f t="shared" si="5"/>
-        <v>2019</v>
+        <v>2021</v>
       </c>
     </row>
     <row r="13">
@@ -603,23 +603,23 @@
       </c>
       <c r="B13" s="3">
         <f t="shared" ref="B13:D13" si="15">IF(RAND()&lt;0.2,"NA",RANDBETWEEN(60,80))</f>
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="C13" s="3">
         <f t="shared" si="15"/>
-        <v>80</v>
+        <v>68</v>
       </c>
       <c r="D13" s="3">
         <f t="shared" si="15"/>
-        <v>62</v>
+        <v>79</v>
       </c>
       <c r="E13" s="2">
         <f t="shared" si="4"/>
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="F13" s="2">
         <f t="shared" si="5"/>
-        <v>2021</v>
+        <v>2020</v>
       </c>
     </row>
     <row r="14">
@@ -629,19 +629,19 @@
       </c>
       <c r="B14" s="3">
         <f t="shared" ref="B14:D14" si="16">IF(RAND()&lt;0.2,"NA",RANDBETWEEN(60,80))</f>
-        <v>63</v>
+        <v>70</v>
       </c>
       <c r="C14" s="3">
         <f t="shared" si="16"/>
-        <v>78</v>
+        <v>60</v>
       </c>
       <c r="D14" s="3">
         <f t="shared" si="16"/>
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="E14" s="2">
         <f t="shared" si="4"/>
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="F14" s="2">
         <f t="shared" si="5"/>
@@ -655,23 +655,23 @@
       </c>
       <c r="B15" s="3">
         <f t="shared" ref="B15:D15" si="17">IF(RAND()&lt;0.2,"NA",RANDBETWEEN(60,80))</f>
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C15" s="3">
         <f t="shared" si="17"/>
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="D15" s="3">
         <f t="shared" si="17"/>
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="E15" s="2">
         <f t="shared" si="4"/>
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="F15" s="2">
         <f t="shared" si="5"/>
-        <v>2018</v>
+        <v>2020</v>
       </c>
     </row>
     <row r="16">
@@ -679,21 +679,21 @@
         <f t="shared" si="2"/>
         <v>15</v>
       </c>
-      <c r="B16" s="3" t="str">
+      <c r="B16" s="3">
         <f t="shared" ref="B16:D16" si="18">IF(RAND()&lt;0.2,"NA",RANDBETWEEN(60,80))</f>
-        <v>NA</v>
+        <v>62</v>
       </c>
       <c r="C16" s="3">
         <f t="shared" si="18"/>
-        <v>72</v>
-      </c>
-      <c r="D16" s="3" t="str">
+        <v>73</v>
+      </c>
+      <c r="D16" s="3">
         <f t="shared" si="18"/>
-        <v>NA</v>
+        <v>76</v>
       </c>
       <c r="E16" s="2">
         <f t="shared" si="4"/>
-        <v>87</v>
+        <v>75</v>
       </c>
       <c r="F16" s="2">
         <f t="shared" si="5"/>
@@ -705,25 +705,25 @@
         <f t="shared" si="2"/>
         <v>16</v>
       </c>
-      <c r="B17" s="3" t="str">
+      <c r="B17" s="3">
         <f t="shared" ref="B17:D17" si="19">IF(RAND()&lt;0.2,"NA",RANDBETWEEN(60,80))</f>
-        <v>NA</v>
-      </c>
-      <c r="C17" s="3">
+        <v>75</v>
+      </c>
+      <c r="C17" s="3" t="str">
         <f t="shared" si="19"/>
-        <v>62</v>
-      </c>
-      <c r="D17" s="3" t="str">
+        <v>NA</v>
+      </c>
+      <c r="D17" s="3">
         <f t="shared" si="19"/>
-        <v>NA</v>
+        <v>60</v>
       </c>
       <c r="E17" s="2">
         <f t="shared" si="4"/>
-        <v>87</v>
+        <v>76</v>
       </c>
       <c r="F17" s="2">
         <f t="shared" si="5"/>
-        <v>2019</v>
+        <v>2020</v>
       </c>
     </row>
     <row r="18">
@@ -733,19 +733,19 @@
       </c>
       <c r="B18" s="3">
         <f t="shared" ref="B18:D18" si="20">IF(RAND()&lt;0.2,"NA",RANDBETWEEN(60,80))</f>
-        <v>75</v>
-      </c>
-      <c r="C18" s="3">
+        <v>63</v>
+      </c>
+      <c r="C18" s="3" t="str">
         <f t="shared" si="20"/>
-        <v>75</v>
+        <v>NA</v>
       </c>
       <c r="D18" s="3">
         <f t="shared" si="20"/>
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="E18" s="2">
         <f t="shared" si="4"/>
-        <v>5</v>
+        <v>90</v>
       </c>
       <c r="F18" s="2">
         <f t="shared" si="5"/>
@@ -759,23 +759,23 @@
       </c>
       <c r="B19" s="3">
         <f t="shared" ref="B19:D19" si="21">IF(RAND()&lt;0.2,"NA",RANDBETWEEN(60,80))</f>
+        <v>76</v>
+      </c>
+      <c r="C19" s="3" t="str">
+        <f t="shared" si="21"/>
+        <v>NA</v>
+      </c>
+      <c r="D19" s="3">
+        <f t="shared" si="21"/>
         <v>80</v>
       </c>
-      <c r="C19" s="3">
-        <f t="shared" si="21"/>
-        <v>70</v>
-      </c>
-      <c r="D19" s="3" t="str">
-        <f t="shared" si="21"/>
-        <v>NA</v>
-      </c>
       <c r="E19" s="2">
         <f t="shared" si="4"/>
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="F19" s="2">
         <f t="shared" si="5"/>
-        <v>2019</v>
+        <v>2018</v>
       </c>
     </row>
     <row r="20">
@@ -785,23 +785,23 @@
       </c>
       <c r="B20" s="3">
         <f t="shared" ref="B20:D20" si="22">IF(RAND()&lt;0.2,"NA",RANDBETWEEN(60,80))</f>
-        <v>75</v>
-      </c>
-      <c r="C20" s="3" t="str">
+        <v>69</v>
+      </c>
+      <c r="C20" s="3">
         <f t="shared" si="22"/>
-        <v>NA</v>
+        <v>77</v>
       </c>
       <c r="D20" s="3">
         <f t="shared" si="22"/>
-        <v>71</v>
+        <v>62</v>
       </c>
       <c r="E20" s="2">
         <f t="shared" si="4"/>
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="F20" s="2">
         <f t="shared" si="5"/>
-        <v>2021</v>
+        <v>2019</v>
       </c>
     </row>
     <row r="21">
@@ -827,7 +827,7 @@
       </c>
       <c r="F21" s="2">
         <f t="shared" si="5"/>
-        <v>2018</v>
+        <v>2021</v>
       </c>
     </row>
     <row r="22">
@@ -837,23 +837,23 @@
       </c>
       <c r="B22" s="3">
         <f t="shared" ref="B22:D22" si="24">IF(RAND()&lt;0.2,"NA",RANDBETWEEN(60,80))</f>
-        <v>62</v>
-      </c>
-      <c r="C22" s="3" t="str">
+        <v>72</v>
+      </c>
+      <c r="C22" s="3">
         <f t="shared" si="24"/>
-        <v>NA</v>
+        <v>67</v>
       </c>
       <c r="D22" s="3">
         <f t="shared" si="24"/>
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="E22" s="2">
         <f t="shared" si="4"/>
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="F22" s="2">
         <f t="shared" si="5"/>
-        <v>2018</v>
+        <v>2021</v>
       </c>
     </row>
     <row r="23">
@@ -861,13 +861,13 @@
         <f t="shared" si="2"/>
         <v>22</v>
       </c>
-      <c r="B23" s="3" t="str">
+      <c r="B23" s="3">
         <f t="shared" ref="B23:D23" si="25">IF(RAND()&lt;0.2,"NA",RANDBETWEEN(60,80))</f>
-        <v>NA</v>
+        <v>72</v>
       </c>
       <c r="C23" s="3">
         <f t="shared" si="25"/>
-        <v>67</v>
+        <v>80</v>
       </c>
       <c r="D23" s="3" t="str">
         <f t="shared" si="25"/>
@@ -875,11 +875,11 @@
       </c>
       <c r="E23" s="2">
         <f t="shared" si="4"/>
-        <v>77</v>
+        <v>90</v>
       </c>
       <c r="F23" s="2">
         <f t="shared" si="5"/>
-        <v>2021</v>
+        <v>2020</v>
       </c>
     </row>
     <row r="24">
@@ -887,25 +887,25 @@
         <f t="shared" si="2"/>
         <v>23</v>
       </c>
-      <c r="B24" s="3" t="str">
+      <c r="B24" s="3">
         <f t="shared" ref="B24:D24" si="26">IF(RAND()&lt;0.2,"NA",RANDBETWEEN(60,80))</f>
-        <v>NA</v>
+        <v>63</v>
       </c>
       <c r="C24" s="3">
         <f t="shared" si="26"/>
-        <v>63</v>
-      </c>
-      <c r="D24" s="3">
+        <v>67</v>
+      </c>
+      <c r="D24" s="3" t="str">
         <f t="shared" si="26"/>
-        <v>66</v>
+        <v>NA</v>
       </c>
       <c r="E24" s="2">
         <f t="shared" si="4"/>
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="F24" s="2">
         <f t="shared" si="5"/>
-        <v>2019</v>
+        <v>2021</v>
       </c>
     </row>
     <row r="25">
@@ -915,23 +915,23 @@
       </c>
       <c r="B25" s="3">
         <f t="shared" ref="B25:D25" si="27">IF(RAND()&lt;0.2,"NA",RANDBETWEEN(60,80))</f>
-        <v>76</v>
-      </c>
-      <c r="C25" s="3" t="str">
+        <v>73</v>
+      </c>
+      <c r="C25" s="3">
         <f t="shared" si="27"/>
-        <v>NA</v>
+        <v>71</v>
       </c>
       <c r="D25" s="3">
         <f t="shared" si="27"/>
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="E25" s="2">
         <f t="shared" si="4"/>
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="F25" s="2">
         <f t="shared" si="5"/>
-        <v>2020</v>
+        <v>2018</v>
       </c>
     </row>
     <row r="26">
@@ -939,13 +939,13 @@
         <f t="shared" si="2"/>
         <v>25</v>
       </c>
-      <c r="B26" s="3">
+      <c r="B26" s="3" t="str">
         <f t="shared" ref="B26:D26" si="28">IF(RAND()&lt;0.2,"NA",RANDBETWEEN(60,80))</f>
-        <v>66</v>
-      </c>
-      <c r="C26" s="3" t="str">
+        <v>NA</v>
+      </c>
+      <c r="C26" s="3">
         <f t="shared" si="28"/>
-        <v>NA</v>
+        <v>69</v>
       </c>
       <c r="D26" s="3" t="str">
         <f t="shared" si="28"/>
@@ -953,11 +953,11 @@
       </c>
       <c r="E26" s="2">
         <f t="shared" si="4"/>
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="F26" s="2">
         <f t="shared" si="5"/>
-        <v>2019</v>
+        <v>2018</v>
       </c>
     </row>
     <row r="27">
@@ -967,19 +967,19 @@
       </c>
       <c r="B27" s="3">
         <f t="shared" ref="B27:D27" si="29">IF(RAND()&lt;0.2,"NA",RANDBETWEEN(60,80))</f>
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="C27" s="3">
         <f t="shared" si="29"/>
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="D27" s="3">
         <f t="shared" si="29"/>
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E27" s="2">
         <f t="shared" si="4"/>
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="F27" s="2">
         <f t="shared" si="5"/>
@@ -995,21 +995,21 @@
         <f t="shared" ref="B28:D28" si="30">IF(RAND()&lt;0.2,"NA",RANDBETWEEN(60,80))</f>
         <v>NA</v>
       </c>
-      <c r="C28" s="3">
+      <c r="C28" s="3" t="str">
         <f t="shared" si="30"/>
+        <v>NA</v>
+      </c>
+      <c r="D28" s="3">
+        <f t="shared" si="30"/>
+        <v>66</v>
+      </c>
+      <c r="E28" s="2">
+        <f t="shared" si="4"/>
         <v>75</v>
       </c>
-      <c r="D28" s="3" t="str">
-        <f t="shared" si="30"/>
-        <v>NA</v>
-      </c>
-      <c r="E28" s="2">
-        <f t="shared" si="4"/>
-        <v>79</v>
-      </c>
       <c r="F28" s="2">
         <f t="shared" si="5"/>
-        <v>2018</v>
+        <v>2019</v>
       </c>
     </row>
     <row r="29">
@@ -1023,15 +1023,15 @@
       </c>
       <c r="C29" s="3">
         <f t="shared" si="31"/>
-        <v>71</v>
-      </c>
-      <c r="D29" s="3">
+        <v>68</v>
+      </c>
+      <c r="D29" s="3" t="str">
         <f t="shared" si="31"/>
-        <v>79</v>
+        <v>NA</v>
       </c>
       <c r="E29" s="2">
         <f t="shared" si="4"/>
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="F29" s="2">
         <f t="shared" si="5"/>
@@ -1045,23 +1045,23 @@
       </c>
       <c r="B30" s="3">
         <f t="shared" ref="B30:D30" si="32">IF(RAND()&lt;0.2,"NA",RANDBETWEEN(60,80))</f>
-        <v>66</v>
+        <v>75</v>
       </c>
       <c r="C30" s="3">
         <f t="shared" si="32"/>
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="D30" s="3">
         <f t="shared" si="32"/>
-        <v>76</v>
+        <v>63</v>
       </c>
       <c r="E30" s="2">
         <f t="shared" si="4"/>
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="F30" s="2">
         <f t="shared" si="5"/>
-        <v>2018</v>
+        <v>2020</v>
       </c>
     </row>
     <row r="31">
@@ -1073,21 +1073,21 @@
         <f t="shared" ref="B31:D31" si="33">IF(RAND()&lt;0.2,"NA",RANDBETWEEN(60,80))</f>
         <v>NA</v>
       </c>
-      <c r="C31" s="3">
+      <c r="C31" s="3" t="str">
+        <f t="shared" si="33"/>
+        <v>NA</v>
+      </c>
+      <c r="D31" s="3">
         <f t="shared" si="33"/>
         <v>74</v>
       </c>
-      <c r="D31" s="3">
-        <f t="shared" si="33"/>
-        <v>80</v>
-      </c>
       <c r="E31" s="2">
         <f t="shared" si="4"/>
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="F31" s="2">
         <f t="shared" si="5"/>
-        <v>2019</v>
+        <v>2021</v>
       </c>
     </row>
     <row r="32">
@@ -1099,21 +1099,21 @@
         <f t="shared" ref="B32:D32" si="34">IF(RAND()&lt;0.2,"NA",RANDBETWEEN(60,80))</f>
         <v>NA</v>
       </c>
-      <c r="C32" s="3" t="str">
+      <c r="C32" s="3">
         <f t="shared" si="34"/>
-        <v>NA</v>
+        <v>72</v>
       </c>
       <c r="D32" s="3">
         <f t="shared" si="34"/>
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E32" s="2">
         <f t="shared" si="4"/>
-        <v>500</v>
+        <v>76</v>
       </c>
       <c r="F32" s="2">
         <f t="shared" si="5"/>
-        <v>2019</v>
+        <v>2021</v>
       </c>
     </row>
     <row r="33">
@@ -1127,15 +1127,15 @@
       </c>
       <c r="C33" s="3">
         <f t="shared" si="35"/>
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="D33" s="3">
         <f t="shared" si="35"/>
-        <v>69</v>
+        <v>77</v>
       </c>
       <c r="E33" s="2">
         <f t="shared" si="4"/>
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="F33" s="2">
         <f t="shared" si="5"/>
@@ -1149,23 +1149,23 @@
       </c>
       <c r="B34" s="3">
         <f t="shared" ref="B34:D34" si="36">IF(RAND()&lt;0.2,"NA",RANDBETWEEN(60,80))</f>
-        <v>62</v>
-      </c>
-      <c r="C34" s="3">
+        <v>61</v>
+      </c>
+      <c r="C34" s="3" t="str">
         <f t="shared" si="36"/>
-        <v>70</v>
+        <v>NA</v>
       </c>
       <c r="D34" s="3">
         <f t="shared" si="36"/>
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="E34" s="2">
         <f t="shared" si="4"/>
-        <v>86</v>
+        <v>5</v>
       </c>
       <c r="F34" s="2">
         <f t="shared" si="5"/>
-        <v>2019</v>
+        <v>2021</v>
       </c>
     </row>
     <row r="35">
@@ -1173,25 +1173,25 @@
         <f t="shared" si="2"/>
         <v>34</v>
       </c>
-      <c r="B35" s="3">
+      <c r="B35" s="3" t="str">
         <f t="shared" ref="B35:D35" si="37">IF(RAND()&lt;0.2,"NA",RANDBETWEEN(60,80))</f>
-        <v>74</v>
+        <v>NA</v>
       </c>
       <c r="C35" s="3">
         <f t="shared" si="37"/>
-        <v>64</v>
+        <v>80</v>
       </c>
       <c r="D35" s="3">
         <f t="shared" si="37"/>
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="E35" s="2">
         <f t="shared" si="4"/>
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="F35" s="2">
         <f t="shared" si="5"/>
-        <v>2019</v>
+        <v>2021</v>
       </c>
     </row>
     <row r="36">
@@ -1201,7 +1201,7 @@
       </c>
       <c r="B36" s="3">
         <f t="shared" ref="B36:D36" si="38">IF(RAND()&lt;0.2,"NA",RANDBETWEEN(60,80))</f>
-        <v>76</v>
+        <v>61</v>
       </c>
       <c r="C36" s="3">
         <f t="shared" si="38"/>
@@ -1209,15 +1209,15 @@
       </c>
       <c r="D36" s="3">
         <f t="shared" si="38"/>
-        <v>67</v>
+        <v>80</v>
       </c>
       <c r="E36" s="2">
         <f t="shared" si="4"/>
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="F36" s="2">
         <f t="shared" si="5"/>
-        <v>2018</v>
+        <v>2021</v>
       </c>
     </row>
     <row r="37">
@@ -1227,23 +1227,23 @@
       </c>
       <c r="B37" s="3">
         <f t="shared" ref="B37:D37" si="39">IF(RAND()&lt;0.2,"NA",RANDBETWEEN(60,80))</f>
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="C37" s="3">
         <f t="shared" si="39"/>
-        <v>69</v>
+        <v>79</v>
       </c>
       <c r="D37" s="3">
         <f t="shared" si="39"/>
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="E37" s="2">
         <f t="shared" si="4"/>
-        <v>80</v>
+        <v>87</v>
       </c>
       <c r="F37" s="2">
         <f t="shared" si="5"/>
-        <v>2019</v>
+        <v>2018</v>
       </c>
     </row>
     <row r="38">
@@ -1253,23 +1253,23 @@
       </c>
       <c r="B38" s="3">
         <f t="shared" ref="B38:D38" si="40">IF(RAND()&lt;0.2,"NA",RANDBETWEEN(60,80))</f>
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C38" s="3">
         <f t="shared" si="40"/>
-        <v>63</v>
-      </c>
-      <c r="D38" s="3" t="str">
+        <v>62</v>
+      </c>
+      <c r="D38" s="3">
         <f t="shared" si="40"/>
-        <v>NA</v>
+        <v>78</v>
       </c>
       <c r="E38" s="2">
         <f t="shared" si="4"/>
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="F38" s="2">
         <f t="shared" si="5"/>
-        <v>2019</v>
+        <v>2018</v>
       </c>
     </row>
     <row r="39">
@@ -1279,19 +1279,19 @@
       </c>
       <c r="B39" s="3">
         <f t="shared" ref="B39:D39" si="41">IF(RAND()&lt;0.2,"NA",RANDBETWEEN(60,80))</f>
-        <v>64</v>
+        <v>77</v>
       </c>
       <c r="C39" s="3">
         <f t="shared" si="41"/>
-        <v>68</v>
+        <v>80</v>
       </c>
       <c r="D39" s="3">
         <f t="shared" si="41"/>
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="E39" s="2">
         <f t="shared" si="4"/>
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="F39" s="2">
         <f t="shared" si="5"/>
@@ -1305,23 +1305,23 @@
       </c>
       <c r="B40" s="3">
         <f t="shared" ref="B40:D40" si="42">IF(RAND()&lt;0.2,"NA",RANDBETWEEN(60,80))</f>
-        <v>71</v>
-      </c>
-      <c r="C40" s="3">
+        <v>60</v>
+      </c>
+      <c r="C40" s="3" t="str">
         <f t="shared" si="42"/>
-        <v>77</v>
+        <v>NA</v>
       </c>
       <c r="D40" s="3">
         <f t="shared" si="42"/>
-        <v>63</v>
+        <v>75</v>
       </c>
       <c r="E40" s="2">
         <f t="shared" si="4"/>
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="F40" s="2">
         <f t="shared" si="5"/>
-        <v>2021</v>
+        <v>2018</v>
       </c>
     </row>
     <row r="41">
@@ -1331,23 +1331,23 @@
       </c>
       <c r="B41" s="3">
         <f t="shared" ref="B41:D41" si="43">IF(RAND()&lt;0.2,"NA",RANDBETWEEN(60,80))</f>
-        <v>79</v>
+        <v>62</v>
       </c>
       <c r="C41" s="3">
         <f t="shared" si="43"/>
-        <v>65</v>
-      </c>
-      <c r="D41" s="3" t="str">
+        <v>64</v>
+      </c>
+      <c r="D41" s="3">
         <f t="shared" si="43"/>
-        <v>NA</v>
+        <v>60</v>
       </c>
       <c r="E41" s="2">
         <f t="shared" si="4"/>
-        <v>85</v>
+        <v>79</v>
       </c>
       <c r="F41" s="2">
         <f t="shared" si="5"/>
-        <v>2020</v>
+        <v>2021</v>
       </c>
     </row>
     <row r="42">
@@ -1357,23 +1357,23 @@
       </c>
       <c r="B42" s="3">
         <f t="shared" ref="B42:D42" si="44">IF(RAND()&lt;0.2,"NA",RANDBETWEEN(60,80))</f>
-        <v>74</v>
-      </c>
-      <c r="C42" s="3" t="str">
+        <v>67</v>
+      </c>
+      <c r="C42" s="3">
         <f t="shared" si="44"/>
-        <v>NA</v>
+        <v>69</v>
       </c>
       <c r="D42" s="3">
         <f t="shared" si="44"/>
-        <v>64</v>
+        <v>72</v>
       </c>
       <c r="E42" s="2">
         <f t="shared" si="4"/>
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="F42" s="2">
         <f t="shared" si="5"/>
-        <v>2019</v>
+        <v>2021</v>
       </c>
     </row>
     <row r="43">
@@ -1383,23 +1383,23 @@
       </c>
       <c r="B43" s="3">
         <f t="shared" ref="B43:D43" si="45">IF(RAND()&lt;0.2,"NA",RANDBETWEEN(60,80))</f>
-        <v>76</v>
-      </c>
-      <c r="C43" s="3" t="str">
+        <v>64</v>
+      </c>
+      <c r="C43" s="3">
         <f t="shared" si="45"/>
-        <v>NA</v>
+        <v>75</v>
       </c>
       <c r="D43" s="3">
         <f t="shared" si="45"/>
-        <v>65</v>
+        <v>74</v>
       </c>
       <c r="E43" s="2">
         <f t="shared" si="4"/>
-        <v>80</v>
+        <v>87</v>
       </c>
       <c r="F43" s="2">
         <f t="shared" si="5"/>
-        <v>2020</v>
+        <v>2019</v>
       </c>
     </row>
     <row r="44">
@@ -1409,23 +1409,23 @@
       </c>
       <c r="B44" s="3">
         <f t="shared" ref="B44:D44" si="46">IF(RAND()&lt;0.2,"NA",RANDBETWEEN(60,80))</f>
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="C44" s="3">
         <f t="shared" si="46"/>
-        <v>76</v>
+        <v>62</v>
       </c>
       <c r="D44" s="3">
         <f t="shared" si="46"/>
-        <v>72</v>
+        <v>66</v>
       </c>
       <c r="E44" s="2">
         <f t="shared" si="4"/>
-        <v>84</v>
+        <v>5</v>
       </c>
       <c r="F44" s="2">
         <f t="shared" si="5"/>
-        <v>2018</v>
+        <v>2021</v>
       </c>
     </row>
     <row r="45">
@@ -1435,23 +1435,23 @@
       </c>
       <c r="B45" s="3">
         <f t="shared" ref="B45:D45" si="47">IF(RAND()&lt;0.2,"NA",RANDBETWEEN(60,80))</f>
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C45" s="3">
         <f t="shared" si="47"/>
-        <v>79</v>
-      </c>
-      <c r="D45" s="3">
+        <v>63</v>
+      </c>
+      <c r="D45" s="3" t="str">
         <f t="shared" si="47"/>
-        <v>64</v>
+        <v>NA</v>
       </c>
       <c r="E45" s="2">
         <f t="shared" si="4"/>
-        <v>86</v>
+        <v>500</v>
       </c>
       <c r="F45" s="2">
         <f t="shared" si="5"/>
-        <v>2021</v>
+        <v>2018</v>
       </c>
     </row>
     <row r="46">
@@ -1459,13 +1459,13 @@
         <f t="shared" si="2"/>
         <v>45</v>
       </c>
-      <c r="B46" s="3">
+      <c r="B46" s="3" t="str">
         <f t="shared" ref="B46:D46" si="48">IF(RAND()&lt;0.2,"NA",RANDBETWEEN(60,80))</f>
-        <v>66</v>
+        <v>NA</v>
       </c>
       <c r="C46" s="3">
         <f t="shared" si="48"/>
-        <v>80</v>
+        <v>72</v>
       </c>
       <c r="D46" s="3" t="str">
         <f t="shared" si="48"/>
@@ -1477,7 +1477,7 @@
       </c>
       <c r="F46" s="2">
         <f t="shared" si="5"/>
-        <v>2021</v>
+        <v>2020</v>
       </c>
     </row>
     <row r="47">
@@ -1487,23 +1487,23 @@
       </c>
       <c r="B47" s="3">
         <f t="shared" ref="B47:D47" si="49">IF(RAND()&lt;0.2,"NA",RANDBETWEEN(60,80))</f>
-        <v>74</v>
+        <v>63</v>
       </c>
       <c r="C47" s="3">
         <f t="shared" si="49"/>
-        <v>61</v>
-      </c>
-      <c r="D47" s="3" t="str">
+        <v>66</v>
+      </c>
+      <c r="D47" s="3">
         <f t="shared" si="49"/>
-        <v>NA</v>
+        <v>72</v>
       </c>
       <c r="E47" s="2">
         <f t="shared" si="4"/>
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="F47" s="2">
         <f t="shared" si="5"/>
-        <v>2021</v>
+        <v>2019</v>
       </c>
     </row>
     <row r="48">
@@ -1511,25 +1511,25 @@
         <f t="shared" si="2"/>
         <v>47</v>
       </c>
-      <c r="B48" s="3" t="str">
+      <c r="B48" s="3">
         <f t="shared" ref="B48:D48" si="50">IF(RAND()&lt;0.2,"NA",RANDBETWEEN(60,80))</f>
-        <v>NA</v>
+        <v>77</v>
       </c>
       <c r="C48" s="3">
         <f t="shared" si="50"/>
-        <v>61</v>
+        <v>76</v>
       </c>
       <c r="D48" s="3">
         <f t="shared" si="50"/>
-        <v>64</v>
+        <v>74</v>
       </c>
       <c r="E48" s="2">
         <f t="shared" si="4"/>
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="F48" s="2">
         <f t="shared" si="5"/>
-        <v>2021</v>
+        <v>2018</v>
       </c>
     </row>
     <row r="49">
@@ -1537,21 +1537,21 @@
         <f t="shared" si="2"/>
         <v>48</v>
       </c>
-      <c r="B49" s="3">
+      <c r="B49" s="3" t="str">
         <f t="shared" ref="B49:D49" si="51">IF(RAND()&lt;0.2,"NA",RANDBETWEEN(60,80))</f>
-        <v>64</v>
-      </c>
-      <c r="C49" s="3" t="str">
+        <v>NA</v>
+      </c>
+      <c r="C49" s="3">
         <f t="shared" si="51"/>
-        <v>NA</v>
+        <v>66</v>
       </c>
       <c r="D49" s="3">
         <f t="shared" si="51"/>
-        <v>69</v>
+        <v>61</v>
       </c>
       <c r="E49" s="2">
         <f t="shared" si="4"/>
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="F49" s="2">
         <f t="shared" si="5"/>
@@ -1563,25 +1563,25 @@
         <f t="shared" si="2"/>
         <v>49</v>
       </c>
-      <c r="B50" s="3">
+      <c r="B50" s="3" t="str">
         <f t="shared" ref="B50:D50" si="52">IF(RAND()&lt;0.2,"NA",RANDBETWEEN(60,80))</f>
-        <v>77</v>
-      </c>
-      <c r="C50" s="3">
+        <v>NA</v>
+      </c>
+      <c r="C50" s="3" t="str">
         <f t="shared" si="52"/>
-        <v>61</v>
-      </c>
-      <c r="D50" s="3" t="str">
+        <v>NA</v>
+      </c>
+      <c r="D50" s="3">
         <f t="shared" si="52"/>
-        <v>NA</v>
+        <v>62</v>
       </c>
       <c r="E50" s="2">
         <f t="shared" si="4"/>
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="F50" s="2">
         <f t="shared" si="5"/>
-        <v>2019</v>
+        <v>2018</v>
       </c>
     </row>
     <row r="51">
@@ -1589,25 +1589,25 @@
         <f t="shared" si="2"/>
         <v>50</v>
       </c>
-      <c r="B51" s="3">
+      <c r="B51" s="3" t="str">
         <f t="shared" ref="B51:D51" si="53">IF(RAND()&lt;0.2,"NA",RANDBETWEEN(60,80))</f>
-        <v>63</v>
+        <v>NA</v>
       </c>
       <c r="C51" s="3">
         <f t="shared" si="53"/>
-        <v>78</v>
-      </c>
-      <c r="D51" s="3">
+        <v>70</v>
+      </c>
+      <c r="D51" s="3" t="str">
         <f t="shared" si="53"/>
-        <v>63</v>
+        <v>NA</v>
       </c>
       <c r="E51" s="2">
         <f t="shared" si="4"/>
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="F51" s="2">
         <f t="shared" si="5"/>
-        <v>2021</v>
+        <v>2020</v>
       </c>
     </row>
     <row r="52">
@@ -1617,23 +1617,23 @@
       </c>
       <c r="B52" s="3">
         <f t="shared" ref="B52:D52" si="54">IF(RAND()&lt;0.2,"NA",RANDBETWEEN(60,80))</f>
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C52" s="3">
         <f t="shared" si="54"/>
-        <v>68</v>
-      </c>
-      <c r="D52" s="3" t="str">
+        <v>67</v>
+      </c>
+      <c r="D52" s="3">
         <f t="shared" si="54"/>
-        <v>NA</v>
+        <v>66</v>
       </c>
       <c r="E52" s="2">
         <f t="shared" si="4"/>
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="F52" s="2">
         <f t="shared" si="5"/>
-        <v>2020</v>
+        <v>2019</v>
       </c>
     </row>
     <row r="53">
@@ -1643,23 +1643,23 @@
       </c>
       <c r="B53" s="3">
         <f t="shared" ref="B53:D53" si="55">IF(RAND()&lt;0.2,"NA",RANDBETWEEN(60,80))</f>
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C53" s="3">
         <f t="shared" si="55"/>
-        <v>76</v>
+        <v>68</v>
       </c>
       <c r="D53" s="3">
         <f t="shared" si="55"/>
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="E53" s="2">
         <f t="shared" si="4"/>
-        <v>84</v>
+        <v>500</v>
       </c>
       <c r="F53" s="2">
         <f t="shared" si="5"/>
-        <v>2019</v>
+        <v>2021</v>
       </c>
     </row>
     <row r="54">
@@ -1669,19 +1669,19 @@
       </c>
       <c r="B54" s="3">
         <f t="shared" ref="B54:D54" si="56">IF(RAND()&lt;0.2,"NA",RANDBETWEEN(60,80))</f>
-        <v>79</v>
-      </c>
-      <c r="C54" s="3" t="str">
+        <v>67</v>
+      </c>
+      <c r="C54" s="3">
         <f t="shared" si="56"/>
-        <v>NA</v>
+        <v>66</v>
       </c>
       <c r="D54" s="3">
         <f t="shared" si="56"/>
-        <v>67</v>
+        <v>62</v>
       </c>
       <c r="E54" s="2">
         <f t="shared" si="4"/>
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="F54" s="2">
         <f t="shared" si="5"/>
@@ -1695,23 +1695,23 @@
       </c>
       <c r="B55" s="3">
         <f t="shared" ref="B55:D55" si="57">IF(RAND()&lt;0.2,"NA",RANDBETWEEN(60,80))</f>
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C55" s="3">
         <f t="shared" si="57"/>
-        <v>79</v>
-      </c>
-      <c r="D55" s="3" t="str">
+        <v>78</v>
+      </c>
+      <c r="D55" s="3">
         <f t="shared" si="57"/>
-        <v>NA</v>
+        <v>69</v>
       </c>
       <c r="E55" s="2">
         <f t="shared" si="4"/>
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="F55" s="2">
         <f t="shared" si="5"/>
-        <v>2020</v>
+        <v>2021</v>
       </c>
     </row>
     <row r="56">
@@ -1721,19 +1721,19 @@
       </c>
       <c r="B56" s="3">
         <f t="shared" ref="B56:D56" si="58">IF(RAND()&lt;0.2,"NA",RANDBETWEEN(60,80))</f>
-        <v>73</v>
-      </c>
-      <c r="C56" s="3" t="str">
+        <v>69</v>
+      </c>
+      <c r="C56" s="3">
         <f t="shared" si="58"/>
-        <v>NA</v>
-      </c>
-      <c r="D56" s="3">
+        <v>66</v>
+      </c>
+      <c r="D56" s="3" t="str">
         <f t="shared" si="58"/>
-        <v>77</v>
+        <v>NA</v>
       </c>
       <c r="E56" s="2">
         <f t="shared" si="4"/>
-        <v>81</v>
+        <v>88</v>
       </c>
       <c r="F56" s="2">
         <f t="shared" si="5"/>
@@ -1749,21 +1749,21 @@
         <f t="shared" ref="B57:D57" si="59">IF(RAND()&lt;0.2,"NA",RANDBETWEEN(60,80))</f>
         <v>NA</v>
       </c>
-      <c r="C57" s="3">
+      <c r="C57" s="3" t="str">
         <f t="shared" si="59"/>
-        <v>80</v>
+        <v>NA</v>
       </c>
       <c r="D57" s="3">
         <f t="shared" si="59"/>
-        <v>60</v>
+        <v>79</v>
       </c>
       <c r="E57" s="2">
         <f t="shared" si="4"/>
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="F57" s="2">
         <f t="shared" si="5"/>
-        <v>2020</v>
+        <v>2021</v>
       </c>
     </row>
     <row r="58">
@@ -1771,25 +1771,25 @@
         <f t="shared" si="2"/>
         <v>57</v>
       </c>
-      <c r="B58" s="3" t="str">
+      <c r="B58" s="3">
         <f t="shared" ref="B58:D58" si="60">IF(RAND()&lt;0.2,"NA",RANDBETWEEN(60,80))</f>
-        <v>NA</v>
+        <v>77</v>
       </c>
       <c r="C58" s="3">
         <f t="shared" si="60"/>
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="D58" s="3">
         <f t="shared" si="60"/>
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E58" s="2">
         <f t="shared" si="4"/>
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="F58" s="2">
         <f t="shared" si="5"/>
-        <v>2020</v>
+        <v>2021</v>
       </c>
     </row>
     <row r="59">
@@ -1797,17 +1797,17 @@
         <f t="shared" si="2"/>
         <v>58</v>
       </c>
-      <c r="B59" s="3" t="str">
+      <c r="B59" s="3">
         <f t="shared" ref="B59:D59" si="61">IF(RAND()&lt;0.2,"NA",RANDBETWEEN(60,80))</f>
-        <v>NA</v>
+        <v>74</v>
       </c>
       <c r="C59" s="3">
         <f t="shared" si="61"/>
-        <v>76</v>
+        <v>60</v>
       </c>
       <c r="D59" s="3">
         <f t="shared" si="61"/>
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="E59" s="2">
         <f t="shared" si="4"/>
@@ -1815,7 +1815,7 @@
       </c>
       <c r="F59" s="2">
         <f t="shared" si="5"/>
-        <v>2018</v>
+        <v>2020</v>
       </c>
     </row>
     <row r="60">
@@ -1825,23 +1825,23 @@
       </c>
       <c r="B60" s="3">
         <f t="shared" ref="B60:D60" si="62">IF(RAND()&lt;0.2,"NA",RANDBETWEEN(60,80))</f>
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="C60" s="3">
         <f t="shared" si="62"/>
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="D60" s="3">
         <f t="shared" si="62"/>
-        <v>74</v>
+        <v>66</v>
       </c>
       <c r="E60" s="2">
         <f t="shared" si="4"/>
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="F60" s="2">
         <f t="shared" si="5"/>
-        <v>2020</v>
+        <v>2018</v>
       </c>
     </row>
     <row r="61">
@@ -1851,23 +1851,23 @@
       </c>
       <c r="B61" s="3">
         <f t="shared" ref="B61:D61" si="63">IF(RAND()&lt;0.2,"NA",RANDBETWEEN(60,80))</f>
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C61" s="3">
         <f t="shared" si="63"/>
-        <v>60</v>
+        <v>74</v>
       </c>
       <c r="D61" s="3">
         <f t="shared" si="63"/>
-        <v>60</v>
+        <v>76</v>
       </c>
       <c r="E61" s="2">
         <f t="shared" si="4"/>
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="F61" s="2">
         <f t="shared" si="5"/>
-        <v>2021</v>
+        <v>2020</v>
       </c>
     </row>
     <row r="62">
@@ -1877,23 +1877,23 @@
       </c>
       <c r="B62" s="3">
         <f t="shared" ref="B62:D62" si="64">IF(RAND()&lt;0.2,"NA",RANDBETWEEN(60,80))</f>
-        <v>62</v>
+        <v>79</v>
       </c>
       <c r="C62" s="3">
         <f t="shared" si="64"/>
-        <v>75</v>
-      </c>
-      <c r="D62" s="3" t="str">
+        <v>76</v>
+      </c>
+      <c r="D62" s="3">
         <f t="shared" si="64"/>
-        <v>NA</v>
+        <v>65</v>
       </c>
       <c r="E62" s="2">
         <f t="shared" si="4"/>
-        <v>86</v>
+        <v>80</v>
       </c>
       <c r="F62" s="2">
         <f t="shared" si="5"/>
-        <v>2020</v>
+        <v>2018</v>
       </c>
     </row>
     <row r="63">
@@ -1903,23 +1903,23 @@
       </c>
       <c r="B63" s="3">
         <f t="shared" ref="B63:D63" si="65">IF(RAND()&lt;0.2,"NA",RANDBETWEEN(60,80))</f>
-        <v>64</v>
-      </c>
-      <c r="C63" s="3">
+        <v>68</v>
+      </c>
+      <c r="C63" s="3" t="str">
         <f t="shared" si="65"/>
-        <v>67</v>
+        <v>NA</v>
       </c>
       <c r="D63" s="3">
         <f t="shared" si="65"/>
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="E63" s="2">
         <f t="shared" si="4"/>
-        <v>500</v>
+        <v>89</v>
       </c>
       <c r="F63" s="2">
         <f t="shared" si="5"/>
-        <v>2019</v>
+        <v>2018</v>
       </c>
     </row>
     <row r="64">
@@ -1929,23 +1929,23 @@
       </c>
       <c r="B64" s="3">
         <f t="shared" ref="B64:D64" si="66">IF(RAND()&lt;0.2,"NA",RANDBETWEEN(60,80))</f>
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="C64" s="3">
         <f t="shared" si="66"/>
-        <v>63</v>
-      </c>
-      <c r="D64" s="3" t="str">
+        <v>78</v>
+      </c>
+      <c r="D64" s="3">
         <f t="shared" si="66"/>
-        <v>NA</v>
+        <v>65</v>
       </c>
       <c r="E64" s="2">
         <f t="shared" si="4"/>
-        <v>500</v>
+        <v>79</v>
       </c>
       <c r="F64" s="2">
         <f t="shared" si="5"/>
-        <v>2021</v>
+        <v>2020</v>
       </c>
     </row>
     <row r="65">
@@ -1953,25 +1953,25 @@
         <f t="shared" si="2"/>
         <v>64</v>
       </c>
-      <c r="B65" s="3" t="str">
+      <c r="B65" s="3">
         <f t="shared" ref="B65:D65" si="67">IF(RAND()&lt;0.2,"NA",RANDBETWEEN(60,80))</f>
-        <v>NA</v>
-      </c>
-      <c r="C65" s="3" t="str">
+        <v>70</v>
+      </c>
+      <c r="C65" s="3">
         <f t="shared" si="67"/>
-        <v>NA</v>
+        <v>75</v>
       </c>
       <c r="D65" s="3">
         <f t="shared" si="67"/>
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="E65" s="2">
         <f t="shared" si="4"/>
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="F65" s="2">
         <f t="shared" si="5"/>
-        <v>2021</v>
+        <v>2020</v>
       </c>
     </row>
     <row r="66">
@@ -1981,23 +1981,23 @@
       </c>
       <c r="B66" s="3">
         <f t="shared" ref="B66:D66" si="68">IF(RAND()&lt;0.2,"NA",RANDBETWEEN(60,80))</f>
-        <v>71</v>
+        <v>80</v>
       </c>
       <c r="C66" s="3">
         <f t="shared" si="68"/>
-        <v>71</v>
+        <v>65</v>
       </c>
       <c r="D66" s="3">
         <f t="shared" si="68"/>
-        <v>63</v>
+        <v>74</v>
       </c>
       <c r="E66" s="2">
         <f t="shared" si="4"/>
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="F66" s="2">
         <f t="shared" si="5"/>
-        <v>2020</v>
+        <v>2019</v>
       </c>
     </row>
     <row r="67">
@@ -2005,25 +2005,25 @@
         <f t="shared" si="2"/>
         <v>66</v>
       </c>
-      <c r="B67" s="3" t="str">
+      <c r="B67" s="3">
         <f t="shared" ref="B67:D67" si="69">IF(RAND()&lt;0.2,"NA",RANDBETWEEN(60,80))</f>
-        <v>NA</v>
+        <v>76</v>
       </c>
       <c r="C67" s="3">
         <f t="shared" si="69"/>
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="D67" s="3">
         <f t="shared" si="69"/>
-        <v>64</v>
+        <v>72</v>
       </c>
       <c r="E67" s="2">
         <f t="shared" si="4"/>
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="F67" s="2">
         <f t="shared" si="5"/>
-        <v>2021</v>
+        <v>2019</v>
       </c>
     </row>
     <row r="68">
@@ -2033,23 +2033,23 @@
       </c>
       <c r="B68" s="3">
         <f t="shared" ref="B68:D68" si="70">IF(RAND()&lt;0.2,"NA",RANDBETWEEN(60,80))</f>
-        <v>78</v>
+        <v>62</v>
       </c>
       <c r="C68" s="3">
         <f t="shared" si="70"/>
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D68" s="3">
         <f t="shared" si="70"/>
-        <v>79</v>
+        <v>63</v>
       </c>
       <c r="E68" s="2">
         <f t="shared" si="4"/>
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="F68" s="2">
         <f t="shared" si="5"/>
-        <v>2021</v>
+        <v>2019</v>
       </c>
     </row>
     <row r="69">
@@ -2057,25 +2057,25 @@
         <f t="shared" si="2"/>
         <v>68</v>
       </c>
-      <c r="B69" s="3" t="str">
+      <c r="B69" s="3">
         <f t="shared" ref="B69:D69" si="71">IF(RAND()&lt;0.2,"NA",RANDBETWEEN(60,80))</f>
-        <v>NA</v>
-      </c>
-      <c r="C69" s="3">
+        <v>67</v>
+      </c>
+      <c r="C69" s="3" t="str">
         <f t="shared" si="71"/>
-        <v>69</v>
+        <v>NA</v>
       </c>
       <c r="D69" s="3">
         <f t="shared" si="71"/>
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="E69" s="2">
         <f t="shared" si="4"/>
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="F69" s="2">
         <f t="shared" si="5"/>
-        <v>2021</v>
+        <v>2018</v>
       </c>
     </row>
     <row r="70">
@@ -2085,23 +2085,23 @@
       </c>
       <c r="B70" s="3">
         <f t="shared" ref="B70:D70" si="72">IF(RAND()&lt;0.2,"NA",RANDBETWEEN(60,80))</f>
-        <v>75</v>
-      </c>
-      <c r="C70" s="3" t="str">
+        <v>79</v>
+      </c>
+      <c r="C70" s="3">
         <f t="shared" si="72"/>
-        <v>NA</v>
+        <v>76</v>
       </c>
       <c r="D70" s="3">
         <f t="shared" si="72"/>
-        <v>67</v>
+        <v>62</v>
       </c>
       <c r="E70" s="2">
         <f t="shared" si="4"/>
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="F70" s="2">
         <f t="shared" si="5"/>
-        <v>2019</v>
+        <v>2020</v>
       </c>
     </row>
     <row r="71">
@@ -2111,19 +2111,19 @@
       </c>
       <c r="B71" s="3">
         <f t="shared" ref="B71:D71" si="73">IF(RAND()&lt;0.2,"NA",RANDBETWEEN(60,80))</f>
-        <v>64</v>
-      </c>
-      <c r="C71" s="3">
+        <v>76</v>
+      </c>
+      <c r="C71" s="3" t="str">
         <f t="shared" si="73"/>
-        <v>79</v>
+        <v>NA</v>
       </c>
       <c r="D71" s="3">
         <f t="shared" si="73"/>
-        <v>63</v>
+        <v>69</v>
       </c>
       <c r="E71" s="2">
         <f t="shared" si="4"/>
-        <v>500</v>
+        <v>89</v>
       </c>
       <c r="F71" s="2">
         <f t="shared" si="5"/>
@@ -2135,25 +2135,25 @@
         <f t="shared" si="2"/>
         <v>71</v>
       </c>
-      <c r="B72" s="3" t="str">
+      <c r="B72" s="3">
         <f t="shared" ref="B72:D72" si="74">IF(RAND()&lt;0.2,"NA",RANDBETWEEN(60,80))</f>
-        <v>NA</v>
+        <v>70</v>
       </c>
       <c r="C72" s="3">
         <f t="shared" si="74"/>
+        <v>74</v>
+      </c>
+      <c r="D72" s="3">
+        <f t="shared" si="74"/>
         <v>67</v>
       </c>
-      <c r="D72" s="3" t="str">
-        <f t="shared" si="74"/>
-        <v>NA</v>
-      </c>
       <c r="E72" s="2">
         <f t="shared" si="4"/>
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="F72" s="2">
         <f t="shared" si="5"/>
-        <v>2018</v>
+        <v>2020</v>
       </c>
     </row>
     <row r="73">
@@ -2161,13 +2161,13 @@
         <f t="shared" si="2"/>
         <v>72</v>
       </c>
-      <c r="B73" s="3" t="str">
+      <c r="B73" s="3">
         <f t="shared" ref="B73:D73" si="75">IF(RAND()&lt;0.2,"NA",RANDBETWEEN(60,80))</f>
-        <v>NA</v>
+        <v>62</v>
       </c>
       <c r="C73" s="3">
         <f t="shared" si="75"/>
-        <v>61</v>
+        <v>80</v>
       </c>
       <c r="D73" s="3">
         <f t="shared" si="75"/>
@@ -2175,11 +2175,11 @@
       </c>
       <c r="E73" s="2">
         <f t="shared" si="4"/>
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="F73" s="2">
         <f t="shared" si="5"/>
-        <v>2019</v>
+        <v>2021</v>
       </c>
     </row>
     <row r="74">
@@ -2189,23 +2189,23 @@
       </c>
       <c r="B74" s="3">
         <f t="shared" ref="B74:D74" si="76">IF(RAND()&lt;0.2,"NA",RANDBETWEEN(60,80))</f>
-        <v>76</v>
+        <v>68</v>
       </c>
       <c r="C74" s="3">
         <f t="shared" si="76"/>
-        <v>71</v>
+        <v>65</v>
       </c>
       <c r="D74" s="3">
         <f t="shared" si="76"/>
-        <v>62</v>
+        <v>80</v>
       </c>
       <c r="E74" s="2">
         <f t="shared" si="4"/>
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="F74" s="2">
         <f t="shared" si="5"/>
-        <v>2019</v>
+        <v>2020</v>
       </c>
     </row>
     <row r="75">
@@ -2213,25 +2213,25 @@
         <f t="shared" si="2"/>
         <v>74</v>
       </c>
-      <c r="B75" s="3" t="str">
+      <c r="B75" s="3">
         <f t="shared" ref="B75:D75" si="77">IF(RAND()&lt;0.2,"NA",RANDBETWEEN(60,80))</f>
-        <v>NA</v>
+        <v>79</v>
       </c>
       <c r="C75" s="3">
         <f t="shared" si="77"/>
-        <v>79</v>
+        <v>64</v>
       </c>
       <c r="D75" s="3">
         <f t="shared" si="77"/>
-        <v>72</v>
+        <v>80</v>
       </c>
       <c r="E75" s="2">
         <f t="shared" si="4"/>
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="F75" s="2">
         <f t="shared" si="5"/>
-        <v>2020</v>
+        <v>2018</v>
       </c>
     </row>
     <row r="76">
@@ -2239,13 +2239,13 @@
         <f t="shared" si="2"/>
         <v>75</v>
       </c>
-      <c r="B76" s="3" t="str">
+      <c r="B76" s="3">
         <f t="shared" ref="B76:D76" si="78">IF(RAND()&lt;0.2,"NA",RANDBETWEEN(60,80))</f>
-        <v>NA</v>
+        <v>73</v>
       </c>
       <c r="C76" s="3">
         <f t="shared" si="78"/>
-        <v>71</v>
+        <v>78</v>
       </c>
       <c r="D76" s="3" t="str">
         <f t="shared" si="78"/>
@@ -2253,11 +2253,11 @@
       </c>
       <c r="E76" s="2">
         <f t="shared" si="4"/>
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="F76" s="2">
         <f t="shared" si="5"/>
-        <v>2018</v>
+        <v>2019</v>
       </c>
     </row>
     <row r="77">
@@ -2267,7 +2267,7 @@
       </c>
       <c r="B77" s="3">
         <f t="shared" ref="B77:D77" si="79">IF(RAND()&lt;0.2,"NA",RANDBETWEEN(60,80))</f>
-        <v>77</v>
+        <v>64</v>
       </c>
       <c r="C77" s="3">
         <f t="shared" si="79"/>
@@ -2275,15 +2275,15 @@
       </c>
       <c r="D77" s="3">
         <f t="shared" si="79"/>
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="E77" s="2">
         <f t="shared" si="4"/>
-        <v>76</v>
+        <v>5</v>
       </c>
       <c r="F77" s="2">
         <f t="shared" si="5"/>
-        <v>2019</v>
+        <v>2020</v>
       </c>
     </row>
     <row r="78">
@@ -2291,13 +2291,13 @@
         <f t="shared" si="2"/>
         <v>77</v>
       </c>
-      <c r="B78" s="3" t="str">
+      <c r="B78" s="3">
         <f t="shared" ref="B78:D78" si="80">IF(RAND()&lt;0.2,"NA",RANDBETWEEN(60,80))</f>
-        <v>NA</v>
-      </c>
-      <c r="C78" s="3" t="str">
+        <v>61</v>
+      </c>
+      <c r="C78" s="3">
         <f t="shared" si="80"/>
-        <v>NA</v>
+        <v>69</v>
       </c>
       <c r="D78" s="3" t="str">
         <f t="shared" si="80"/>
@@ -2305,7 +2305,7 @@
       </c>
       <c r="E78" s="2">
         <f t="shared" si="4"/>
-        <v>76</v>
+        <v>89</v>
       </c>
       <c r="F78" s="2">
         <f t="shared" si="5"/>
@@ -2319,19 +2319,19 @@
       </c>
       <c r="B79" s="3">
         <f t="shared" ref="B79:D79" si="81">IF(RAND()&lt;0.2,"NA",RANDBETWEEN(60,80))</f>
-        <v>63</v>
+        <v>71</v>
       </c>
       <c r="C79" s="3">
         <f t="shared" si="81"/>
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="D79" s="3">
         <f t="shared" si="81"/>
-        <v>77</v>
+        <v>65</v>
       </c>
       <c r="E79" s="2">
         <f t="shared" si="4"/>
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="F79" s="2">
         <f t="shared" si="5"/>
@@ -2345,7 +2345,7 @@
       </c>
       <c r="B80" s="3">
         <f t="shared" ref="B80:D80" si="82">IF(RAND()&lt;0.2,"NA",RANDBETWEEN(60,80))</f>
-        <v>77</v>
+        <v>60</v>
       </c>
       <c r="C80" s="3" t="str">
         <f t="shared" si="82"/>
@@ -2353,15 +2353,15 @@
       </c>
       <c r="D80" s="3">
         <f t="shared" si="82"/>
-        <v>71</v>
+        <v>62</v>
       </c>
       <c r="E80" s="2">
         <f t="shared" si="4"/>
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="F80" s="2">
         <f t="shared" si="5"/>
-        <v>2020</v>
+        <v>2021</v>
       </c>
     </row>
     <row r="81">
@@ -2371,19 +2371,19 @@
       </c>
       <c r="B81" s="3">
         <f t="shared" ref="B81:D81" si="83">IF(RAND()&lt;0.2,"NA",RANDBETWEEN(60,80))</f>
-        <v>71</v>
-      </c>
-      <c r="C81" s="3">
+        <v>65</v>
+      </c>
+      <c r="C81" s="3" t="str">
+        <f t="shared" si="83"/>
+        <v>NA</v>
+      </c>
+      <c r="D81" s="3">
         <f t="shared" si="83"/>
         <v>76</v>
       </c>
-      <c r="D81" s="3">
-        <f t="shared" si="83"/>
-        <v>71</v>
-      </c>
       <c r="E81" s="2">
         <f t="shared" si="4"/>
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="F81" s="2">
         <f t="shared" si="5"/>
@@ -2397,23 +2397,23 @@
       </c>
       <c r="B82" s="3">
         <f t="shared" ref="B82:D82" si="84">IF(RAND()&lt;0.2,"NA",RANDBETWEEN(60,80))</f>
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="C82" s="3">
         <f t="shared" si="84"/>
-        <v>72</v>
-      </c>
-      <c r="D82" s="3" t="str">
+        <v>70</v>
+      </c>
+      <c r="D82" s="3">
         <f t="shared" si="84"/>
-        <v>NA</v>
+        <v>79</v>
       </c>
       <c r="E82" s="2">
         <f t="shared" si="4"/>
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="F82" s="2">
         <f t="shared" si="5"/>
-        <v>2020</v>
+        <v>2021</v>
       </c>
     </row>
     <row r="83">
@@ -2421,25 +2421,25 @@
         <f t="shared" si="2"/>
         <v>82</v>
       </c>
-      <c r="B83" s="3">
+      <c r="B83" s="3" t="str">
         <f t="shared" ref="B83:D83" si="85">IF(RAND()&lt;0.2,"NA",RANDBETWEEN(60,80))</f>
-        <v>61</v>
-      </c>
-      <c r="C83" s="3" t="str">
+        <v>NA</v>
+      </c>
+      <c r="C83" s="3">
         <f t="shared" si="85"/>
-        <v>NA</v>
+        <v>74</v>
       </c>
       <c r="D83" s="3">
         <f t="shared" si="85"/>
-        <v>61</v>
+        <v>71</v>
       </c>
       <c r="E83" s="2">
         <f t="shared" si="4"/>
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="F83" s="2">
         <f t="shared" si="5"/>
-        <v>2019</v>
+        <v>2020</v>
       </c>
     </row>
     <row r="84">
@@ -2447,25 +2447,25 @@
         <f t="shared" si="2"/>
         <v>83</v>
       </c>
-      <c r="B84" s="3">
+      <c r="B84" s="3" t="str">
         <f t="shared" ref="B84:D84" si="86">IF(RAND()&lt;0.2,"NA",RANDBETWEEN(60,80))</f>
-        <v>66</v>
+        <v>NA</v>
       </c>
       <c r="C84" s="3">
         <f t="shared" si="86"/>
-        <v>72</v>
+        <v>66</v>
       </c>
       <c r="D84" s="3">
         <f t="shared" si="86"/>
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="E84" s="2">
         <f t="shared" si="4"/>
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="F84" s="2">
         <f t="shared" si="5"/>
-        <v>2020</v>
+        <v>2021</v>
       </c>
     </row>
     <row r="85">
@@ -2475,19 +2475,19 @@
       </c>
       <c r="B85" s="3">
         <f t="shared" ref="B85:D85" si="87">IF(RAND()&lt;0.2,"NA",RANDBETWEEN(60,80))</f>
-        <v>61</v>
+        <v>77</v>
       </c>
       <c r="C85" s="3">
         <f t="shared" si="87"/>
-        <v>77</v>
-      </c>
-      <c r="D85" s="3">
+        <v>67</v>
+      </c>
+      <c r="D85" s="3" t="str">
         <f t="shared" si="87"/>
+        <v>NA</v>
+      </c>
+      <c r="E85" s="2">
+        <f t="shared" si="4"/>
         <v>75</v>
-      </c>
-      <c r="E85" s="2">
-        <f t="shared" si="4"/>
-        <v>87</v>
       </c>
       <c r="F85" s="2">
         <f t="shared" si="5"/>
@@ -2499,17 +2499,17 @@
         <f t="shared" si="2"/>
         <v>85</v>
       </c>
-      <c r="B86" s="3">
+      <c r="B86" s="3" t="str">
         <f t="shared" ref="B86:D86" si="88">IF(RAND()&lt;0.2,"NA",RANDBETWEEN(60,80))</f>
-        <v>61</v>
-      </c>
-      <c r="C86" s="3" t="str">
+        <v>NA</v>
+      </c>
+      <c r="C86" s="3">
         <f t="shared" si="88"/>
-        <v>NA</v>
-      </c>
-      <c r="D86" s="3">
+        <v>68</v>
+      </c>
+      <c r="D86" s="3" t="str">
         <f t="shared" si="88"/>
-        <v>75</v>
+        <v>NA</v>
       </c>
       <c r="E86" s="2">
         <f t="shared" si="4"/>
@@ -2517,7 +2517,7 @@
       </c>
       <c r="F86" s="2">
         <f t="shared" si="5"/>
-        <v>2019</v>
+        <v>2021</v>
       </c>
     </row>
     <row r="87">
@@ -2527,11 +2527,11 @@
       </c>
       <c r="B87" s="3">
         <f t="shared" ref="B87:D87" si="89">IF(RAND()&lt;0.2,"NA",RANDBETWEEN(60,80))</f>
-        <v>74</v>
-      </c>
-      <c r="C87" s="3">
+        <v>75</v>
+      </c>
+      <c r="C87" s="3" t="str">
         <f t="shared" si="89"/>
-        <v>66</v>
+        <v>NA</v>
       </c>
       <c r="D87" s="3">
         <f t="shared" si="89"/>
@@ -2539,7 +2539,7 @@
       </c>
       <c r="E87" s="2">
         <f t="shared" si="4"/>
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="F87" s="2">
         <f t="shared" si="5"/>
@@ -2551,25 +2551,25 @@
         <f t="shared" si="2"/>
         <v>87</v>
       </c>
-      <c r="B88" s="3" t="str">
+      <c r="B88" s="3">
         <f t="shared" ref="B88:D88" si="90">IF(RAND()&lt;0.2,"NA",RANDBETWEEN(60,80))</f>
-        <v>NA</v>
+        <v>77</v>
       </c>
       <c r="C88" s="3">
         <f t="shared" si="90"/>
-        <v>67</v>
-      </c>
-      <c r="D88" s="3">
+        <v>64</v>
+      </c>
+      <c r="D88" s="3" t="str">
         <f t="shared" si="90"/>
-        <v>77</v>
+        <v>NA</v>
       </c>
       <c r="E88" s="2">
         <f t="shared" si="4"/>
-        <v>75</v>
+        <v>86</v>
       </c>
       <c r="F88" s="2">
         <f t="shared" si="5"/>
-        <v>2020</v>
+        <v>2019</v>
       </c>
     </row>
     <row r="89">
@@ -2577,13 +2577,13 @@
         <f t="shared" si="2"/>
         <v>88</v>
       </c>
-      <c r="B89" s="3">
+      <c r="B89" s="3" t="str">
         <f t="shared" ref="B89:D89" si="91">IF(RAND()&lt;0.2,"NA",RANDBETWEEN(60,80))</f>
-        <v>61</v>
+        <v>NA</v>
       </c>
       <c r="C89" s="3">
         <f t="shared" si="91"/>
-        <v>79</v>
+        <v>65</v>
       </c>
       <c r="D89" s="3">
         <f t="shared" si="91"/>
@@ -2591,11 +2591,11 @@
       </c>
       <c r="E89" s="2">
         <f t="shared" si="4"/>
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="F89" s="2">
         <f t="shared" si="5"/>
-        <v>2019</v>
+        <v>2020</v>
       </c>
     </row>
     <row r="90">
@@ -2605,23 +2605,23 @@
       </c>
       <c r="B90" s="3">
         <f t="shared" ref="B90:D90" si="92">IF(RAND()&lt;0.2,"NA",RANDBETWEEN(60,80))</f>
-        <v>61</v>
+        <v>71</v>
       </c>
       <c r="C90" s="3">
         <f t="shared" si="92"/>
-        <v>77</v>
+        <v>66</v>
       </c>
       <c r="D90" s="3">
         <f t="shared" si="92"/>
-        <v>68</v>
+        <v>78</v>
       </c>
       <c r="E90" s="2">
         <f t="shared" si="4"/>
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="F90" s="2">
         <f t="shared" si="5"/>
-        <v>2018</v>
+        <v>2019</v>
       </c>
     </row>
     <row r="91">
@@ -2631,23 +2631,23 @@
       </c>
       <c r="B91" s="3">
         <f t="shared" ref="B91:D91" si="93">IF(RAND()&lt;0.2,"NA",RANDBETWEEN(60,80))</f>
-        <v>80</v>
+        <v>71</v>
       </c>
       <c r="C91" s="3">
         <f t="shared" si="93"/>
-        <v>73</v>
-      </c>
-      <c r="D91" s="3" t="str">
+        <v>78</v>
+      </c>
+      <c r="D91" s="3">
         <f t="shared" si="93"/>
-        <v>NA</v>
+        <v>72</v>
       </c>
       <c r="E91" s="2">
         <f t="shared" si="4"/>
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="F91" s="2">
         <f t="shared" si="5"/>
-        <v>2018</v>
+        <v>2019</v>
       </c>
     </row>
     <row r="92">
@@ -2661,15 +2661,15 @@
       </c>
       <c r="C92" s="3">
         <f t="shared" si="94"/>
-        <v>60</v>
+        <v>79</v>
       </c>
       <c r="D92" s="3">
         <f t="shared" si="94"/>
-        <v>70</v>
+        <v>64</v>
       </c>
       <c r="E92" s="2">
         <f t="shared" si="4"/>
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="F92" s="2">
         <f t="shared" si="5"/>
@@ -2683,23 +2683,23 @@
       </c>
       <c r="B93" s="3">
         <f t="shared" ref="B93:D93" si="95">IF(RAND()&lt;0.2,"NA",RANDBETWEEN(60,80))</f>
-        <v>60</v>
+        <v>79</v>
       </c>
       <c r="C93" s="3">
         <f t="shared" si="95"/>
-        <v>60</v>
-      </c>
-      <c r="D93" s="3">
+        <v>65</v>
+      </c>
+      <c r="D93" s="3" t="str">
         <f t="shared" si="95"/>
-        <v>71</v>
+        <v>NA</v>
       </c>
       <c r="E93" s="2">
         <f t="shared" si="4"/>
-        <v>500</v>
+        <v>80</v>
       </c>
       <c r="F93" s="2">
         <f t="shared" si="5"/>
-        <v>2019</v>
+        <v>2018</v>
       </c>
     </row>
     <row r="94">
@@ -2709,15 +2709,15 @@
       </c>
       <c r="B94" s="3">
         <f t="shared" ref="B94:D94" si="96">IF(RAND()&lt;0.2,"NA",RANDBETWEEN(60,80))</f>
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="C94" s="3">
         <f t="shared" si="96"/>
-        <v>73</v>
-      </c>
-      <c r="D94" s="3" t="str">
+        <v>78</v>
+      </c>
+      <c r="D94" s="3">
         <f t="shared" si="96"/>
-        <v>NA</v>
+        <v>69</v>
       </c>
       <c r="E94" s="2">
         <f t="shared" si="4"/>
@@ -2725,7 +2725,7 @@
       </c>
       <c r="F94" s="2">
         <f t="shared" si="5"/>
-        <v>2019</v>
+        <v>2018</v>
       </c>
     </row>
     <row r="95">
@@ -2733,25 +2733,25 @@
         <f t="shared" si="2"/>
         <v>94</v>
       </c>
-      <c r="B95" s="3">
+      <c r="B95" s="3" t="str">
         <f t="shared" ref="B95:D95" si="97">IF(RAND()&lt;0.2,"NA",RANDBETWEEN(60,80))</f>
-        <v>80</v>
-      </c>
-      <c r="C95" s="3">
+        <v>NA</v>
+      </c>
+      <c r="C95" s="3" t="str">
         <f t="shared" si="97"/>
-        <v>65</v>
-      </c>
-      <c r="D95" s="3" t="str">
+        <v>NA</v>
+      </c>
+      <c r="D95" s="3">
         <f t="shared" si="97"/>
-        <v>NA</v>
+        <v>76</v>
       </c>
       <c r="E95" s="2">
         <f t="shared" si="4"/>
-        <v>500</v>
+        <v>75</v>
       </c>
       <c r="F95" s="2">
         <f t="shared" si="5"/>
-        <v>2019</v>
+        <v>2020</v>
       </c>
     </row>
     <row r="96">
@@ -2761,23 +2761,23 @@
       </c>
       <c r="B96" s="3">
         <f t="shared" ref="B96:D96" si="98">IF(RAND()&lt;0.2,"NA",RANDBETWEEN(60,80))</f>
-        <v>61</v>
-      </c>
-      <c r="C96" s="3">
+        <v>64</v>
+      </c>
+      <c r="C96" s="3" t="str">
         <f t="shared" si="98"/>
-        <v>75</v>
+        <v>NA</v>
       </c>
       <c r="D96" s="3">
         <f t="shared" si="98"/>
-        <v>77</v>
+        <v>61</v>
       </c>
       <c r="E96" s="2">
         <f t="shared" si="4"/>
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="F96" s="2">
         <f t="shared" si="5"/>
-        <v>2020</v>
+        <v>2021</v>
       </c>
     </row>
     <row r="97">
@@ -2787,23 +2787,23 @@
       </c>
       <c r="B97" s="3">
         <f t="shared" ref="B97:D97" si="99">IF(RAND()&lt;0.2,"NA",RANDBETWEEN(60,80))</f>
-        <v>78</v>
+        <v>60</v>
       </c>
       <c r="C97" s="3">
         <f t="shared" si="99"/>
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D97" s="3">
         <f t="shared" si="99"/>
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="E97" s="2">
         <f t="shared" si="4"/>
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="F97" s="2">
         <f t="shared" si="5"/>
-        <v>2018</v>
+        <v>2019</v>
       </c>
     </row>
     <row r="98">
@@ -2811,25 +2811,25 @@
         <f t="shared" si="2"/>
         <v>97</v>
       </c>
-      <c r="B98" s="3">
+      <c r="B98" s="3" t="str">
         <f t="shared" ref="B98:D98" si="100">IF(RAND()&lt;0.2,"NA",RANDBETWEEN(60,80))</f>
-        <v>74</v>
+        <v>NA</v>
       </c>
       <c r="C98" s="3">
         <f t="shared" si="100"/>
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="D98" s="3">
         <f t="shared" si="100"/>
-        <v>67</v>
+        <v>62</v>
       </c>
       <c r="E98" s="2">
         <f t="shared" si="4"/>
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="F98" s="2">
         <f t="shared" si="5"/>
-        <v>2020</v>
+        <v>2019</v>
       </c>
     </row>
     <row r="99">
@@ -2839,23 +2839,23 @@
       </c>
       <c r="B99" s="3">
         <f t="shared" ref="B99:D99" si="101">IF(RAND()&lt;0.2,"NA",RANDBETWEEN(60,80))</f>
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="C99" s="3">
         <f t="shared" si="101"/>
-        <v>68</v>
+        <v>79</v>
       </c>
       <c r="D99" s="3">
         <f t="shared" si="101"/>
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="E99" s="2">
         <f t="shared" si="4"/>
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="F99" s="2">
         <f t="shared" si="5"/>
-        <v>2019</v>
+        <v>2018</v>
       </c>
     </row>
     <row r="100">
@@ -2863,13 +2863,13 @@
         <f t="shared" si="2"/>
         <v>99</v>
       </c>
-      <c r="B100" s="3" t="str">
+      <c r="B100" s="3">
         <f t="shared" ref="B100:D100" si="102">IF(RAND()&lt;0.2,"NA",RANDBETWEEN(60,80))</f>
-        <v>NA</v>
+        <v>77</v>
       </c>
       <c r="C100" s="3">
         <f t="shared" si="102"/>
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="D100" s="3" t="str">
         <f t="shared" si="102"/>
@@ -2877,7 +2877,7 @@
       </c>
       <c r="E100" s="2">
         <f t="shared" si="4"/>
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="F100" s="2">
         <f t="shared" si="5"/>
@@ -2891,23 +2891,23 @@
       </c>
       <c r="B101" s="3">
         <f t="shared" ref="B101:D101" si="103">IF(RAND()&lt;0.2,"NA",RANDBETWEEN(60,80))</f>
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C101" s="3">
         <f t="shared" si="103"/>
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="D101" s="3">
         <f t="shared" si="103"/>
-        <v>78</v>
+        <v>68</v>
       </c>
       <c r="E101" s="2">
         <f t="shared" si="4"/>
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="F101" s="2">
         <f t="shared" si="5"/>
-        <v>2020</v>
+        <v>2021</v>
       </c>
     </row>
     <row r="102">
@@ -2917,23 +2917,23 @@
       </c>
       <c r="B102" s="3">
         <f t="shared" ref="B102:D102" si="104">IF(RAND()&lt;0.2,"NA",RANDBETWEEN(60,80))</f>
-        <v>73</v>
-      </c>
-      <c r="C102" s="3">
+        <v>68</v>
+      </c>
+      <c r="C102" s="3" t="str">
         <f t="shared" si="104"/>
-        <v>80</v>
+        <v>NA</v>
       </c>
       <c r="D102" s="3">
         <f t="shared" si="104"/>
-        <v>75</v>
+        <v>67</v>
       </c>
       <c r="E102" s="2">
         <f t="shared" si="4"/>
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="F102" s="2">
         <f t="shared" si="5"/>
-        <v>2018</v>
+        <v>2021</v>
       </c>
     </row>
     <row r="103">
@@ -2943,23 +2943,23 @@
       </c>
       <c r="B103" s="3">
         <f t="shared" ref="B103:D103" si="105">IF(RAND()&lt;0.2,"NA",RANDBETWEEN(60,80))</f>
-        <v>63</v>
+        <v>73</v>
       </c>
       <c r="C103" s="3">
         <f t="shared" si="105"/>
-        <v>79</v>
-      </c>
-      <c r="D103" s="3">
+        <v>61</v>
+      </c>
+      <c r="D103" s="3" t="str">
         <f t="shared" si="105"/>
-        <v>62</v>
+        <v>NA</v>
       </c>
       <c r="E103" s="2">
         <f t="shared" si="4"/>
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="F103" s="2">
         <f t="shared" si="5"/>
-        <v>2018</v>
+        <v>2020</v>
       </c>
     </row>
     <row r="104">
@@ -2969,23 +2969,23 @@
       </c>
       <c r="B104" s="3">
         <f t="shared" ref="B104:D104" si="106">IF(RAND()&lt;0.2,"NA",RANDBETWEEN(60,80))</f>
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C104" s="3">
         <f t="shared" si="106"/>
-        <v>75</v>
-      </c>
-      <c r="D104" s="3">
+        <v>68</v>
+      </c>
+      <c r="D104" s="3" t="str">
         <f t="shared" si="106"/>
-        <v>64</v>
+        <v>NA</v>
       </c>
       <c r="E104" s="2">
         <f t="shared" si="4"/>
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="F104" s="2">
         <f t="shared" si="5"/>
-        <v>2021</v>
+        <v>2020</v>
       </c>
     </row>
     <row r="105">
@@ -2995,19 +2995,19 @@
       </c>
       <c r="B105" s="3">
         <f t="shared" ref="B105:D105" si="107">IF(RAND()&lt;0.2,"NA",RANDBETWEEN(60,80))</f>
-        <v>80</v>
-      </c>
-      <c r="C105" s="3">
+        <v>78</v>
+      </c>
+      <c r="C105" s="3" t="str">
         <f t="shared" si="107"/>
-        <v>77</v>
+        <v>NA</v>
       </c>
       <c r="D105" s="3">
         <f t="shared" si="107"/>
-        <v>78</v>
+        <v>66</v>
       </c>
       <c r="E105" s="2">
         <f t="shared" si="4"/>
-        <v>90</v>
+        <v>76</v>
       </c>
       <c r="F105" s="2">
         <f t="shared" si="5"/>
@@ -3021,23 +3021,23 @@
       </c>
       <c r="B106" s="3">
         <f t="shared" ref="B106:D106" si="108">IF(RAND()&lt;0.2,"NA",RANDBETWEEN(60,80))</f>
-        <v>67</v>
-      </c>
-      <c r="C106" s="3">
+        <v>78</v>
+      </c>
+      <c r="C106" s="3" t="str">
         <f t="shared" si="108"/>
-        <v>61</v>
+        <v>NA</v>
       </c>
       <c r="D106" s="3">
         <f t="shared" si="108"/>
-        <v>60</v>
+        <v>75</v>
       </c>
       <c r="E106" s="2">
         <f t="shared" si="4"/>
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="F106" s="2">
         <f t="shared" si="5"/>
-        <v>2018</v>
+        <v>2020</v>
       </c>
     </row>
     <row r="107">
@@ -3047,23 +3047,23 @@
       </c>
       <c r="B107" s="3">
         <f t="shared" ref="B107:D107" si="109">IF(RAND()&lt;0.2,"NA",RANDBETWEEN(60,80))</f>
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="C107" s="3">
         <f t="shared" si="109"/>
-        <v>80</v>
+        <v>71</v>
       </c>
       <c r="D107" s="3">
         <f t="shared" si="109"/>
-        <v>73</v>
+        <v>66</v>
       </c>
       <c r="E107" s="2">
         <f t="shared" si="4"/>
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="F107" s="2">
         <f t="shared" si="5"/>
-        <v>2018</v>
+        <v>2021</v>
       </c>
     </row>
     <row r="108">
@@ -3073,23 +3073,23 @@
       </c>
       <c r="B108" s="3">
         <f t="shared" ref="B108:D108" si="110">IF(RAND()&lt;0.2,"NA",RANDBETWEEN(60,80))</f>
-        <v>66</v>
-      </c>
-      <c r="C108" s="3">
+        <v>61</v>
+      </c>
+      <c r="C108" s="3" t="str">
         <f t="shared" si="110"/>
-        <v>71</v>
-      </c>
-      <c r="D108" s="3">
+        <v>NA</v>
+      </c>
+      <c r="D108" s="3" t="str">
         <f t="shared" si="110"/>
-        <v>75</v>
+        <v>NA</v>
       </c>
       <c r="E108" s="2">
         <f t="shared" si="4"/>
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="F108" s="2">
         <f t="shared" si="5"/>
-        <v>2021</v>
+        <v>2020</v>
       </c>
     </row>
     <row r="109">
@@ -3099,19 +3099,19 @@
       </c>
       <c r="B109" s="3">
         <f t="shared" ref="B109:D109" si="111">IF(RAND()&lt;0.2,"NA",RANDBETWEEN(60,80))</f>
-        <v>71</v>
-      </c>
-      <c r="C109" s="3">
+        <v>65</v>
+      </c>
+      <c r="C109" s="3" t="str">
         <f t="shared" si="111"/>
-        <v>66</v>
+        <v>NA</v>
       </c>
       <c r="D109" s="3">
         <f t="shared" si="111"/>
-        <v>64</v>
+        <v>77</v>
       </c>
       <c r="E109" s="2">
         <f t="shared" si="4"/>
-        <v>83</v>
+        <v>78</v>
       </c>
       <c r="F109" s="2">
         <f t="shared" si="5"/>
@@ -3125,19 +3125,19 @@
       </c>
       <c r="B110" s="3">
         <f t="shared" ref="B110:D110" si="112">IF(RAND()&lt;0.2,"NA",RANDBETWEEN(60,80))</f>
-        <v>79</v>
-      </c>
-      <c r="C110" s="3">
+        <v>73</v>
+      </c>
+      <c r="C110" s="3" t="str">
         <f t="shared" si="112"/>
-        <v>60</v>
+        <v>NA</v>
       </c>
       <c r="D110" s="3">
         <f t="shared" si="112"/>
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="E110" s="2">
         <f t="shared" si="4"/>
-        <v>90</v>
+        <v>77</v>
       </c>
       <c r="F110" s="2">
         <f t="shared" si="5"/>
@@ -3151,23 +3151,23 @@
       </c>
       <c r="B111" s="3">
         <f t="shared" ref="B111:D111" si="113">IF(RAND()&lt;0.2,"NA",RANDBETWEEN(60,80))</f>
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C111" s="3">
         <f t="shared" si="113"/>
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="D111" s="3">
         <f t="shared" si="113"/>
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="E111" s="2">
         <f t="shared" si="4"/>
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="F111" s="2">
         <f t="shared" si="5"/>
-        <v>2018</v>
+        <v>2021</v>
       </c>
     </row>
     <row r="112">
@@ -3177,23 +3177,23 @@
       </c>
       <c r="B112" s="3">
         <f t="shared" ref="B112:D112" si="114">IF(RAND()&lt;0.2,"NA",RANDBETWEEN(60,80))</f>
-        <v>80</v>
-      </c>
-      <c r="C112" s="3" t="str">
+        <v>76</v>
+      </c>
+      <c r="C112" s="3">
         <f t="shared" si="114"/>
-        <v>NA</v>
+        <v>61</v>
       </c>
       <c r="D112" s="3">
         <f t="shared" si="114"/>
-        <v>76</v>
+        <v>60</v>
       </c>
       <c r="E112" s="2">
         <f t="shared" si="4"/>
-        <v>500</v>
+        <v>82</v>
       </c>
       <c r="F112" s="2">
         <f t="shared" si="5"/>
-        <v>2018</v>
+        <v>2020</v>
       </c>
     </row>
     <row r="113">
@@ -3203,19 +3203,19 @@
       </c>
       <c r="B113" s="3">
         <f t="shared" ref="B113:D113" si="115">IF(RAND()&lt;0.2,"NA",RANDBETWEEN(60,80))</f>
-        <v>68</v>
+        <v>61</v>
       </c>
       <c r="C113" s="3">
         <f t="shared" si="115"/>
-        <v>74</v>
+        <v>69</v>
       </c>
       <c r="D113" s="3">
         <f t="shared" si="115"/>
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="E113" s="2">
         <f t="shared" si="4"/>
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="F113" s="2">
         <f t="shared" si="5"/>
@@ -3227,13 +3227,13 @@
         <f t="shared" si="2"/>
         <v>113</v>
       </c>
-      <c r="B114" s="3" t="str">
+      <c r="B114" s="3">
         <f t="shared" ref="B114:D114" si="116">IF(RAND()&lt;0.2,"NA",RANDBETWEEN(60,80))</f>
-        <v>NA</v>
+        <v>80</v>
       </c>
       <c r="C114" s="3">
         <f t="shared" si="116"/>
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="D114" s="3" t="str">
         <f t="shared" si="116"/>
@@ -3241,11 +3241,11 @@
       </c>
       <c r="E114" s="2">
         <f t="shared" si="4"/>
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="F114" s="2">
         <f t="shared" si="5"/>
-        <v>2020</v>
+        <v>2018</v>
       </c>
     </row>
     <row r="115">
@@ -3255,23 +3255,23 @@
       </c>
       <c r="B115" s="3">
         <f t="shared" ref="B115:D115" si="117">IF(RAND()&lt;0.2,"NA",RANDBETWEEN(60,80))</f>
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="C115" s="3">
         <f t="shared" si="117"/>
-        <v>61</v>
-      </c>
-      <c r="D115" s="3" t="str">
+        <v>68</v>
+      </c>
+      <c r="D115" s="3">
         <f t="shared" si="117"/>
-        <v>NA</v>
+        <v>64</v>
       </c>
       <c r="E115" s="2">
         <f t="shared" si="4"/>
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="F115" s="2">
         <f t="shared" si="5"/>
-        <v>2018</v>
+        <v>2019</v>
       </c>
     </row>
     <row r="116">
@@ -3281,19 +3281,19 @@
       </c>
       <c r="B116" s="3">
         <f t="shared" ref="B116:D116" si="118">IF(RAND()&lt;0.2,"NA",RANDBETWEEN(60,80))</f>
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C116" s="3">
         <f t="shared" si="118"/>
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="D116" s="3">
         <f t="shared" si="118"/>
-        <v>79</v>
+        <v>68</v>
       </c>
       <c r="E116" s="2">
         <f t="shared" si="4"/>
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="F116" s="2">
         <f t="shared" si="5"/>
@@ -3305,25 +3305,25 @@
         <f t="shared" si="2"/>
         <v>116</v>
       </c>
-      <c r="B117" s="3" t="str">
+      <c r="B117" s="3">
         <f t="shared" ref="B117:D117" si="119">IF(RAND()&lt;0.2,"NA",RANDBETWEEN(60,80))</f>
-        <v>NA</v>
+        <v>71</v>
       </c>
       <c r="C117" s="3">
         <f t="shared" si="119"/>
+        <v>66</v>
+      </c>
+      <c r="D117" s="3" t="str">
+        <f t="shared" si="119"/>
+        <v>NA</v>
+      </c>
+      <c r="E117" s="2">
+        <f t="shared" si="4"/>
         <v>80</v>
       </c>
-      <c r="D117" s="3">
-        <f t="shared" si="119"/>
-        <v>64</v>
-      </c>
-      <c r="E117" s="2">
-        <f t="shared" si="4"/>
-        <v>87</v>
-      </c>
       <c r="F117" s="2">
         <f t="shared" si="5"/>
-        <v>2019</v>
+        <v>2020</v>
       </c>
     </row>
     <row r="118">
@@ -3333,19 +3333,19 @@
       </c>
       <c r="B118" s="3">
         <f t="shared" ref="B118:D118" si="120">IF(RAND()&lt;0.2,"NA",RANDBETWEEN(60,80))</f>
-        <v>66</v>
+        <v>75</v>
       </c>
       <c r="C118" s="3">
         <f t="shared" si="120"/>
-        <v>65</v>
+        <v>77</v>
       </c>
       <c r="D118" s="3">
         <f t="shared" si="120"/>
-        <v>62</v>
+        <v>68</v>
       </c>
       <c r="E118" s="2">
         <f t="shared" si="4"/>
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="F118" s="2">
         <f t="shared" si="5"/>
@@ -3359,23 +3359,23 @@
       </c>
       <c r="B119" s="3">
         <f t="shared" ref="B119:D119" si="121">IF(RAND()&lt;0.2,"NA",RANDBETWEEN(60,80))</f>
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="C119" s="3">
         <f t="shared" si="121"/>
-        <v>61</v>
-      </c>
-      <c r="D119" s="3" t="str">
+        <v>68</v>
+      </c>
+      <c r="D119" s="3">
         <f t="shared" si="121"/>
-        <v>NA</v>
+        <v>70</v>
       </c>
       <c r="E119" s="2">
         <f t="shared" si="4"/>
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="F119" s="2">
         <f t="shared" si="5"/>
-        <v>2021</v>
+        <v>2020</v>
       </c>
     </row>
     <row r="120">
@@ -3383,21 +3383,21 @@
         <f t="shared" si="2"/>
         <v>119</v>
       </c>
-      <c r="B120" s="3">
+      <c r="B120" s="3" t="str">
         <f t="shared" ref="B120:D120" si="122">IF(RAND()&lt;0.2,"NA",RANDBETWEEN(60,80))</f>
-        <v>77</v>
+        <v>NA</v>
       </c>
       <c r="C120" s="3">
         <f t="shared" si="122"/>
-        <v>61</v>
-      </c>
-      <c r="D120" s="3">
+        <v>70</v>
+      </c>
+      <c r="D120" s="3" t="str">
         <f t="shared" si="122"/>
-        <v>68</v>
+        <v>NA</v>
       </c>
       <c r="E120" s="2">
         <f t="shared" si="4"/>
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="F120" s="2">
         <f t="shared" si="5"/>
@@ -3409,25 +3409,25 @@
         <f t="shared" si="2"/>
         <v>120</v>
       </c>
-      <c r="B121" s="3">
+      <c r="B121" s="3" t="str">
         <f t="shared" ref="B121:D121" si="123">IF(RAND()&lt;0.2,"NA",RANDBETWEEN(60,80))</f>
-        <v>63</v>
+        <v>NA</v>
       </c>
       <c r="C121" s="3">
         <f t="shared" si="123"/>
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="D121" s="3">
         <f t="shared" si="123"/>
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="E121" s="2">
         <f t="shared" si="4"/>
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="F121" s="2">
         <f t="shared" si="5"/>
-        <v>2019</v>
+        <v>2021</v>
       </c>
     </row>
     <row r="122">
@@ -3435,17 +3435,17 @@
         <f t="shared" si="2"/>
         <v>121</v>
       </c>
-      <c r="B122" s="3" t="str">
+      <c r="B122" s="3">
         <f t="shared" ref="B122:D122" si="124">IF(RAND()&lt;0.2,"NA",RANDBETWEEN(60,80))</f>
-        <v>NA</v>
+        <v>61</v>
       </c>
       <c r="C122" s="3">
         <f t="shared" si="124"/>
-        <v>62</v>
+        <v>73</v>
       </c>
       <c r="D122" s="3">
         <f t="shared" si="124"/>
-        <v>62</v>
+        <v>69</v>
       </c>
       <c r="E122" s="2">
         <f t="shared" si="4"/>
@@ -3453,7 +3453,7 @@
       </c>
       <c r="F122" s="2">
         <f t="shared" si="5"/>
-        <v>2018</v>
+        <v>2021</v>
       </c>
     </row>
     <row r="123">
@@ -3461,25 +3461,25 @@
         <f t="shared" si="2"/>
         <v>122</v>
       </c>
-      <c r="B123" s="3" t="str">
+      <c r="B123" s="3">
         <f t="shared" ref="B123:D123" si="125">IF(RAND()&lt;0.2,"NA",RANDBETWEEN(60,80))</f>
-        <v>NA</v>
+        <v>72</v>
       </c>
       <c r="C123" s="3">
         <f t="shared" si="125"/>
-        <v>73</v>
+        <v>61</v>
       </c>
       <c r="D123" s="3">
         <f t="shared" si="125"/>
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="E123" s="2">
         <f t="shared" si="4"/>
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="F123" s="2">
         <f t="shared" si="5"/>
-        <v>2021</v>
+        <v>2020</v>
       </c>
     </row>
     <row r="124">
@@ -3489,23 +3489,23 @@
       </c>
       <c r="B124" s="3">
         <f t="shared" ref="B124:D124" si="126">IF(RAND()&lt;0.2,"NA",RANDBETWEEN(60,80))</f>
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="C124" s="3">
         <f t="shared" si="126"/>
-        <v>79</v>
+        <v>67</v>
       </c>
       <c r="D124" s="3">
         <f t="shared" si="126"/>
-        <v>80</v>
+        <v>63</v>
       </c>
       <c r="E124" s="2">
         <f t="shared" si="4"/>
-        <v>90</v>
+        <v>75</v>
       </c>
       <c r="F124" s="2">
         <f t="shared" si="5"/>
-        <v>2019</v>
+        <v>2021</v>
       </c>
     </row>
     <row r="125">
@@ -3515,15 +3515,15 @@
       </c>
       <c r="B125" s="3">
         <f t="shared" ref="B125:D125" si="127">IF(RAND()&lt;0.2,"NA",RANDBETWEEN(60,80))</f>
-        <v>61</v>
+        <v>74</v>
       </c>
       <c r="C125" s="3">
         <f t="shared" si="127"/>
-        <v>74</v>
-      </c>
-      <c r="D125" s="3" t="str">
+        <v>71</v>
+      </c>
+      <c r="D125" s="3">
         <f t="shared" si="127"/>
-        <v>NA</v>
+        <v>78</v>
       </c>
       <c r="E125" s="2">
         <f t="shared" si="4"/>
@@ -3531,7 +3531,7 @@
       </c>
       <c r="F125" s="2">
         <f t="shared" si="5"/>
-        <v>2021</v>
+        <v>2018</v>
       </c>
     </row>
     <row r="126">
@@ -3541,23 +3541,23 @@
       </c>
       <c r="B126" s="3">
         <f t="shared" ref="B126:D126" si="128">IF(RAND()&lt;0.2,"NA",RANDBETWEEN(60,80))</f>
-        <v>79</v>
+        <v>69</v>
       </c>
       <c r="C126" s="3">
         <f t="shared" si="128"/>
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="D126" s="3">
         <f t="shared" si="128"/>
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="E126" s="2">
         <f t="shared" si="4"/>
-        <v>83</v>
+        <v>89</v>
       </c>
       <c r="F126" s="2">
         <f t="shared" si="5"/>
-        <v>2019</v>
+        <v>2018</v>
       </c>
     </row>
     <row r="127">
@@ -3567,23 +3567,23 @@
       </c>
       <c r="B127" s="3">
         <f t="shared" ref="B127:D127" si="129">IF(RAND()&lt;0.2,"NA",RANDBETWEEN(60,80))</f>
-        <v>78</v>
-      </c>
-      <c r="C127" s="3" t="str">
+        <v>60</v>
+      </c>
+      <c r="C127" s="3">
         <f t="shared" si="129"/>
-        <v>NA</v>
+        <v>80</v>
       </c>
       <c r="D127" s="3">
         <f t="shared" si="129"/>
-        <v>71</v>
+        <v>60</v>
       </c>
       <c r="E127" s="2">
         <f t="shared" si="4"/>
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="F127" s="2">
         <f t="shared" si="5"/>
-        <v>2019</v>
+        <v>2020</v>
       </c>
     </row>
     <row r="128">
@@ -3591,21 +3591,21 @@
         <f t="shared" si="2"/>
         <v>127</v>
       </c>
-      <c r="B128" s="3" t="str">
+      <c r="B128" s="3">
         <f t="shared" ref="B128:D128" si="130">IF(RAND()&lt;0.2,"NA",RANDBETWEEN(60,80))</f>
-        <v>NA</v>
+        <v>77</v>
       </c>
       <c r="C128" s="3">
         <f t="shared" si="130"/>
-        <v>71</v>
-      </c>
-      <c r="D128" s="3" t="str">
+        <v>64</v>
+      </c>
+      <c r="D128" s="3">
         <f t="shared" si="130"/>
-        <v>NA</v>
+        <v>73</v>
       </c>
       <c r="E128" s="2">
         <f t="shared" si="4"/>
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="F128" s="2">
         <f t="shared" si="5"/>
@@ -3621,21 +3621,21 @@
         <f t="shared" ref="B129:D129" si="131">IF(RAND()&lt;0.2,"NA",RANDBETWEEN(60,80))</f>
         <v>NA</v>
       </c>
-      <c r="C129" s="3" t="str">
+      <c r="C129" s="3">
         <f t="shared" si="131"/>
-        <v>NA</v>
-      </c>
-      <c r="D129" s="3">
+        <v>68</v>
+      </c>
+      <c r="D129" s="3" t="str">
         <f t="shared" si="131"/>
-        <v>71</v>
+        <v>NA</v>
       </c>
       <c r="E129" s="2">
         <f t="shared" si="4"/>
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="F129" s="2">
         <f t="shared" si="5"/>
-        <v>2019</v>
+        <v>2020</v>
       </c>
     </row>
     <row r="130">
@@ -3645,23 +3645,23 @@
       </c>
       <c r="B130" s="3">
         <f t="shared" ref="B130:D130" si="132">IF(RAND()&lt;0.2,"NA",RANDBETWEEN(60,80))</f>
-        <v>66</v>
+        <v>75</v>
       </c>
       <c r="C130" s="3">
         <f t="shared" si="132"/>
-        <v>69</v>
+        <v>79</v>
       </c>
       <c r="D130" s="3">
         <f t="shared" si="132"/>
-        <v>79</v>
+        <v>67</v>
       </c>
       <c r="E130" s="2">
         <f t="shared" si="4"/>
-        <v>83</v>
+        <v>90</v>
       </c>
       <c r="F130" s="2">
         <f t="shared" si="5"/>
-        <v>2019</v>
+        <v>2020</v>
       </c>
     </row>
     <row r="131">
@@ -3671,23 +3671,23 @@
       </c>
       <c r="B131" s="3">
         <f t="shared" ref="B131:D131" si="133">IF(RAND()&lt;0.2,"NA",RANDBETWEEN(60,80))</f>
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="C131" s="3">
         <f t="shared" si="133"/>
-        <v>80</v>
-      </c>
-      <c r="D131" s="3">
+        <v>63</v>
+      </c>
+      <c r="D131" s="3" t="str">
         <f t="shared" si="133"/>
-        <v>76</v>
+        <v>NA</v>
       </c>
       <c r="E131" s="2">
         <f t="shared" si="4"/>
-        <v>75</v>
+        <v>88</v>
       </c>
       <c r="F131" s="2">
         <f t="shared" si="5"/>
-        <v>2021</v>
+        <v>2018</v>
       </c>
     </row>
     <row r="132">
@@ -3695,9 +3695,9 @@
         <f t="shared" si="2"/>
         <v>131</v>
       </c>
-      <c r="B132" s="3">
+      <c r="B132" s="3" t="str">
         <f t="shared" ref="B132:D132" si="134">IF(RAND()&lt;0.2,"NA",RANDBETWEEN(60,80))</f>
-        <v>77</v>
+        <v>NA</v>
       </c>
       <c r="C132" s="3" t="str">
         <f t="shared" si="134"/>
@@ -3705,11 +3705,11 @@
       </c>
       <c r="D132" s="3">
         <f t="shared" si="134"/>
-        <v>67</v>
+        <v>80</v>
       </c>
       <c r="E132" s="2">
         <f t="shared" si="4"/>
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="F132" s="2">
         <f t="shared" si="5"/>
@@ -3729,13 +3729,13 @@
         <f t="shared" si="135"/>
         <v>71</v>
       </c>
-      <c r="D133" s="3" t="str">
+      <c r="D133" s="3">
         <f t="shared" si="135"/>
-        <v>NA</v>
+        <v>72</v>
       </c>
       <c r="E133" s="2">
         <f t="shared" si="4"/>
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="F133" s="2">
         <f t="shared" si="5"/>
@@ -3749,23 +3749,23 @@
       </c>
       <c r="B134" s="3">
         <f t="shared" ref="B134:D134" si="136">IF(RAND()&lt;0.2,"NA",RANDBETWEEN(60,80))</f>
-        <v>78</v>
-      </c>
-      <c r="C134" s="3">
+        <v>70</v>
+      </c>
+      <c r="C134" s="3" t="str">
         <f t="shared" si="136"/>
-        <v>67</v>
-      </c>
-      <c r="D134" s="3">
+        <v>NA</v>
+      </c>
+      <c r="D134" s="3" t="str">
         <f t="shared" si="136"/>
-        <v>75</v>
+        <v>NA</v>
       </c>
       <c r="E134" s="2">
         <f t="shared" si="4"/>
-        <v>90</v>
+        <v>77</v>
       </c>
       <c r="F134" s="2">
         <f t="shared" si="5"/>
-        <v>2020</v>
+        <v>2019</v>
       </c>
     </row>
     <row r="135">
@@ -3775,19 +3775,19 @@
       </c>
       <c r="B135" s="3">
         <f t="shared" ref="B135:D135" si="137">IF(RAND()&lt;0.2,"NA",RANDBETWEEN(60,80))</f>
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C135" s="3">
         <f t="shared" si="137"/>
-        <v>74</v>
+        <v>63</v>
       </c>
       <c r="D135" s="3">
         <f t="shared" si="137"/>
-        <v>62</v>
+        <v>73</v>
       </c>
       <c r="E135" s="2">
         <f t="shared" si="4"/>
-        <v>90</v>
+        <v>83</v>
       </c>
       <c r="F135" s="2">
         <f t="shared" si="5"/>
@@ -3801,15 +3801,15 @@
       </c>
       <c r="B136" s="3">
         <f t="shared" ref="B136:D136" si="138">IF(RAND()&lt;0.2,"NA",RANDBETWEEN(60,80))</f>
-        <v>71</v>
+        <v>79</v>
       </c>
       <c r="C136" s="3">
         <f t="shared" si="138"/>
-        <v>77</v>
-      </c>
-      <c r="D136" s="3" t="str">
+        <v>66</v>
+      </c>
+      <c r="D136" s="3">
         <f t="shared" si="138"/>
-        <v>NA</v>
+        <v>68</v>
       </c>
       <c r="E136" s="2">
         <f t="shared" si="4"/>
@@ -3817,7 +3817,7 @@
       </c>
       <c r="F136" s="2">
         <f t="shared" si="5"/>
-        <v>2018</v>
+        <v>2021</v>
       </c>
     </row>
     <row r="137">
@@ -3827,23 +3827,23 @@
       </c>
       <c r="B137" s="3">
         <f t="shared" ref="B137:D137" si="139">IF(RAND()&lt;0.2,"NA",RANDBETWEEN(60,80))</f>
-        <v>66</v>
+        <v>77</v>
       </c>
       <c r="C137" s="3">
         <f t="shared" si="139"/>
-        <v>78</v>
+        <v>63</v>
       </c>
       <c r="D137" s="3">
         <f t="shared" si="139"/>
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="E137" s="2">
         <f t="shared" si="4"/>
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="F137" s="2">
         <f t="shared" si="5"/>
-        <v>2020</v>
+        <v>2018</v>
       </c>
     </row>
     <row r="138">
@@ -3853,23 +3853,23 @@
       </c>
       <c r="B138" s="3">
         <f t="shared" ref="B138:D138" si="140">IF(RAND()&lt;0.2,"NA",RANDBETWEEN(60,80))</f>
-        <v>70</v>
-      </c>
-      <c r="C138" s="3" t="str">
+        <v>75</v>
+      </c>
+      <c r="C138" s="3">
         <f t="shared" si="140"/>
-        <v>NA</v>
+        <v>76</v>
       </c>
       <c r="D138" s="3">
         <f t="shared" si="140"/>
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="E138" s="2">
         <f t="shared" si="4"/>
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="F138" s="2">
         <f t="shared" si="5"/>
-        <v>2021</v>
+        <v>2018</v>
       </c>
     </row>
     <row r="139">
@@ -3877,25 +3877,25 @@
         <f t="shared" si="2"/>
         <v>138</v>
       </c>
-      <c r="B139" s="3" t="str">
+      <c r="B139" s="3">
         <f t="shared" ref="B139:D139" si="141">IF(RAND()&lt;0.2,"NA",RANDBETWEEN(60,80))</f>
-        <v>NA</v>
+        <v>71</v>
       </c>
       <c r="C139" s="3">
         <f t="shared" si="141"/>
-        <v>70</v>
-      </c>
-      <c r="D139" s="3">
+        <v>60</v>
+      </c>
+      <c r="D139" s="3" t="str">
         <f t="shared" si="141"/>
-        <v>69</v>
+        <v>NA</v>
       </c>
       <c r="E139" s="2">
         <f t="shared" si="4"/>
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="F139" s="2">
         <f t="shared" si="5"/>
-        <v>2020</v>
+        <v>2021</v>
       </c>
     </row>
   </sheetData>

--- a/DSBDAL/Assignment2/CreatedData.xlsx
+++ b/DSBDAL/Assignment2/CreatedData.xlsx
@@ -317,23 +317,23 @@
       </c>
       <c r="B2" s="3">
         <f t="shared" ref="B2:D2" si="1">IF(RAND()&lt;0.2,"NA",RANDBETWEEN(60,80))</f>
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="C2" s="3">
         <f t="shared" si="1"/>
-        <v>61</v>
-      </c>
-      <c r="D2" s="3">
+        <v>80</v>
+      </c>
+      <c r="D2" s="3" t="str">
         <f t="shared" si="1"/>
-        <v>74</v>
+        <v>NA</v>
       </c>
       <c r="E2" s="2">
         <f t="shared" ref="E2:E139" si="4">IF(RAND()&lt;0.05,CHOOSE(RANDBETWEEN(1,2),500,5),RANDBETWEEN(75,90))</f>
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="F2" s="2">
         <f t="shared" ref="F2:F139" si="5">RANDBETWEEN(2018,2021)</f>
-        <v>2019</v>
+        <v>2018</v>
       </c>
     </row>
     <row r="3">
@@ -343,23 +343,23 @@
       </c>
       <c r="B3" s="3">
         <f t="shared" ref="B3:D3" si="3">IF(RAND()&lt;0.2,"NA",RANDBETWEEN(60,80))</f>
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="C3" s="3">
         <f t="shared" si="3"/>
-        <v>73</v>
-      </c>
-      <c r="D3" s="3" t="str">
+        <v>61</v>
+      </c>
+      <c r="D3" s="3">
         <f t="shared" si="3"/>
-        <v>NA</v>
+        <v>63</v>
       </c>
       <c r="E3" s="2">
         <f t="shared" si="4"/>
-        <v>87</v>
+        <v>77</v>
       </c>
       <c r="F3" s="2">
         <f t="shared" si="5"/>
-        <v>2021</v>
+        <v>2019</v>
       </c>
     </row>
     <row r="4">
@@ -367,9 +367,9 @@
         <f t="shared" si="2"/>
         <v>3</v>
       </c>
-      <c r="B4" s="3">
+      <c r="B4" s="3" t="str">
         <f t="shared" ref="B4:D4" si="6">IF(RAND()&lt;0.2,"NA",RANDBETWEEN(60,80))</f>
-        <v>71</v>
+        <v>NA</v>
       </c>
       <c r="C4" s="3" t="str">
         <f t="shared" si="6"/>
@@ -377,15 +377,15 @@
       </c>
       <c r="D4" s="3">
         <f t="shared" si="6"/>
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="E4" s="2">
         <f t="shared" si="4"/>
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="F4" s="2">
         <f t="shared" si="5"/>
-        <v>2020</v>
+        <v>2021</v>
       </c>
     </row>
     <row r="5">
@@ -393,25 +393,25 @@
         <f t="shared" si="2"/>
         <v>4</v>
       </c>
-      <c r="B5" s="3">
+      <c r="B5" s="3" t="str">
         <f t="shared" ref="B5:D5" si="7">IF(RAND()&lt;0.2,"NA",RANDBETWEEN(60,80))</f>
-        <v>79</v>
+        <v>NA</v>
       </c>
       <c r="C5" s="3">
         <f t="shared" si="7"/>
-        <v>78</v>
+        <v>62</v>
       </c>
       <c r="D5" s="3">
         <f t="shared" si="7"/>
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="E5" s="2">
         <f t="shared" si="4"/>
-        <v>90</v>
+        <v>76</v>
       </c>
       <c r="F5" s="2">
         <f t="shared" si="5"/>
-        <v>2019</v>
+        <v>2018</v>
       </c>
     </row>
     <row r="6">
@@ -421,23 +421,23 @@
       </c>
       <c r="B6" s="3">
         <f t="shared" ref="B6:D6" si="8">IF(RAND()&lt;0.2,"NA",RANDBETWEEN(60,80))</f>
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C6" s="3">
         <f t="shared" si="8"/>
-        <v>64</v>
-      </c>
-      <c r="D6" s="3" t="str">
+        <v>66</v>
+      </c>
+      <c r="D6" s="3">
         <f t="shared" si="8"/>
-        <v>NA</v>
+        <v>67</v>
       </c>
       <c r="E6" s="2">
         <f t="shared" si="4"/>
-        <v>80</v>
+        <v>87</v>
       </c>
       <c r="F6" s="2">
         <f t="shared" si="5"/>
-        <v>2021</v>
+        <v>2018</v>
       </c>
     </row>
     <row r="7">
@@ -447,23 +447,23 @@
       </c>
       <c r="B7" s="3">
         <f t="shared" ref="B7:D7" si="9">IF(RAND()&lt;0.2,"NA",RANDBETWEEN(60,80))</f>
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="C7" s="3">
         <f t="shared" si="9"/>
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="D7" s="3">
         <f t="shared" si="9"/>
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="E7" s="2">
         <f t="shared" si="4"/>
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="F7" s="2">
         <f t="shared" si="5"/>
-        <v>2018</v>
+        <v>2021</v>
       </c>
     </row>
     <row r="8">
@@ -471,9 +471,9 @@
         <f t="shared" si="2"/>
         <v>7</v>
       </c>
-      <c r="B8" s="3">
+      <c r="B8" s="3" t="str">
         <f t="shared" ref="B8:D8" si="10">IF(RAND()&lt;0.2,"NA",RANDBETWEEN(60,80))</f>
-        <v>78</v>
+        <v>NA</v>
       </c>
       <c r="C8" s="3">
         <f t="shared" si="10"/>
@@ -481,15 +481,15 @@
       </c>
       <c r="D8" s="3">
         <f t="shared" si="10"/>
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E8" s="2">
         <f t="shared" si="4"/>
-        <v>88</v>
+        <v>76</v>
       </c>
       <c r="F8" s="2">
         <f t="shared" si="5"/>
-        <v>2020</v>
+        <v>2019</v>
       </c>
     </row>
     <row r="9">
@@ -497,21 +497,21 @@
         <f t="shared" si="2"/>
         <v>8</v>
       </c>
-      <c r="B9" s="3" t="str">
+      <c r="B9" s="3">
         <f t="shared" ref="B9:D9" si="11">IF(RAND()&lt;0.2,"NA",RANDBETWEEN(60,80))</f>
-        <v>NA</v>
-      </c>
-      <c r="C9" s="3">
+        <v>69</v>
+      </c>
+      <c r="C9" s="3" t="str">
         <f t="shared" si="11"/>
-        <v>67</v>
+        <v>NA</v>
       </c>
       <c r="D9" s="3">
         <f t="shared" si="11"/>
-        <v>62</v>
+        <v>77</v>
       </c>
       <c r="E9" s="2">
         <f t="shared" si="4"/>
-        <v>88</v>
+        <v>76</v>
       </c>
       <c r="F9" s="2">
         <f t="shared" si="5"/>
@@ -525,11 +525,11 @@
       </c>
       <c r="B10" s="3">
         <f t="shared" ref="B10:D10" si="12">IF(RAND()&lt;0.2,"NA",RANDBETWEEN(60,80))</f>
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="C10" s="3">
         <f t="shared" si="12"/>
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="D10" s="3" t="str">
         <f t="shared" si="12"/>
@@ -537,11 +537,11 @@
       </c>
       <c r="E10" s="2">
         <f t="shared" si="4"/>
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="F10" s="2">
         <f t="shared" si="5"/>
-        <v>2018</v>
+        <v>2021</v>
       </c>
     </row>
     <row r="11">
@@ -549,25 +549,25 @@
         <f t="shared" si="2"/>
         <v>10</v>
       </c>
-      <c r="B11" s="3" t="str">
+      <c r="B11" s="3">
         <f t="shared" ref="B11:D11" si="13">IF(RAND()&lt;0.2,"NA",RANDBETWEEN(60,80))</f>
-        <v>NA</v>
+        <v>63</v>
       </c>
       <c r="C11" s="3">
         <f t="shared" si="13"/>
-        <v>62</v>
-      </c>
-      <c r="D11" s="3" t="str">
+        <v>80</v>
+      </c>
+      <c r="D11" s="3">
         <f t="shared" si="13"/>
-        <v>NA</v>
+        <v>76</v>
       </c>
       <c r="E11" s="2">
         <f t="shared" si="4"/>
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="F11" s="2">
         <f t="shared" si="5"/>
-        <v>2018</v>
+        <v>2020</v>
       </c>
     </row>
     <row r="12">
@@ -577,23 +577,23 @@
       </c>
       <c r="B12" s="3">
         <f t="shared" ref="B12:D12" si="14">IF(RAND()&lt;0.2,"NA",RANDBETWEEN(60,80))</f>
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="C12" s="3">
         <f t="shared" si="14"/>
-        <v>63</v>
-      </c>
-      <c r="D12" s="3" t="str">
+        <v>77</v>
+      </c>
+      <c r="D12" s="3">
         <f t="shared" si="14"/>
-        <v>NA</v>
+        <v>69</v>
       </c>
       <c r="E12" s="2">
         <f t="shared" si="4"/>
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="F12" s="2">
         <f t="shared" si="5"/>
-        <v>2021</v>
+        <v>2018</v>
       </c>
     </row>
     <row r="13">
@@ -603,23 +603,23 @@
       </c>
       <c r="B13" s="3">
         <f t="shared" ref="B13:D13" si="15">IF(RAND()&lt;0.2,"NA",RANDBETWEEN(60,80))</f>
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="C13" s="3">
         <f t="shared" si="15"/>
-        <v>68</v>
-      </c>
-      <c r="D13" s="3">
+        <v>77</v>
+      </c>
+      <c r="D13" s="3" t="str">
         <f t="shared" si="15"/>
-        <v>79</v>
+        <v>NA</v>
       </c>
       <c r="E13" s="2">
         <f t="shared" si="4"/>
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="F13" s="2">
         <f t="shared" si="5"/>
-        <v>2020</v>
+        <v>2018</v>
       </c>
     </row>
     <row r="14">
@@ -629,11 +629,11 @@
       </c>
       <c r="B14" s="3">
         <f t="shared" ref="B14:D14" si="16">IF(RAND()&lt;0.2,"NA",RANDBETWEEN(60,80))</f>
-        <v>70</v>
+        <v>61</v>
       </c>
       <c r="C14" s="3">
         <f t="shared" si="16"/>
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="D14" s="3">
         <f t="shared" si="16"/>
@@ -641,11 +641,11 @@
       </c>
       <c r="E14" s="2">
         <f t="shared" si="4"/>
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="F14" s="2">
         <f t="shared" si="5"/>
-        <v>2021</v>
+        <v>2020</v>
       </c>
     </row>
     <row r="15">
@@ -655,23 +655,23 @@
       </c>
       <c r="B15" s="3">
         <f t="shared" ref="B15:D15" si="17">IF(RAND()&lt;0.2,"NA",RANDBETWEEN(60,80))</f>
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="C15" s="3">
         <f t="shared" si="17"/>
-        <v>66</v>
+        <v>79</v>
       </c>
       <c r="D15" s="3">
         <f t="shared" si="17"/>
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="E15" s="2">
         <f t="shared" si="4"/>
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="F15" s="2">
         <f t="shared" si="5"/>
-        <v>2020</v>
+        <v>2019</v>
       </c>
     </row>
     <row r="16">
@@ -681,23 +681,23 @@
       </c>
       <c r="B16" s="3">
         <f t="shared" ref="B16:D16" si="18">IF(RAND()&lt;0.2,"NA",RANDBETWEEN(60,80))</f>
-        <v>62</v>
+        <v>74</v>
       </c>
       <c r="C16" s="3">
         <f t="shared" si="18"/>
-        <v>73</v>
+        <v>66</v>
       </c>
       <c r="D16" s="3">
         <f t="shared" si="18"/>
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E16" s="2">
         <f t="shared" si="4"/>
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="F16" s="2">
         <f t="shared" si="5"/>
-        <v>2018</v>
+        <v>2019</v>
       </c>
     </row>
     <row r="17">
@@ -707,7 +707,7 @@
       </c>
       <c r="B17" s="3">
         <f t="shared" ref="B17:D17" si="19">IF(RAND()&lt;0.2,"NA",RANDBETWEEN(60,80))</f>
-        <v>75</v>
+        <v>63</v>
       </c>
       <c r="C17" s="3" t="str">
         <f t="shared" si="19"/>
@@ -715,15 +715,15 @@
       </c>
       <c r="D17" s="3">
         <f t="shared" si="19"/>
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="E17" s="2">
         <f t="shared" si="4"/>
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="F17" s="2">
         <f t="shared" si="5"/>
-        <v>2020</v>
+        <v>2018</v>
       </c>
     </row>
     <row r="18">
@@ -733,19 +733,19 @@
       </c>
       <c r="B18" s="3">
         <f t="shared" ref="B18:D18" si="20">IF(RAND()&lt;0.2,"NA",RANDBETWEEN(60,80))</f>
-        <v>63</v>
-      </c>
-      <c r="C18" s="3" t="str">
+        <v>80</v>
+      </c>
+      <c r="C18" s="3">
         <f t="shared" si="20"/>
-        <v>NA</v>
+        <v>61</v>
       </c>
       <c r="D18" s="3">
         <f t="shared" si="20"/>
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="E18" s="2">
         <f t="shared" si="4"/>
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="F18" s="2">
         <f t="shared" si="5"/>
@@ -759,7 +759,7 @@
       </c>
       <c r="B19" s="3">
         <f t="shared" ref="B19:D19" si="21">IF(RAND()&lt;0.2,"NA",RANDBETWEEN(60,80))</f>
-        <v>76</v>
+        <v>62</v>
       </c>
       <c r="C19" s="3" t="str">
         <f t="shared" si="21"/>
@@ -767,15 +767,15 @@
       </c>
       <c r="D19" s="3">
         <f t="shared" si="21"/>
-        <v>80</v>
+        <v>62</v>
       </c>
       <c r="E19" s="2">
         <f t="shared" si="4"/>
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="F19" s="2">
         <f t="shared" si="5"/>
-        <v>2018</v>
+        <v>2021</v>
       </c>
     </row>
     <row r="20">
@@ -785,23 +785,23 @@
       </c>
       <c r="B20" s="3">
         <f t="shared" ref="B20:D20" si="22">IF(RAND()&lt;0.2,"NA",RANDBETWEEN(60,80))</f>
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="C20" s="3">
         <f t="shared" si="22"/>
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="D20" s="3">
         <f t="shared" si="22"/>
-        <v>62</v>
+        <v>78</v>
       </c>
       <c r="E20" s="2">
         <f t="shared" si="4"/>
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="F20" s="2">
         <f t="shared" si="5"/>
-        <v>2019</v>
+        <v>2018</v>
       </c>
     </row>
     <row r="21">
@@ -809,13 +809,13 @@
         <f t="shared" si="2"/>
         <v>20</v>
       </c>
-      <c r="B21" s="3" t="str">
+      <c r="B21" s="3">
         <f t="shared" ref="B21:D21" si="23">IF(RAND()&lt;0.2,"NA",RANDBETWEEN(60,80))</f>
-        <v>NA</v>
-      </c>
-      <c r="C21" s="3">
+        <v>61</v>
+      </c>
+      <c r="C21" s="3" t="str">
         <f t="shared" si="23"/>
-        <v>77</v>
+        <v>NA</v>
       </c>
       <c r="D21" s="3">
         <f t="shared" si="23"/>
@@ -823,7 +823,7 @@
       </c>
       <c r="E21" s="2">
         <f t="shared" si="4"/>
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="F21" s="2">
         <f t="shared" si="5"/>
@@ -837,15 +837,15 @@
       </c>
       <c r="B22" s="3">
         <f t="shared" ref="B22:D22" si="24">IF(RAND()&lt;0.2,"NA",RANDBETWEEN(60,80))</f>
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="C22" s="3">
         <f t="shared" si="24"/>
-        <v>67</v>
-      </c>
-      <c r="D22" s="3">
+        <v>80</v>
+      </c>
+      <c r="D22" s="3" t="str">
         <f t="shared" si="24"/>
-        <v>60</v>
+        <v>NA</v>
       </c>
       <c r="E22" s="2">
         <f t="shared" si="4"/>
@@ -853,7 +853,7 @@
       </c>
       <c r="F22" s="2">
         <f t="shared" si="5"/>
-        <v>2021</v>
+        <v>2019</v>
       </c>
     </row>
     <row r="23">
@@ -867,19 +867,19 @@
       </c>
       <c r="C23" s="3">
         <f t="shared" si="25"/>
-        <v>80</v>
-      </c>
-      <c r="D23" s="3" t="str">
+        <v>71</v>
+      </c>
+      <c r="D23" s="3">
         <f t="shared" si="25"/>
-        <v>NA</v>
+        <v>78</v>
       </c>
       <c r="E23" s="2">
         <f t="shared" si="4"/>
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="F23" s="2">
         <f t="shared" si="5"/>
-        <v>2020</v>
+        <v>2021</v>
       </c>
     </row>
     <row r="24">
@@ -889,11 +889,11 @@
       </c>
       <c r="B24" s="3">
         <f t="shared" ref="B24:D24" si="26">IF(RAND()&lt;0.2,"NA",RANDBETWEEN(60,80))</f>
-        <v>63</v>
-      </c>
-      <c r="C24" s="3">
+        <v>64</v>
+      </c>
+      <c r="C24" s="3" t="str">
         <f t="shared" si="26"/>
-        <v>67</v>
+        <v>NA</v>
       </c>
       <c r="D24" s="3" t="str">
         <f t="shared" si="26"/>
@@ -901,7 +901,7 @@
       </c>
       <c r="E24" s="2">
         <f t="shared" si="4"/>
-        <v>82</v>
+        <v>5</v>
       </c>
       <c r="F24" s="2">
         <f t="shared" si="5"/>
@@ -913,25 +913,25 @@
         <f t="shared" si="2"/>
         <v>24</v>
       </c>
-      <c r="B25" s="3">
+      <c r="B25" s="3" t="str">
         <f t="shared" ref="B25:D25" si="27">IF(RAND()&lt;0.2,"NA",RANDBETWEEN(60,80))</f>
-        <v>73</v>
+        <v>NA</v>
       </c>
       <c r="C25" s="3">
         <f t="shared" si="27"/>
-        <v>71</v>
+        <v>62</v>
       </c>
       <c r="D25" s="3">
         <f t="shared" si="27"/>
-        <v>62</v>
+        <v>72</v>
       </c>
       <c r="E25" s="2">
         <f t="shared" si="4"/>
-        <v>76</v>
+        <v>87</v>
       </c>
       <c r="F25" s="2">
         <f t="shared" si="5"/>
-        <v>2018</v>
+        <v>2021</v>
       </c>
     </row>
     <row r="26">
@@ -939,13 +939,13 @@
         <f t="shared" si="2"/>
         <v>25</v>
       </c>
-      <c r="B26" s="3" t="str">
+      <c r="B26" s="3">
         <f t="shared" ref="B26:D26" si="28">IF(RAND()&lt;0.2,"NA",RANDBETWEEN(60,80))</f>
-        <v>NA</v>
+        <v>62</v>
       </c>
       <c r="C26" s="3">
         <f t="shared" si="28"/>
-        <v>69</v>
+        <v>62</v>
       </c>
       <c r="D26" s="3" t="str">
         <f t="shared" si="28"/>
@@ -953,11 +953,11 @@
       </c>
       <c r="E26" s="2">
         <f t="shared" si="4"/>
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="F26" s="2">
         <f t="shared" si="5"/>
-        <v>2018</v>
+        <v>2020</v>
       </c>
     </row>
     <row r="27">
@@ -967,23 +967,23 @@
       </c>
       <c r="B27" s="3">
         <f t="shared" ref="B27:D27" si="29">IF(RAND()&lt;0.2,"NA",RANDBETWEEN(60,80))</f>
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="C27" s="3">
         <f t="shared" si="29"/>
-        <v>65</v>
+        <v>80</v>
       </c>
       <c r="D27" s="3">
         <f t="shared" si="29"/>
-        <v>79</v>
+        <v>62</v>
       </c>
       <c r="E27" s="2">
         <f t="shared" si="4"/>
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="F27" s="2">
         <f t="shared" si="5"/>
-        <v>2021</v>
+        <v>2019</v>
       </c>
     </row>
     <row r="28">
@@ -991,9 +991,9 @@
         <f t="shared" si="2"/>
         <v>27</v>
       </c>
-      <c r="B28" s="3" t="str">
+      <c r="B28" s="3">
         <f t="shared" ref="B28:D28" si="30">IF(RAND()&lt;0.2,"NA",RANDBETWEEN(60,80))</f>
-        <v>NA</v>
+        <v>65</v>
       </c>
       <c r="C28" s="3" t="str">
         <f t="shared" si="30"/>
@@ -1001,15 +1001,15 @@
       </c>
       <c r="D28" s="3">
         <f t="shared" si="30"/>
-        <v>66</v>
+        <v>79</v>
       </c>
       <c r="E28" s="2">
         <f t="shared" si="4"/>
-        <v>75</v>
+        <v>500</v>
       </c>
       <c r="F28" s="2">
         <f t="shared" si="5"/>
-        <v>2019</v>
+        <v>2020</v>
       </c>
     </row>
     <row r="29">
@@ -1019,23 +1019,23 @@
       </c>
       <c r="B29" s="3">
         <f t="shared" ref="B29:D29" si="31">IF(RAND()&lt;0.2,"NA",RANDBETWEEN(60,80))</f>
-        <v>71</v>
+        <v>80</v>
       </c>
       <c r="C29" s="3">
         <f t="shared" si="31"/>
         <v>68</v>
       </c>
-      <c r="D29" s="3" t="str">
+      <c r="D29" s="3">
         <f t="shared" si="31"/>
-        <v>NA</v>
+        <v>77</v>
       </c>
       <c r="E29" s="2">
         <f t="shared" si="4"/>
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="F29" s="2">
         <f t="shared" si="5"/>
-        <v>2020</v>
+        <v>2018</v>
       </c>
     </row>
     <row r="30">
@@ -1045,23 +1045,23 @@
       </c>
       <c r="B30" s="3">
         <f t="shared" ref="B30:D30" si="32">IF(RAND()&lt;0.2,"NA",RANDBETWEEN(60,80))</f>
-        <v>75</v>
+        <v>60</v>
       </c>
       <c r="C30" s="3">
         <f t="shared" si="32"/>
-        <v>68</v>
-      </c>
-      <c r="D30" s="3">
+        <v>75</v>
+      </c>
+      <c r="D30" s="3" t="str">
         <f t="shared" si="32"/>
-        <v>63</v>
+        <v>NA</v>
       </c>
       <c r="E30" s="2">
         <f t="shared" si="4"/>
-        <v>88</v>
+        <v>76</v>
       </c>
       <c r="F30" s="2">
         <f t="shared" si="5"/>
-        <v>2020</v>
+        <v>2019</v>
       </c>
     </row>
     <row r="31">
@@ -1069,25 +1069,25 @@
         <f t="shared" si="2"/>
         <v>30</v>
       </c>
-      <c r="B31" s="3" t="str">
+      <c r="B31" s="3">
         <f t="shared" ref="B31:D31" si="33">IF(RAND()&lt;0.2,"NA",RANDBETWEEN(60,80))</f>
-        <v>NA</v>
-      </c>
-      <c r="C31" s="3" t="str">
+        <v>75</v>
+      </c>
+      <c r="C31" s="3">
         <f t="shared" si="33"/>
-        <v>NA</v>
+        <v>66</v>
       </c>
       <c r="D31" s="3">
         <f t="shared" si="33"/>
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="E31" s="2">
         <f t="shared" si="4"/>
-        <v>86</v>
+        <v>80</v>
       </c>
       <c r="F31" s="2">
         <f t="shared" si="5"/>
-        <v>2021</v>
+        <v>2020</v>
       </c>
     </row>
     <row r="32">
@@ -1095,21 +1095,21 @@
         <f t="shared" si="2"/>
         <v>31</v>
       </c>
-      <c r="B32" s="3" t="str">
+      <c r="B32" s="3">
         <f t="shared" ref="B32:D32" si="34">IF(RAND()&lt;0.2,"NA",RANDBETWEEN(60,80))</f>
-        <v>NA</v>
-      </c>
-      <c r="C32" s="3">
+        <v>70</v>
+      </c>
+      <c r="C32" s="3" t="str">
         <f t="shared" si="34"/>
-        <v>72</v>
+        <v>NA</v>
       </c>
       <c r="D32" s="3">
         <f t="shared" si="34"/>
-        <v>61</v>
+        <v>80</v>
       </c>
       <c r="E32" s="2">
         <f t="shared" si="4"/>
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="F32" s="2">
         <f t="shared" si="5"/>
@@ -1123,7 +1123,7 @@
       </c>
       <c r="B33" s="3">
         <f t="shared" ref="B33:D33" si="35">IF(RAND()&lt;0.2,"NA",RANDBETWEEN(60,80))</f>
-        <v>69</v>
+        <v>80</v>
       </c>
       <c r="C33" s="3">
         <f t="shared" si="35"/>
@@ -1131,15 +1131,15 @@
       </c>
       <c r="D33" s="3">
         <f t="shared" si="35"/>
-        <v>77</v>
+        <v>65</v>
       </c>
       <c r="E33" s="2">
         <f t="shared" si="4"/>
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="F33" s="2">
         <f t="shared" si="5"/>
-        <v>2021</v>
+        <v>2020</v>
       </c>
     </row>
     <row r="34">
@@ -1149,7 +1149,7 @@
       </c>
       <c r="B34" s="3">
         <f t="shared" ref="B34:D34" si="36">IF(RAND()&lt;0.2,"NA",RANDBETWEEN(60,80))</f>
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="C34" s="3" t="str">
         <f t="shared" si="36"/>
@@ -1157,11 +1157,11 @@
       </c>
       <c r="D34" s="3">
         <f t="shared" si="36"/>
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="E34" s="2">
         <f t="shared" si="4"/>
-        <v>5</v>
+        <v>78</v>
       </c>
       <c r="F34" s="2">
         <f t="shared" si="5"/>
@@ -1173,21 +1173,21 @@
         <f t="shared" si="2"/>
         <v>34</v>
       </c>
-      <c r="B35" s="3" t="str">
+      <c r="B35" s="3">
         <f t="shared" ref="B35:D35" si="37">IF(RAND()&lt;0.2,"NA",RANDBETWEEN(60,80))</f>
-        <v>NA</v>
+        <v>77</v>
       </c>
       <c r="C35" s="3">
         <f t="shared" si="37"/>
-        <v>80</v>
+        <v>74</v>
       </c>
       <c r="D35" s="3">
         <f t="shared" si="37"/>
-        <v>79</v>
+        <v>67</v>
       </c>
       <c r="E35" s="2">
         <f t="shared" si="4"/>
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="F35" s="2">
         <f t="shared" si="5"/>
@@ -1201,19 +1201,19 @@
       </c>
       <c r="B36" s="3">
         <f t="shared" ref="B36:D36" si="38">IF(RAND()&lt;0.2,"NA",RANDBETWEEN(60,80))</f>
-        <v>61</v>
-      </c>
-      <c r="C36" s="3">
+        <v>68</v>
+      </c>
+      <c r="C36" s="3" t="str">
         <f t="shared" si="38"/>
-        <v>72</v>
+        <v>NA</v>
       </c>
       <c r="D36" s="3">
         <f t="shared" si="38"/>
-        <v>80</v>
+        <v>64</v>
       </c>
       <c r="E36" s="2">
         <f t="shared" si="4"/>
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="F36" s="2">
         <f t="shared" si="5"/>
@@ -1227,23 +1227,23 @@
       </c>
       <c r="B37" s="3">
         <f t="shared" ref="B37:D37" si="39">IF(RAND()&lt;0.2,"NA",RANDBETWEEN(60,80))</f>
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="C37" s="3">
         <f t="shared" si="39"/>
-        <v>79</v>
+        <v>68</v>
       </c>
       <c r="D37" s="3">
         <f t="shared" si="39"/>
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="E37" s="2">
         <f t="shared" si="4"/>
-        <v>87</v>
+        <v>76</v>
       </c>
       <c r="F37" s="2">
         <f t="shared" si="5"/>
-        <v>2018</v>
+        <v>2020</v>
       </c>
     </row>
     <row r="38">
@@ -1253,7 +1253,7 @@
       </c>
       <c r="B38" s="3">
         <f t="shared" ref="B38:D38" si="40">IF(RAND()&lt;0.2,"NA",RANDBETWEEN(60,80))</f>
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C38" s="3">
         <f t="shared" si="40"/>
@@ -1261,15 +1261,15 @@
       </c>
       <c r="D38" s="3">
         <f t="shared" si="40"/>
-        <v>78</v>
+        <v>69</v>
       </c>
       <c r="E38" s="2">
         <f t="shared" si="4"/>
-        <v>75</v>
+        <v>88</v>
       </c>
       <c r="F38" s="2">
         <f t="shared" si="5"/>
-        <v>2018</v>
+        <v>2019</v>
       </c>
     </row>
     <row r="39">
@@ -1279,23 +1279,23 @@
       </c>
       <c r="B39" s="3">
         <f t="shared" ref="B39:D39" si="41">IF(RAND()&lt;0.2,"NA",RANDBETWEEN(60,80))</f>
-        <v>77</v>
-      </c>
-      <c r="C39" s="3">
+        <v>68</v>
+      </c>
+      <c r="C39" s="3" t="str">
         <f t="shared" si="41"/>
-        <v>80</v>
+        <v>NA</v>
       </c>
       <c r="D39" s="3">
         <f t="shared" si="41"/>
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="E39" s="2">
         <f t="shared" si="4"/>
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="F39" s="2">
         <f t="shared" si="5"/>
-        <v>2019</v>
+        <v>2020</v>
       </c>
     </row>
     <row r="40">
@@ -1303,21 +1303,21 @@
         <f t="shared" si="2"/>
         <v>39</v>
       </c>
-      <c r="B40" s="3">
+      <c r="B40" s="3" t="str">
         <f t="shared" ref="B40:D40" si="42">IF(RAND()&lt;0.2,"NA",RANDBETWEEN(60,80))</f>
-        <v>60</v>
-      </c>
-      <c r="C40" s="3" t="str">
+        <v>NA</v>
+      </c>
+      <c r="C40" s="3">
         <f t="shared" si="42"/>
-        <v>NA</v>
-      </c>
-      <c r="D40" s="3">
+        <v>78</v>
+      </c>
+      <c r="D40" s="3" t="str">
         <f t="shared" si="42"/>
-        <v>75</v>
+        <v>NA</v>
       </c>
       <c r="E40" s="2">
         <f t="shared" si="4"/>
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="F40" s="2">
         <f t="shared" si="5"/>
@@ -1331,23 +1331,23 @@
       </c>
       <c r="B41" s="3">
         <f t="shared" ref="B41:D41" si="43">IF(RAND()&lt;0.2,"NA",RANDBETWEEN(60,80))</f>
-        <v>62</v>
+        <v>68</v>
       </c>
       <c r="C41" s="3">
         <f t="shared" si="43"/>
-        <v>64</v>
-      </c>
-      <c r="D41" s="3">
+        <v>76</v>
+      </c>
+      <c r="D41" s="3" t="str">
         <f t="shared" si="43"/>
-        <v>60</v>
+        <v>NA</v>
       </c>
       <c r="E41" s="2">
         <f t="shared" si="4"/>
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F41" s="2">
         <f t="shared" si="5"/>
-        <v>2021</v>
+        <v>2018</v>
       </c>
     </row>
     <row r="42">
@@ -1357,7 +1357,7 @@
       </c>
       <c r="B42" s="3">
         <f t="shared" ref="B42:D42" si="44">IF(RAND()&lt;0.2,"NA",RANDBETWEEN(60,80))</f>
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="C42" s="3">
         <f t="shared" si="44"/>
@@ -1365,15 +1365,15 @@
       </c>
       <c r="D42" s="3">
         <f t="shared" si="44"/>
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="E42" s="2">
         <f t="shared" si="4"/>
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="F42" s="2">
         <f t="shared" si="5"/>
-        <v>2021</v>
+        <v>2018</v>
       </c>
     </row>
     <row r="43">
@@ -1383,19 +1383,19 @@
       </c>
       <c r="B43" s="3">
         <f t="shared" ref="B43:D43" si="45">IF(RAND()&lt;0.2,"NA",RANDBETWEEN(60,80))</f>
-        <v>64</v>
-      </c>
-      <c r="C43" s="3">
+        <v>75</v>
+      </c>
+      <c r="C43" s="3" t="str">
         <f t="shared" si="45"/>
-        <v>75</v>
-      </c>
-      <c r="D43" s="3">
+        <v>NA</v>
+      </c>
+      <c r="D43" s="3" t="str">
         <f t="shared" si="45"/>
-        <v>74</v>
+        <v>NA</v>
       </c>
       <c r="E43" s="2">
         <f t="shared" si="4"/>
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="F43" s="2">
         <f t="shared" si="5"/>
@@ -1409,23 +1409,23 @@
       </c>
       <c r="B44" s="3">
         <f t="shared" ref="B44:D44" si="46">IF(RAND()&lt;0.2,"NA",RANDBETWEEN(60,80))</f>
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="C44" s="3">
         <f t="shared" si="46"/>
-        <v>62</v>
+        <v>70</v>
       </c>
       <c r="D44" s="3">
         <f t="shared" si="46"/>
-        <v>66</v>
+        <v>75</v>
       </c>
       <c r="E44" s="2">
         <f t="shared" si="4"/>
-        <v>5</v>
+        <v>79</v>
       </c>
       <c r="F44" s="2">
         <f t="shared" si="5"/>
-        <v>2021</v>
+        <v>2019</v>
       </c>
     </row>
     <row r="45">
@@ -1435,19 +1435,19 @@
       </c>
       <c r="B45" s="3">
         <f t="shared" ref="B45:D45" si="47">IF(RAND()&lt;0.2,"NA",RANDBETWEEN(60,80))</f>
-        <v>74</v>
+        <v>61</v>
       </c>
       <c r="C45" s="3">
         <f t="shared" si="47"/>
-        <v>63</v>
-      </c>
-      <c r="D45" s="3" t="str">
+        <v>66</v>
+      </c>
+      <c r="D45" s="3">
         <f t="shared" si="47"/>
-        <v>NA</v>
+        <v>66</v>
       </c>
       <c r="E45" s="2">
         <f t="shared" si="4"/>
-        <v>500</v>
+        <v>82</v>
       </c>
       <c r="F45" s="2">
         <f t="shared" si="5"/>
@@ -1459,25 +1459,25 @@
         <f t="shared" si="2"/>
         <v>45</v>
       </c>
-      <c r="B46" s="3" t="str">
+      <c r="B46" s="3">
         <f t="shared" ref="B46:D46" si="48">IF(RAND()&lt;0.2,"NA",RANDBETWEEN(60,80))</f>
-        <v>NA</v>
+        <v>67</v>
       </c>
       <c r="C46" s="3">
         <f t="shared" si="48"/>
-        <v>72</v>
-      </c>
-      <c r="D46" s="3" t="str">
+        <v>61</v>
+      </c>
+      <c r="D46" s="3">
         <f t="shared" si="48"/>
-        <v>NA</v>
+        <v>70</v>
       </c>
       <c r="E46" s="2">
         <f t="shared" si="4"/>
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="F46" s="2">
         <f t="shared" si="5"/>
-        <v>2020</v>
+        <v>2019</v>
       </c>
     </row>
     <row r="47">
@@ -1487,23 +1487,23 @@
       </c>
       <c r="B47" s="3">
         <f t="shared" ref="B47:D47" si="49">IF(RAND()&lt;0.2,"NA",RANDBETWEEN(60,80))</f>
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="C47" s="3">
         <f t="shared" si="49"/>
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="D47" s="3">
         <f t="shared" si="49"/>
-        <v>72</v>
+        <v>60</v>
       </c>
       <c r="E47" s="2">
         <f t="shared" si="4"/>
-        <v>86</v>
+        <v>79</v>
       </c>
       <c r="F47" s="2">
         <f t="shared" si="5"/>
-        <v>2019</v>
+        <v>2020</v>
       </c>
     </row>
     <row r="48">
@@ -1513,23 +1513,23 @@
       </c>
       <c r="B48" s="3">
         <f t="shared" ref="B48:D48" si="50">IF(RAND()&lt;0.2,"NA",RANDBETWEEN(60,80))</f>
-        <v>77</v>
+        <v>64</v>
       </c>
       <c r="C48" s="3">
         <f t="shared" si="50"/>
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="D48" s="3">
         <f t="shared" si="50"/>
-        <v>74</v>
+        <v>62</v>
       </c>
       <c r="E48" s="2">
         <f t="shared" si="4"/>
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="F48" s="2">
         <f t="shared" si="5"/>
-        <v>2018</v>
+        <v>2020</v>
       </c>
     </row>
     <row r="49">
@@ -1537,25 +1537,25 @@
         <f t="shared" si="2"/>
         <v>48</v>
       </c>
-      <c r="B49" s="3" t="str">
+      <c r="B49" s="3">
         <f t="shared" ref="B49:D49" si="51">IF(RAND()&lt;0.2,"NA",RANDBETWEEN(60,80))</f>
-        <v>NA</v>
+        <v>80</v>
       </c>
       <c r="C49" s="3">
         <f t="shared" si="51"/>
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D49" s="3">
         <f t="shared" si="51"/>
-        <v>61</v>
+        <v>80</v>
       </c>
       <c r="E49" s="2">
         <f t="shared" si="4"/>
-        <v>84</v>
+        <v>75</v>
       </c>
       <c r="F49" s="2">
         <f t="shared" si="5"/>
-        <v>2020</v>
+        <v>2019</v>
       </c>
     </row>
     <row r="50">
@@ -1563,9 +1563,9 @@
         <f t="shared" si="2"/>
         <v>49</v>
       </c>
-      <c r="B50" s="3" t="str">
+      <c r="B50" s="3">
         <f t="shared" ref="B50:D50" si="52">IF(RAND()&lt;0.2,"NA",RANDBETWEEN(60,80))</f>
-        <v>NA</v>
+        <v>80</v>
       </c>
       <c r="C50" s="3" t="str">
         <f t="shared" si="52"/>
@@ -1573,11 +1573,11 @@
       </c>
       <c r="D50" s="3">
         <f t="shared" si="52"/>
-        <v>62</v>
+        <v>74</v>
       </c>
       <c r="E50" s="2">
         <f t="shared" si="4"/>
-        <v>86</v>
+        <v>80</v>
       </c>
       <c r="F50" s="2">
         <f t="shared" si="5"/>
@@ -1589,25 +1589,25 @@
         <f t="shared" si="2"/>
         <v>50</v>
       </c>
-      <c r="B51" s="3" t="str">
+      <c r="B51" s="3">
         <f t="shared" ref="B51:D51" si="53">IF(RAND()&lt;0.2,"NA",RANDBETWEEN(60,80))</f>
-        <v>NA</v>
+        <v>62</v>
       </c>
       <c r="C51" s="3">
         <f t="shared" si="53"/>
-        <v>70</v>
-      </c>
-      <c r="D51" s="3" t="str">
+        <v>67</v>
+      </c>
+      <c r="D51" s="3">
         <f t="shared" si="53"/>
-        <v>NA</v>
+        <v>60</v>
       </c>
       <c r="E51" s="2">
         <f t="shared" si="4"/>
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="F51" s="2">
         <f t="shared" si="5"/>
-        <v>2020</v>
+        <v>2018</v>
       </c>
     </row>
     <row r="52">
@@ -1615,25 +1615,25 @@
         <f t="shared" si="2"/>
         <v>51</v>
       </c>
-      <c r="B52" s="3">
+      <c r="B52" s="3" t="str">
         <f t="shared" ref="B52:D52" si="54">IF(RAND()&lt;0.2,"NA",RANDBETWEEN(60,80))</f>
-        <v>63</v>
+        <v>NA</v>
       </c>
       <c r="C52" s="3">
         <f t="shared" si="54"/>
-        <v>67</v>
+        <v>79</v>
       </c>
       <c r="D52" s="3">
         <f t="shared" si="54"/>
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="E52" s="2">
         <f t="shared" si="4"/>
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="F52" s="2">
         <f t="shared" si="5"/>
-        <v>2019</v>
+        <v>2021</v>
       </c>
     </row>
     <row r="53">
@@ -1643,23 +1643,23 @@
       </c>
       <c r="B53" s="3">
         <f t="shared" ref="B53:D53" si="55">IF(RAND()&lt;0.2,"NA",RANDBETWEEN(60,80))</f>
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="C53" s="3">
         <f t="shared" si="55"/>
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="D53" s="3">
         <f t="shared" si="55"/>
-        <v>69</v>
+        <v>76</v>
       </c>
       <c r="E53" s="2">
         <f t="shared" si="4"/>
-        <v>500</v>
+        <v>87</v>
       </c>
       <c r="F53" s="2">
         <f t="shared" si="5"/>
-        <v>2021</v>
+        <v>2020</v>
       </c>
     </row>
     <row r="54">
@@ -1669,23 +1669,23 @@
       </c>
       <c r="B54" s="3">
         <f t="shared" ref="B54:D54" si="56">IF(RAND()&lt;0.2,"NA",RANDBETWEEN(60,80))</f>
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C54" s="3">
         <f t="shared" si="56"/>
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="D54" s="3">
         <f t="shared" si="56"/>
-        <v>62</v>
+        <v>68</v>
       </c>
       <c r="E54" s="2">
         <f t="shared" si="4"/>
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="F54" s="2">
         <f t="shared" si="5"/>
-        <v>2019</v>
+        <v>2020</v>
       </c>
     </row>
     <row r="55">
@@ -1695,23 +1695,23 @@
       </c>
       <c r="B55" s="3">
         <f t="shared" ref="B55:D55" si="57">IF(RAND()&lt;0.2,"NA",RANDBETWEEN(60,80))</f>
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="C55" s="3">
         <f t="shared" si="57"/>
+        <v>66</v>
+      </c>
+      <c r="D55" s="3" t="str">
+        <f t="shared" si="57"/>
+        <v>NA</v>
+      </c>
+      <c r="E55" s="2">
+        <f t="shared" si="4"/>
         <v>78</v>
       </c>
-      <c r="D55" s="3">
-        <f t="shared" si="57"/>
-        <v>69</v>
-      </c>
-      <c r="E55" s="2">
-        <f t="shared" si="4"/>
-        <v>84</v>
-      </c>
       <c r="F55" s="2">
         <f t="shared" si="5"/>
-        <v>2021</v>
+        <v>2020</v>
       </c>
     </row>
     <row r="56">
@@ -1725,19 +1725,19 @@
       </c>
       <c r="C56" s="3">
         <f t="shared" si="58"/>
-        <v>66</v>
-      </c>
-      <c r="D56" s="3" t="str">
+        <v>62</v>
+      </c>
+      <c r="D56" s="3">
         <f t="shared" si="58"/>
-        <v>NA</v>
+        <v>62</v>
       </c>
       <c r="E56" s="2">
         <f t="shared" si="4"/>
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="F56" s="2">
         <f t="shared" si="5"/>
-        <v>2019</v>
+        <v>2020</v>
       </c>
     </row>
     <row r="57">
@@ -1745,25 +1745,25 @@
         <f t="shared" si="2"/>
         <v>56</v>
       </c>
-      <c r="B57" s="3" t="str">
+      <c r="B57" s="3">
         <f t="shared" ref="B57:D57" si="59">IF(RAND()&lt;0.2,"NA",RANDBETWEEN(60,80))</f>
-        <v>NA</v>
-      </c>
-      <c r="C57" s="3" t="str">
+        <v>66</v>
+      </c>
+      <c r="C57" s="3">
         <f t="shared" si="59"/>
-        <v>NA</v>
+        <v>79</v>
       </c>
       <c r="D57" s="3">
         <f t="shared" si="59"/>
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="E57" s="2">
         <f t="shared" si="4"/>
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="F57" s="2">
         <f t="shared" si="5"/>
-        <v>2021</v>
+        <v>2019</v>
       </c>
     </row>
     <row r="58">
@@ -1771,25 +1771,25 @@
         <f t="shared" si="2"/>
         <v>57</v>
       </c>
-      <c r="B58" s="3">
+      <c r="B58" s="3" t="str">
         <f t="shared" ref="B58:D58" si="60">IF(RAND()&lt;0.2,"NA",RANDBETWEEN(60,80))</f>
-        <v>77</v>
+        <v>NA</v>
       </c>
       <c r="C58" s="3">
         <f t="shared" si="60"/>
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="D58" s="3">
         <f t="shared" si="60"/>
-        <v>73</v>
+        <v>63</v>
       </c>
       <c r="E58" s="2">
         <f t="shared" si="4"/>
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="F58" s="2">
         <f t="shared" si="5"/>
-        <v>2021</v>
+        <v>2020</v>
       </c>
     </row>
     <row r="59">
@@ -1799,19 +1799,19 @@
       </c>
       <c r="B59" s="3">
         <f t="shared" ref="B59:D59" si="61">IF(RAND()&lt;0.2,"NA",RANDBETWEEN(60,80))</f>
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="C59" s="3">
         <f t="shared" si="61"/>
-        <v>60</v>
+        <v>75</v>
       </c>
       <c r="D59" s="3">
         <f t="shared" si="61"/>
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="E59" s="2">
         <f t="shared" si="4"/>
-        <v>83</v>
+        <v>90</v>
       </c>
       <c r="F59" s="2">
         <f t="shared" si="5"/>
@@ -1823,25 +1823,25 @@
         <f t="shared" si="2"/>
         <v>59</v>
       </c>
-      <c r="B60" s="3">
+      <c r="B60" s="3" t="str">
         <f t="shared" ref="B60:D60" si="62">IF(RAND()&lt;0.2,"NA",RANDBETWEEN(60,80))</f>
-        <v>60</v>
+        <v>NA</v>
       </c>
       <c r="C60" s="3">
         <f t="shared" si="62"/>
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="D60" s="3">
         <f t="shared" si="62"/>
-        <v>66</v>
+        <v>78</v>
       </c>
       <c r="E60" s="2">
         <f t="shared" si="4"/>
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="F60" s="2">
         <f t="shared" si="5"/>
-        <v>2018</v>
+        <v>2019</v>
       </c>
     </row>
     <row r="61">
@@ -1851,23 +1851,23 @@
       </c>
       <c r="B61" s="3">
         <f t="shared" ref="B61:D61" si="63">IF(RAND()&lt;0.2,"NA",RANDBETWEEN(60,80))</f>
-        <v>76</v>
-      </c>
-      <c r="C61" s="3">
+        <v>70</v>
+      </c>
+      <c r="C61" s="3" t="str">
         <f t="shared" si="63"/>
-        <v>74</v>
+        <v>NA</v>
       </c>
       <c r="D61" s="3">
         <f t="shared" si="63"/>
-        <v>76</v>
+        <v>63</v>
       </c>
       <c r="E61" s="2">
         <f t="shared" si="4"/>
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="F61" s="2">
         <f t="shared" si="5"/>
-        <v>2020</v>
+        <v>2018</v>
       </c>
     </row>
     <row r="62">
@@ -1875,9 +1875,9 @@
         <f t="shared" si="2"/>
         <v>61</v>
       </c>
-      <c r="B62" s="3">
+      <c r="B62" s="3" t="str">
         <f t="shared" ref="B62:D62" si="64">IF(RAND()&lt;0.2,"NA",RANDBETWEEN(60,80))</f>
-        <v>79</v>
+        <v>NA</v>
       </c>
       <c r="C62" s="3">
         <f t="shared" si="64"/>
@@ -1885,15 +1885,15 @@
       </c>
       <c r="D62" s="3">
         <f t="shared" si="64"/>
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="E62" s="2">
         <f t="shared" si="4"/>
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="F62" s="2">
         <f t="shared" si="5"/>
-        <v>2018</v>
+        <v>2021</v>
       </c>
     </row>
     <row r="63">
@@ -1903,23 +1903,23 @@
       </c>
       <c r="B63" s="3">
         <f t="shared" ref="B63:D63" si="65">IF(RAND()&lt;0.2,"NA",RANDBETWEEN(60,80))</f>
-        <v>68</v>
-      </c>
-      <c r="C63" s="3" t="str">
+        <v>72</v>
+      </c>
+      <c r="C63" s="3">
         <f t="shared" si="65"/>
-        <v>NA</v>
+        <v>75</v>
       </c>
       <c r="D63" s="3">
         <f t="shared" si="65"/>
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="E63" s="2">
         <f t="shared" si="4"/>
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="F63" s="2">
         <f t="shared" si="5"/>
-        <v>2018</v>
+        <v>2020</v>
       </c>
     </row>
     <row r="64">
@@ -1929,19 +1929,19 @@
       </c>
       <c r="B64" s="3">
         <f t="shared" ref="B64:D64" si="66">IF(RAND()&lt;0.2,"NA",RANDBETWEEN(60,80))</f>
-        <v>71</v>
+        <v>63</v>
       </c>
       <c r="C64" s="3">
         <f t="shared" si="66"/>
-        <v>78</v>
+        <v>61</v>
       </c>
       <c r="D64" s="3">
         <f t="shared" si="66"/>
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="E64" s="2">
         <f t="shared" si="4"/>
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="F64" s="2">
         <f t="shared" si="5"/>
@@ -1955,19 +1955,19 @@
       </c>
       <c r="B65" s="3">
         <f t="shared" ref="B65:D65" si="67">IF(RAND()&lt;0.2,"NA",RANDBETWEEN(60,80))</f>
-        <v>70</v>
+        <v>61</v>
       </c>
       <c r="C65" s="3">
         <f t="shared" si="67"/>
-        <v>75</v>
-      </c>
-      <c r="D65" s="3">
+        <v>74</v>
+      </c>
+      <c r="D65" s="3" t="str">
         <f t="shared" si="67"/>
-        <v>78</v>
+        <v>NA</v>
       </c>
       <c r="E65" s="2">
         <f t="shared" si="4"/>
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="F65" s="2">
         <f t="shared" si="5"/>
@@ -1981,23 +1981,23 @@
       </c>
       <c r="B66" s="3">
         <f t="shared" ref="B66:D66" si="68">IF(RAND()&lt;0.2,"NA",RANDBETWEEN(60,80))</f>
-        <v>80</v>
+        <v>69</v>
       </c>
       <c r="C66" s="3">
         <f t="shared" si="68"/>
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D66" s="3">
         <f t="shared" si="68"/>
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="E66" s="2">
         <f t="shared" si="4"/>
-        <v>81</v>
+        <v>500</v>
       </c>
       <c r="F66" s="2">
         <f t="shared" si="5"/>
-        <v>2019</v>
+        <v>2018</v>
       </c>
     </row>
     <row r="67">
@@ -2007,23 +2007,23 @@
       </c>
       <c r="B67" s="3">
         <f t="shared" ref="B67:D67" si="69">IF(RAND()&lt;0.2,"NA",RANDBETWEEN(60,80))</f>
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="C67" s="3">
         <f t="shared" si="69"/>
-        <v>73</v>
+        <v>63</v>
       </c>
       <c r="D67" s="3">
         <f t="shared" si="69"/>
-        <v>72</v>
+        <v>79</v>
       </c>
       <c r="E67" s="2">
         <f t="shared" si="4"/>
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="F67" s="2">
         <f t="shared" si="5"/>
-        <v>2019</v>
+        <v>2018</v>
       </c>
     </row>
     <row r="68">
@@ -2031,21 +2031,21 @@
         <f t="shared" si="2"/>
         <v>67</v>
       </c>
-      <c r="B68" s="3">
+      <c r="B68" s="3" t="str">
         <f t="shared" ref="B68:D68" si="70">IF(RAND()&lt;0.2,"NA",RANDBETWEEN(60,80))</f>
-        <v>62</v>
+        <v>NA</v>
       </c>
       <c r="C68" s="3">
         <f t="shared" si="70"/>
-        <v>62</v>
-      </c>
-      <c r="D68" s="3">
+        <v>67</v>
+      </c>
+      <c r="D68" s="3" t="str">
         <f t="shared" si="70"/>
-        <v>63</v>
+        <v>NA</v>
       </c>
       <c r="E68" s="2">
         <f t="shared" si="4"/>
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="F68" s="2">
         <f t="shared" si="5"/>
@@ -2059,23 +2059,23 @@
       </c>
       <c r="B69" s="3">
         <f t="shared" ref="B69:D69" si="71">IF(RAND()&lt;0.2,"NA",RANDBETWEEN(60,80))</f>
+        <v>79</v>
+      </c>
+      <c r="C69" s="3">
+        <f t="shared" si="71"/>
         <v>67</v>
       </c>
-      <c r="C69" s="3" t="str">
+      <c r="D69" s="3" t="str">
         <f t="shared" si="71"/>
         <v>NA</v>
       </c>
-      <c r="D69" s="3">
-        <f t="shared" si="71"/>
-        <v>65</v>
-      </c>
       <c r="E69" s="2">
         <f t="shared" si="4"/>
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="F69" s="2">
         <f t="shared" si="5"/>
-        <v>2018</v>
+        <v>2019</v>
       </c>
     </row>
     <row r="70">
@@ -2083,17 +2083,17 @@
         <f t="shared" si="2"/>
         <v>69</v>
       </c>
-      <c r="B70" s="3">
+      <c r="B70" s="3" t="str">
         <f t="shared" ref="B70:D70" si="72">IF(RAND()&lt;0.2,"NA",RANDBETWEEN(60,80))</f>
-        <v>79</v>
+        <v>NA</v>
       </c>
       <c r="C70" s="3">
         <f t="shared" si="72"/>
-        <v>76</v>
+        <v>69</v>
       </c>
       <c r="D70" s="3">
         <f t="shared" si="72"/>
-        <v>62</v>
+        <v>78</v>
       </c>
       <c r="E70" s="2">
         <f t="shared" si="4"/>
@@ -2111,23 +2111,23 @@
       </c>
       <c r="B71" s="3">
         <f t="shared" ref="B71:D71" si="73">IF(RAND()&lt;0.2,"NA",RANDBETWEEN(60,80))</f>
-        <v>76</v>
-      </c>
-      <c r="C71" s="3" t="str">
+        <v>66</v>
+      </c>
+      <c r="C71" s="3">
         <f t="shared" si="73"/>
-        <v>NA</v>
+        <v>73</v>
       </c>
       <c r="D71" s="3">
         <f t="shared" si="73"/>
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E71" s="2">
         <f t="shared" si="4"/>
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="F71" s="2">
         <f t="shared" si="5"/>
-        <v>2019</v>
+        <v>2020</v>
       </c>
     </row>
     <row r="72">
@@ -2135,25 +2135,25 @@
         <f t="shared" si="2"/>
         <v>71</v>
       </c>
-      <c r="B72" s="3">
+      <c r="B72" s="3" t="str">
         <f t="shared" ref="B72:D72" si="74">IF(RAND()&lt;0.2,"NA",RANDBETWEEN(60,80))</f>
-        <v>70</v>
+        <v>NA</v>
       </c>
       <c r="C72" s="3">
         <f t="shared" si="74"/>
-        <v>74</v>
-      </c>
-      <c r="D72" s="3">
+        <v>80</v>
+      </c>
+      <c r="D72" s="3" t="str">
         <f t="shared" si="74"/>
-        <v>67</v>
+        <v>NA</v>
       </c>
       <c r="E72" s="2">
         <f t="shared" si="4"/>
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="F72" s="2">
         <f t="shared" si="5"/>
-        <v>2020</v>
+        <v>2021</v>
       </c>
     </row>
     <row r="73">
@@ -2163,23 +2163,23 @@
       </c>
       <c r="B73" s="3">
         <f t="shared" ref="B73:D73" si="75">IF(RAND()&lt;0.2,"NA",RANDBETWEEN(60,80))</f>
-        <v>62</v>
+        <v>69</v>
       </c>
       <c r="C73" s="3">
         <f t="shared" si="75"/>
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="D73" s="3">
         <f t="shared" si="75"/>
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E73" s="2">
         <f t="shared" si="4"/>
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="F73" s="2">
         <f t="shared" si="5"/>
-        <v>2021</v>
+        <v>2019</v>
       </c>
     </row>
     <row r="74">
@@ -2189,23 +2189,23 @@
       </c>
       <c r="B74" s="3">
         <f t="shared" ref="B74:D74" si="76">IF(RAND()&lt;0.2,"NA",RANDBETWEEN(60,80))</f>
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="C74" s="3">
         <f t="shared" si="76"/>
-        <v>65</v>
+        <v>73</v>
       </c>
       <c r="D74" s="3">
         <f t="shared" si="76"/>
-        <v>80</v>
+        <v>61</v>
       </c>
       <c r="E74" s="2">
         <f t="shared" si="4"/>
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="F74" s="2">
         <f t="shared" si="5"/>
-        <v>2020</v>
+        <v>2019</v>
       </c>
     </row>
     <row r="75">
@@ -2215,23 +2215,23 @@
       </c>
       <c r="B75" s="3">
         <f t="shared" ref="B75:D75" si="77">IF(RAND()&lt;0.2,"NA",RANDBETWEEN(60,80))</f>
-        <v>79</v>
+        <v>62</v>
       </c>
       <c r="C75" s="3">
         <f t="shared" si="77"/>
         <v>64</v>
       </c>
-      <c r="D75" s="3">
+      <c r="D75" s="3" t="str">
         <f t="shared" si="77"/>
-        <v>80</v>
+        <v>NA</v>
       </c>
       <c r="E75" s="2">
         <f t="shared" si="4"/>
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="F75" s="2">
         <f t="shared" si="5"/>
-        <v>2018</v>
+        <v>2019</v>
       </c>
     </row>
     <row r="76">
@@ -2241,11 +2241,11 @@
       </c>
       <c r="B76" s="3">
         <f t="shared" ref="B76:D76" si="78">IF(RAND()&lt;0.2,"NA",RANDBETWEEN(60,80))</f>
-        <v>73</v>
-      </c>
-      <c r="C76" s="3">
+        <v>71</v>
+      </c>
+      <c r="C76" s="3" t="str">
         <f t="shared" si="78"/>
-        <v>78</v>
+        <v>NA</v>
       </c>
       <c r="D76" s="3" t="str">
         <f t="shared" si="78"/>
@@ -2253,11 +2253,11 @@
       </c>
       <c r="E76" s="2">
         <f t="shared" si="4"/>
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="F76" s="2">
         <f t="shared" si="5"/>
-        <v>2019</v>
+        <v>2020</v>
       </c>
     </row>
     <row r="77">
@@ -2265,21 +2265,21 @@
         <f t="shared" si="2"/>
         <v>76</v>
       </c>
-      <c r="B77" s="3">
+      <c r="B77" s="3" t="str">
         <f t="shared" ref="B77:D77" si="79">IF(RAND()&lt;0.2,"NA",RANDBETWEEN(60,80))</f>
-        <v>64</v>
+        <v>NA</v>
       </c>
       <c r="C77" s="3">
         <f t="shared" si="79"/>
-        <v>77</v>
+        <v>70</v>
       </c>
       <c r="D77" s="3">
         <f t="shared" si="79"/>
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="E77" s="2">
         <f t="shared" si="4"/>
-        <v>5</v>
+        <v>82</v>
       </c>
       <c r="F77" s="2">
         <f t="shared" si="5"/>
@@ -2293,11 +2293,11 @@
       </c>
       <c r="B78" s="3">
         <f t="shared" ref="B78:D78" si="80">IF(RAND()&lt;0.2,"NA",RANDBETWEEN(60,80))</f>
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="C78" s="3">
         <f t="shared" si="80"/>
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="D78" s="3" t="str">
         <f t="shared" si="80"/>
@@ -2305,11 +2305,11 @@
       </c>
       <c r="E78" s="2">
         <f t="shared" si="4"/>
-        <v>89</v>
+        <v>76</v>
       </c>
       <c r="F78" s="2">
         <f t="shared" si="5"/>
-        <v>2021</v>
+        <v>2019</v>
       </c>
     </row>
     <row r="79">
@@ -2319,23 +2319,23 @@
       </c>
       <c r="B79" s="3">
         <f t="shared" ref="B79:D79" si="81">IF(RAND()&lt;0.2,"NA",RANDBETWEEN(60,80))</f>
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C79" s="3">
         <f t="shared" si="81"/>
-        <v>69</v>
+        <v>60</v>
       </c>
       <c r="D79" s="3">
         <f t="shared" si="81"/>
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="E79" s="2">
         <f t="shared" si="4"/>
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="F79" s="2">
         <f t="shared" si="5"/>
-        <v>2020</v>
+        <v>2021</v>
       </c>
     </row>
     <row r="80">
@@ -2345,19 +2345,19 @@
       </c>
       <c r="B80" s="3">
         <f t="shared" ref="B80:D80" si="82">IF(RAND()&lt;0.2,"NA",RANDBETWEEN(60,80))</f>
-        <v>60</v>
-      </c>
-      <c r="C80" s="3" t="str">
+        <v>77</v>
+      </c>
+      <c r="C80" s="3">
         <f t="shared" si="82"/>
-        <v>NA</v>
+        <v>61</v>
       </c>
       <c r="D80" s="3">
         <f t="shared" si="82"/>
-        <v>62</v>
+        <v>75</v>
       </c>
       <c r="E80" s="2">
         <f t="shared" si="4"/>
-        <v>89</v>
+        <v>84</v>
       </c>
       <c r="F80" s="2">
         <f t="shared" si="5"/>
@@ -2371,23 +2371,23 @@
       </c>
       <c r="B81" s="3">
         <f t="shared" ref="B81:D81" si="83">IF(RAND()&lt;0.2,"NA",RANDBETWEEN(60,80))</f>
-        <v>65</v>
-      </c>
-      <c r="C81" s="3" t="str">
+        <v>66</v>
+      </c>
+      <c r="C81" s="3">
         <f t="shared" si="83"/>
-        <v>NA</v>
+        <v>67</v>
       </c>
       <c r="D81" s="3">
         <f t="shared" si="83"/>
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E81" s="2">
         <f t="shared" si="4"/>
-        <v>90</v>
+        <v>5</v>
       </c>
       <c r="F81" s="2">
         <f t="shared" si="5"/>
-        <v>2018</v>
+        <v>2020</v>
       </c>
     </row>
     <row r="82">
@@ -2395,25 +2395,25 @@
         <f t="shared" si="2"/>
         <v>81</v>
       </c>
-      <c r="B82" s="3">
+      <c r="B82" s="3" t="str">
         <f t="shared" ref="B82:D82" si="84">IF(RAND()&lt;0.2,"NA",RANDBETWEEN(60,80))</f>
-        <v>75</v>
+        <v>NA</v>
       </c>
       <c r="C82" s="3">
         <f t="shared" si="84"/>
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="D82" s="3">
         <f t="shared" si="84"/>
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="E82" s="2">
         <f t="shared" si="4"/>
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="F82" s="2">
         <f t="shared" si="5"/>
-        <v>2021</v>
+        <v>2019</v>
       </c>
     </row>
     <row r="83">
@@ -2421,25 +2421,25 @@
         <f t="shared" si="2"/>
         <v>82</v>
       </c>
-      <c r="B83" s="3" t="str">
+      <c r="B83" s="3">
         <f t="shared" ref="B83:D83" si="85">IF(RAND()&lt;0.2,"NA",RANDBETWEEN(60,80))</f>
-        <v>NA</v>
+        <v>80</v>
       </c>
       <c r="C83" s="3">
         <f t="shared" si="85"/>
-        <v>74</v>
-      </c>
-      <c r="D83" s="3">
+        <v>75</v>
+      </c>
+      <c r="D83" s="3" t="str">
         <f t="shared" si="85"/>
-        <v>71</v>
+        <v>NA</v>
       </c>
       <c r="E83" s="2">
         <f t="shared" si="4"/>
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="F83" s="2">
         <f t="shared" si="5"/>
-        <v>2020</v>
+        <v>2018</v>
       </c>
     </row>
     <row r="84">
@@ -2447,25 +2447,25 @@
         <f t="shared" si="2"/>
         <v>83</v>
       </c>
-      <c r="B84" s="3" t="str">
+      <c r="B84" s="3">
         <f t="shared" ref="B84:D84" si="86">IF(RAND()&lt;0.2,"NA",RANDBETWEEN(60,80))</f>
-        <v>NA</v>
+        <v>66</v>
       </c>
       <c r="C84" s="3">
         <f t="shared" si="86"/>
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="D84" s="3">
         <f t="shared" si="86"/>
-        <v>74</v>
+        <v>61</v>
       </c>
       <c r="E84" s="2">
         <f t="shared" si="4"/>
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="F84" s="2">
         <f t="shared" si="5"/>
-        <v>2021</v>
+        <v>2018</v>
       </c>
     </row>
     <row r="85">
@@ -2475,23 +2475,23 @@
       </c>
       <c r="B85" s="3">
         <f t="shared" ref="B85:D85" si="87">IF(RAND()&lt;0.2,"NA",RANDBETWEEN(60,80))</f>
-        <v>77</v>
+        <v>70</v>
       </c>
       <c r="C85" s="3">
         <f t="shared" si="87"/>
-        <v>67</v>
-      </c>
-      <c r="D85" s="3" t="str">
+        <v>76</v>
+      </c>
+      <c r="D85" s="3">
         <f t="shared" si="87"/>
-        <v>NA</v>
+        <v>65</v>
       </c>
       <c r="E85" s="2">
         <f t="shared" si="4"/>
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="F85" s="2">
         <f t="shared" si="5"/>
-        <v>2019</v>
+        <v>2020</v>
       </c>
     </row>
     <row r="86">
@@ -2499,17 +2499,17 @@
         <f t="shared" si="2"/>
         <v>85</v>
       </c>
-      <c r="B86" s="3" t="str">
+      <c r="B86" s="3">
         <f t="shared" ref="B86:D86" si="88">IF(RAND()&lt;0.2,"NA",RANDBETWEEN(60,80))</f>
-        <v>NA</v>
+        <v>77</v>
       </c>
       <c r="C86" s="3">
         <f t="shared" si="88"/>
-        <v>68</v>
-      </c>
-      <c r="D86" s="3" t="str">
+        <v>78</v>
+      </c>
+      <c r="D86" s="3">
         <f t="shared" si="88"/>
-        <v>NA</v>
+        <v>73</v>
       </c>
       <c r="E86" s="2">
         <f t="shared" si="4"/>
@@ -2517,7 +2517,7 @@
       </c>
       <c r="F86" s="2">
         <f t="shared" si="5"/>
-        <v>2021</v>
+        <v>2020</v>
       </c>
     </row>
     <row r="87">
@@ -2525,25 +2525,25 @@
         <f t="shared" si="2"/>
         <v>86</v>
       </c>
-      <c r="B87" s="3">
+      <c r="B87" s="3" t="str">
         <f t="shared" ref="B87:D87" si="89">IF(RAND()&lt;0.2,"NA",RANDBETWEEN(60,80))</f>
-        <v>75</v>
-      </c>
-      <c r="C87" s="3" t="str">
+        <v>NA</v>
+      </c>
+      <c r="C87" s="3">
         <f t="shared" si="89"/>
-        <v>NA</v>
+        <v>74</v>
       </c>
       <c r="D87" s="3">
         <f t="shared" si="89"/>
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="E87" s="2">
         <f t="shared" si="4"/>
-        <v>75</v>
+        <v>90</v>
       </c>
       <c r="F87" s="2">
         <f t="shared" si="5"/>
-        <v>2020</v>
+        <v>2021</v>
       </c>
     </row>
     <row r="88">
@@ -2553,11 +2553,11 @@
       </c>
       <c r="B88" s="3">
         <f t="shared" ref="B88:D88" si="90">IF(RAND()&lt;0.2,"NA",RANDBETWEEN(60,80))</f>
-        <v>77</v>
+        <v>70</v>
       </c>
       <c r="C88" s="3">
         <f t="shared" si="90"/>
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="D88" s="3" t="str">
         <f t="shared" si="90"/>
@@ -2565,11 +2565,11 @@
       </c>
       <c r="E88" s="2">
         <f t="shared" si="4"/>
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="F88" s="2">
         <f t="shared" si="5"/>
-        <v>2019</v>
+        <v>2018</v>
       </c>
     </row>
     <row r="89">
@@ -2583,19 +2583,19 @@
       </c>
       <c r="C89" s="3">
         <f t="shared" si="91"/>
-        <v>65</v>
-      </c>
-      <c r="D89" s="3">
+        <v>75</v>
+      </c>
+      <c r="D89" s="3" t="str">
         <f t="shared" si="91"/>
-        <v>64</v>
+        <v>NA</v>
       </c>
       <c r="E89" s="2">
         <f t="shared" si="4"/>
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="F89" s="2">
         <f t="shared" si="5"/>
-        <v>2020</v>
+        <v>2019</v>
       </c>
     </row>
     <row r="90">
@@ -2605,23 +2605,23 @@
       </c>
       <c r="B90" s="3">
         <f t="shared" ref="B90:D90" si="92">IF(RAND()&lt;0.2,"NA",RANDBETWEEN(60,80))</f>
-        <v>71</v>
-      </c>
-      <c r="C90" s="3">
+        <v>65</v>
+      </c>
+      <c r="C90" s="3" t="str">
         <f t="shared" si="92"/>
-        <v>66</v>
+        <v>NA</v>
       </c>
       <c r="D90" s="3">
         <f t="shared" si="92"/>
-        <v>78</v>
+        <v>64</v>
       </c>
       <c r="E90" s="2">
         <f t="shared" si="4"/>
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="F90" s="2">
         <f t="shared" si="5"/>
-        <v>2019</v>
+        <v>2018</v>
       </c>
     </row>
     <row r="91">
@@ -2631,23 +2631,23 @@
       </c>
       <c r="B91" s="3">
         <f t="shared" ref="B91:D91" si="93">IF(RAND()&lt;0.2,"NA",RANDBETWEEN(60,80))</f>
-        <v>71</v>
+        <v>60</v>
       </c>
       <c r="C91" s="3">
         <f t="shared" si="93"/>
-        <v>78</v>
+        <v>61</v>
       </c>
       <c r="D91" s="3">
         <f t="shared" si="93"/>
-        <v>72</v>
+        <v>60</v>
       </c>
       <c r="E91" s="2">
         <f t="shared" si="4"/>
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="F91" s="2">
         <f t="shared" si="5"/>
-        <v>2019</v>
+        <v>2021</v>
       </c>
     </row>
     <row r="92">
@@ -2655,21 +2655,21 @@
         <f t="shared" si="2"/>
         <v>91</v>
       </c>
-      <c r="B92" s="3" t="str">
+      <c r="B92" s="3">
         <f t="shared" ref="B92:D92" si="94">IF(RAND()&lt;0.2,"NA",RANDBETWEEN(60,80))</f>
-        <v>NA</v>
-      </c>
-      <c r="C92" s="3">
+        <v>70</v>
+      </c>
+      <c r="C92" s="3" t="str">
         <f t="shared" si="94"/>
-        <v>79</v>
-      </c>
-      <c r="D92" s="3">
+        <v>NA</v>
+      </c>
+      <c r="D92" s="3" t="str">
         <f t="shared" si="94"/>
-        <v>64</v>
+        <v>NA</v>
       </c>
       <c r="E92" s="2">
         <f t="shared" si="4"/>
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="F92" s="2">
         <f t="shared" si="5"/>
@@ -2683,11 +2683,11 @@
       </c>
       <c r="B93" s="3">
         <f t="shared" ref="B93:D93" si="95">IF(RAND()&lt;0.2,"NA",RANDBETWEEN(60,80))</f>
-        <v>79</v>
+        <v>61</v>
       </c>
       <c r="C93" s="3">
         <f t="shared" si="95"/>
-        <v>65</v>
+        <v>72</v>
       </c>
       <c r="D93" s="3" t="str">
         <f t="shared" si="95"/>
@@ -2695,11 +2695,11 @@
       </c>
       <c r="E93" s="2">
         <f t="shared" si="4"/>
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="F93" s="2">
         <f t="shared" si="5"/>
-        <v>2018</v>
+        <v>2021</v>
       </c>
     </row>
     <row r="94">
@@ -2709,23 +2709,23 @@
       </c>
       <c r="B94" s="3">
         <f t="shared" ref="B94:D94" si="96">IF(RAND()&lt;0.2,"NA",RANDBETWEEN(60,80))</f>
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="C94" s="3">
         <f t="shared" si="96"/>
-        <v>78</v>
+        <v>67</v>
       </c>
       <c r="D94" s="3">
         <f t="shared" si="96"/>
-        <v>69</v>
+        <v>61</v>
       </c>
       <c r="E94" s="2">
         <f t="shared" si="4"/>
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="F94" s="2">
         <f t="shared" si="5"/>
-        <v>2018</v>
+        <v>2021</v>
       </c>
     </row>
     <row r="95">
@@ -2733,25 +2733,25 @@
         <f t="shared" si="2"/>
         <v>94</v>
       </c>
-      <c r="B95" s="3" t="str">
+      <c r="B95" s="3">
         <f t="shared" ref="B95:D95" si="97">IF(RAND()&lt;0.2,"NA",RANDBETWEEN(60,80))</f>
-        <v>NA</v>
-      </c>
-      <c r="C95" s="3" t="str">
+        <v>79</v>
+      </c>
+      <c r="C95" s="3">
         <f t="shared" si="97"/>
-        <v>NA</v>
+        <v>78</v>
       </c>
       <c r="D95" s="3">
         <f t="shared" si="97"/>
-        <v>76</v>
+        <v>63</v>
       </c>
       <c r="E95" s="2">
         <f t="shared" si="4"/>
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="F95" s="2">
         <f t="shared" si="5"/>
-        <v>2020</v>
+        <v>2021</v>
       </c>
     </row>
     <row r="96">
@@ -2761,19 +2761,19 @@
       </c>
       <c r="B96" s="3">
         <f t="shared" ref="B96:D96" si="98">IF(RAND()&lt;0.2,"NA",RANDBETWEEN(60,80))</f>
-        <v>64</v>
-      </c>
-      <c r="C96" s="3" t="str">
+        <v>79</v>
+      </c>
+      <c r="C96" s="3">
         <f t="shared" si="98"/>
-        <v>NA</v>
+        <v>71</v>
       </c>
       <c r="D96" s="3">
         <f t="shared" si="98"/>
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="E96" s="2">
         <f t="shared" si="4"/>
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="F96" s="2">
         <f t="shared" si="5"/>
@@ -2787,19 +2787,19 @@
       </c>
       <c r="B97" s="3">
         <f t="shared" ref="B97:D97" si="99">IF(RAND()&lt;0.2,"NA",RANDBETWEEN(60,80))</f>
-        <v>60</v>
-      </c>
-      <c r="C97" s="3">
+        <v>68</v>
+      </c>
+      <c r="C97" s="3" t="str">
         <f t="shared" si="99"/>
-        <v>62</v>
+        <v>NA</v>
       </c>
       <c r="D97" s="3">
         <f t="shared" si="99"/>
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="E97" s="2">
         <f t="shared" si="4"/>
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="F97" s="2">
         <f t="shared" si="5"/>
@@ -2811,25 +2811,25 @@
         <f t="shared" si="2"/>
         <v>97</v>
       </c>
-      <c r="B98" s="3" t="str">
+      <c r="B98" s="3">
         <f t="shared" ref="B98:D98" si="100">IF(RAND()&lt;0.2,"NA",RANDBETWEEN(60,80))</f>
-        <v>NA</v>
+        <v>66</v>
       </c>
       <c r="C98" s="3">
         <f t="shared" si="100"/>
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="D98" s="3">
         <f t="shared" si="100"/>
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="E98" s="2">
         <f t="shared" si="4"/>
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="F98" s="2">
         <f t="shared" si="5"/>
-        <v>2019</v>
+        <v>2020</v>
       </c>
     </row>
     <row r="99">
@@ -2839,19 +2839,19 @@
       </c>
       <c r="B99" s="3">
         <f t="shared" ref="B99:D99" si="101">IF(RAND()&lt;0.2,"NA",RANDBETWEEN(60,80))</f>
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="C99" s="3">
         <f t="shared" si="101"/>
-        <v>79</v>
-      </c>
-      <c r="D99" s="3">
+        <v>62</v>
+      </c>
+      <c r="D99" s="3" t="str">
         <f t="shared" si="101"/>
-        <v>70</v>
+        <v>NA</v>
       </c>
       <c r="E99" s="2">
         <f t="shared" si="4"/>
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="F99" s="2">
         <f t="shared" si="5"/>
@@ -2865,23 +2865,23 @@
       </c>
       <c r="B100" s="3">
         <f t="shared" ref="B100:D100" si="102">IF(RAND()&lt;0.2,"NA",RANDBETWEEN(60,80))</f>
-        <v>77</v>
+        <v>64</v>
       </c>
       <c r="C100" s="3">
         <f t="shared" si="102"/>
-        <v>61</v>
-      </c>
-      <c r="D100" s="3" t="str">
+        <v>74</v>
+      </c>
+      <c r="D100" s="3">
         <f t="shared" si="102"/>
-        <v>NA</v>
+        <v>66</v>
       </c>
       <c r="E100" s="2">
         <f t="shared" si="4"/>
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="F100" s="2">
         <f t="shared" si="5"/>
-        <v>2019</v>
+        <v>2018</v>
       </c>
     </row>
     <row r="101">
@@ -2891,23 +2891,23 @@
       </c>
       <c r="B101" s="3">
         <f t="shared" ref="B101:D101" si="103">IF(RAND()&lt;0.2,"NA",RANDBETWEEN(60,80))</f>
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C101" s="3">
         <f t="shared" si="103"/>
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="D101" s="3">
         <f t="shared" si="103"/>
-        <v>68</v>
+        <v>60</v>
       </c>
       <c r="E101" s="2">
         <f t="shared" si="4"/>
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="F101" s="2">
         <f t="shared" si="5"/>
-        <v>2021</v>
+        <v>2020</v>
       </c>
     </row>
     <row r="102">
@@ -2917,7 +2917,7 @@
       </c>
       <c r="B102" s="3">
         <f t="shared" ref="B102:D102" si="104">IF(RAND()&lt;0.2,"NA",RANDBETWEEN(60,80))</f>
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="C102" s="3" t="str">
         <f t="shared" si="104"/>
@@ -2925,15 +2925,15 @@
       </c>
       <c r="D102" s="3">
         <f t="shared" si="104"/>
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="E102" s="2">
         <f t="shared" si="4"/>
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="F102" s="2">
         <f t="shared" si="5"/>
-        <v>2021</v>
+        <v>2018</v>
       </c>
     </row>
     <row r="103">
@@ -2943,19 +2943,19 @@
       </c>
       <c r="B103" s="3">
         <f t="shared" ref="B103:D103" si="105">IF(RAND()&lt;0.2,"NA",RANDBETWEEN(60,80))</f>
-        <v>73</v>
-      </c>
-      <c r="C103" s="3">
+        <v>69</v>
+      </c>
+      <c r="C103" s="3" t="str">
         <f t="shared" si="105"/>
-        <v>61</v>
-      </c>
-      <c r="D103" s="3" t="str">
+        <v>NA</v>
+      </c>
+      <c r="D103" s="3">
         <f t="shared" si="105"/>
-        <v>NA</v>
+        <v>67</v>
       </c>
       <c r="E103" s="2">
         <f t="shared" si="4"/>
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="F103" s="2">
         <f t="shared" si="5"/>
@@ -2969,23 +2969,23 @@
       </c>
       <c r="B104" s="3">
         <f t="shared" ref="B104:D104" si="106">IF(RAND()&lt;0.2,"NA",RANDBETWEEN(60,80))</f>
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="C104" s="3">
         <f t="shared" si="106"/>
-        <v>68</v>
-      </c>
-      <c r="D104" s="3" t="str">
+        <v>80</v>
+      </c>
+      <c r="D104" s="3">
         <f t="shared" si="106"/>
-        <v>NA</v>
+        <v>79</v>
       </c>
       <c r="E104" s="2">
         <f t="shared" si="4"/>
-        <v>86</v>
+        <v>76</v>
       </c>
       <c r="F104" s="2">
         <f t="shared" si="5"/>
-        <v>2020</v>
+        <v>2021</v>
       </c>
     </row>
     <row r="105">
@@ -2995,19 +2995,19 @@
       </c>
       <c r="B105" s="3">
         <f t="shared" ref="B105:D105" si="107">IF(RAND()&lt;0.2,"NA",RANDBETWEEN(60,80))</f>
-        <v>78</v>
-      </c>
-      <c r="C105" s="3" t="str">
+        <v>76</v>
+      </c>
+      <c r="C105" s="3">
         <f t="shared" si="107"/>
-        <v>NA</v>
+        <v>73</v>
       </c>
       <c r="D105" s="3">
         <f t="shared" si="107"/>
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="E105" s="2">
         <f t="shared" si="4"/>
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="F105" s="2">
         <f t="shared" si="5"/>
@@ -3021,23 +3021,23 @@
       </c>
       <c r="B106" s="3">
         <f t="shared" ref="B106:D106" si="108">IF(RAND()&lt;0.2,"NA",RANDBETWEEN(60,80))</f>
-        <v>78</v>
-      </c>
-      <c r="C106" s="3" t="str">
+        <v>65</v>
+      </c>
+      <c r="C106" s="3">
         <f t="shared" si="108"/>
-        <v>NA</v>
+        <v>66</v>
       </c>
       <c r="D106" s="3">
         <f t="shared" si="108"/>
+        <v>64</v>
+      </c>
+      <c r="E106" s="2">
+        <f t="shared" si="4"/>
         <v>75</v>
       </c>
-      <c r="E106" s="2">
-        <f t="shared" si="4"/>
-        <v>85</v>
-      </c>
       <c r="F106" s="2">
         <f t="shared" si="5"/>
-        <v>2020</v>
+        <v>2018</v>
       </c>
     </row>
     <row r="107">
@@ -3047,23 +3047,23 @@
       </c>
       <c r="B107" s="3">
         <f t="shared" ref="B107:D107" si="109">IF(RAND()&lt;0.2,"NA",RANDBETWEEN(60,80))</f>
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="C107" s="3">
         <f t="shared" si="109"/>
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="D107" s="3">
         <f t="shared" si="109"/>
-        <v>66</v>
+        <v>80</v>
       </c>
       <c r="E107" s="2">
         <f t="shared" si="4"/>
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="F107" s="2">
         <f t="shared" si="5"/>
-        <v>2021</v>
+        <v>2018</v>
       </c>
     </row>
     <row r="108">
@@ -3073,19 +3073,19 @@
       </c>
       <c r="B108" s="3">
         <f t="shared" ref="B108:D108" si="110">IF(RAND()&lt;0.2,"NA",RANDBETWEEN(60,80))</f>
-        <v>61</v>
-      </c>
-      <c r="C108" s="3" t="str">
+        <v>66</v>
+      </c>
+      <c r="C108" s="3">
         <f t="shared" si="110"/>
-        <v>NA</v>
-      </c>
-      <c r="D108" s="3" t="str">
+        <v>71</v>
+      </c>
+      <c r="D108" s="3">
         <f t="shared" si="110"/>
-        <v>NA</v>
+        <v>78</v>
       </c>
       <c r="E108" s="2">
         <f t="shared" si="4"/>
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="F108" s="2">
         <f t="shared" si="5"/>
@@ -3097,25 +3097,25 @@
         <f t="shared" si="2"/>
         <v>108</v>
       </c>
-      <c r="B109" s="3">
+      <c r="B109" s="3" t="str">
         <f t="shared" ref="B109:D109" si="111">IF(RAND()&lt;0.2,"NA",RANDBETWEEN(60,80))</f>
-        <v>65</v>
-      </c>
-      <c r="C109" s="3" t="str">
+        <v>NA</v>
+      </c>
+      <c r="C109" s="3">
         <f t="shared" si="111"/>
-        <v>NA</v>
+        <v>80</v>
       </c>
       <c r="D109" s="3">
         <f t="shared" si="111"/>
-        <v>77</v>
+        <v>69</v>
       </c>
       <c r="E109" s="2">
         <f t="shared" si="4"/>
-        <v>78</v>
+        <v>5</v>
       </c>
       <c r="F109" s="2">
         <f t="shared" si="5"/>
-        <v>2018</v>
+        <v>2019</v>
       </c>
     </row>
     <row r="110">
@@ -3125,23 +3125,23 @@
       </c>
       <c r="B110" s="3">
         <f t="shared" ref="B110:D110" si="112">IF(RAND()&lt;0.2,"NA",RANDBETWEEN(60,80))</f>
-        <v>73</v>
-      </c>
-      <c r="C110" s="3" t="str">
+        <v>76</v>
+      </c>
+      <c r="C110" s="3">
         <f t="shared" si="112"/>
-        <v>NA</v>
+        <v>77</v>
       </c>
       <c r="D110" s="3">
         <f t="shared" si="112"/>
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="E110" s="2">
         <f t="shared" si="4"/>
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="F110" s="2">
         <f t="shared" si="5"/>
-        <v>2019</v>
+        <v>2018</v>
       </c>
     </row>
     <row r="111">
@@ -3151,19 +3151,19 @@
       </c>
       <c r="B111" s="3">
         <f t="shared" ref="B111:D111" si="113">IF(RAND()&lt;0.2,"NA",RANDBETWEEN(60,80))</f>
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C111" s="3">
         <f t="shared" si="113"/>
-        <v>60</v>
-      </c>
-      <c r="D111" s="3">
+        <v>62</v>
+      </c>
+      <c r="D111" s="3" t="str">
         <f t="shared" si="113"/>
-        <v>66</v>
+        <v>NA</v>
       </c>
       <c r="E111" s="2">
         <f t="shared" si="4"/>
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="F111" s="2">
         <f t="shared" si="5"/>
@@ -3177,23 +3177,23 @@
       </c>
       <c r="B112" s="3">
         <f t="shared" ref="B112:D112" si="114">IF(RAND()&lt;0.2,"NA",RANDBETWEEN(60,80))</f>
-        <v>76</v>
-      </c>
-      <c r="C112" s="3">
+        <v>75</v>
+      </c>
+      <c r="C112" s="3" t="str">
         <f t="shared" si="114"/>
-        <v>61</v>
-      </c>
-      <c r="D112" s="3">
+        <v>NA</v>
+      </c>
+      <c r="D112" s="3" t="str">
         <f t="shared" si="114"/>
-        <v>60</v>
+        <v>NA</v>
       </c>
       <c r="E112" s="2">
         <f t="shared" si="4"/>
-        <v>82</v>
+        <v>89</v>
       </c>
       <c r="F112" s="2">
         <f t="shared" si="5"/>
-        <v>2020</v>
+        <v>2019</v>
       </c>
     </row>
     <row r="113">
@@ -3203,11 +3203,11 @@
       </c>
       <c r="B113" s="3">
         <f t="shared" ref="B113:D113" si="115">IF(RAND()&lt;0.2,"NA",RANDBETWEEN(60,80))</f>
-        <v>61</v>
+        <v>79</v>
       </c>
       <c r="C113" s="3">
         <f t="shared" si="115"/>
-        <v>69</v>
+        <v>63</v>
       </c>
       <c r="D113" s="3">
         <f t="shared" si="115"/>
@@ -3215,11 +3215,11 @@
       </c>
       <c r="E113" s="2">
         <f t="shared" si="4"/>
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="F113" s="2">
         <f t="shared" si="5"/>
-        <v>2021</v>
+        <v>2020</v>
       </c>
     </row>
     <row r="114">
@@ -3229,23 +3229,23 @@
       </c>
       <c r="B114" s="3">
         <f t="shared" ref="B114:D114" si="116">IF(RAND()&lt;0.2,"NA",RANDBETWEEN(60,80))</f>
-        <v>80</v>
+        <v>63</v>
       </c>
       <c r="C114" s="3">
         <f t="shared" si="116"/>
-        <v>65</v>
-      </c>
-      <c r="D114" s="3" t="str">
+        <v>77</v>
+      </c>
+      <c r="D114" s="3">
         <f t="shared" si="116"/>
-        <v>NA</v>
+        <v>70</v>
       </c>
       <c r="E114" s="2">
         <f t="shared" si="4"/>
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="F114" s="2">
         <f t="shared" si="5"/>
-        <v>2018</v>
+        <v>2021</v>
       </c>
     </row>
     <row r="115">
@@ -3255,15 +3255,15 @@
       </c>
       <c r="B115" s="3">
         <f t="shared" ref="B115:D115" si="117">IF(RAND()&lt;0.2,"NA",RANDBETWEEN(60,80))</f>
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="C115" s="3">
         <f t="shared" si="117"/>
-        <v>68</v>
+        <v>75</v>
       </c>
       <c r="D115" s="3">
         <f t="shared" si="117"/>
-        <v>64</v>
+        <v>70</v>
       </c>
       <c r="E115" s="2">
         <f t="shared" si="4"/>
@@ -3271,7 +3271,7 @@
       </c>
       <c r="F115" s="2">
         <f t="shared" si="5"/>
-        <v>2019</v>
+        <v>2020</v>
       </c>
     </row>
     <row r="116">
@@ -3281,23 +3281,23 @@
       </c>
       <c r="B116" s="3">
         <f t="shared" ref="B116:D116" si="118">IF(RAND()&lt;0.2,"NA",RANDBETWEEN(60,80))</f>
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="C116" s="3">
         <f t="shared" si="118"/>
-        <v>64</v>
+        <v>70</v>
       </c>
       <c r="D116" s="3">
         <f t="shared" si="118"/>
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="E116" s="2">
         <f t="shared" si="4"/>
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="F116" s="2">
         <f t="shared" si="5"/>
-        <v>2019</v>
+        <v>2018</v>
       </c>
     </row>
     <row r="117">
@@ -3305,21 +3305,21 @@
         <f t="shared" si="2"/>
         <v>116</v>
       </c>
-      <c r="B117" s="3">
+      <c r="B117" s="3" t="str">
         <f t="shared" ref="B117:D117" si="119">IF(RAND()&lt;0.2,"NA",RANDBETWEEN(60,80))</f>
-        <v>71</v>
+        <v>NA</v>
       </c>
       <c r="C117" s="3">
         <f t="shared" si="119"/>
-        <v>66</v>
-      </c>
-      <c r="D117" s="3" t="str">
+        <v>76</v>
+      </c>
+      <c r="D117" s="3">
         <f t="shared" si="119"/>
-        <v>NA</v>
+        <v>67</v>
       </c>
       <c r="E117" s="2">
         <f t="shared" si="4"/>
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="F117" s="2">
         <f t="shared" si="5"/>
@@ -3333,19 +3333,19 @@
       </c>
       <c r="B118" s="3">
         <f t="shared" ref="B118:D118" si="120">IF(RAND()&lt;0.2,"NA",RANDBETWEEN(60,80))</f>
-        <v>75</v>
+        <v>60</v>
       </c>
       <c r="C118" s="3">
         <f t="shared" si="120"/>
-        <v>77</v>
+        <v>66</v>
       </c>
       <c r="D118" s="3">
         <f t="shared" si="120"/>
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="E118" s="2">
         <f t="shared" si="4"/>
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="F118" s="2">
         <f t="shared" si="5"/>
@@ -3357,21 +3357,21 @@
         <f t="shared" si="2"/>
         <v>118</v>
       </c>
-      <c r="B119" s="3">
+      <c r="B119" s="3" t="str">
         <f t="shared" ref="B119:D119" si="121">IF(RAND()&lt;0.2,"NA",RANDBETWEEN(60,80))</f>
-        <v>75</v>
+        <v>NA</v>
       </c>
       <c r="C119" s="3">
         <f t="shared" si="121"/>
-        <v>68</v>
+        <v>75</v>
       </c>
       <c r="D119" s="3">
         <f t="shared" si="121"/>
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="E119" s="2">
         <f t="shared" si="4"/>
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="F119" s="2">
         <f t="shared" si="5"/>
@@ -3383,25 +3383,25 @@
         <f t="shared" si="2"/>
         <v>119</v>
       </c>
-      <c r="B120" s="3" t="str">
+      <c r="B120" s="3">
         <f t="shared" ref="B120:D120" si="122">IF(RAND()&lt;0.2,"NA",RANDBETWEEN(60,80))</f>
-        <v>NA</v>
+        <v>71</v>
       </c>
       <c r="C120" s="3">
         <f t="shared" si="122"/>
-        <v>70</v>
-      </c>
-      <c r="D120" s="3" t="str">
+        <v>64</v>
+      </c>
+      <c r="D120" s="3">
         <f t="shared" si="122"/>
-        <v>NA</v>
+        <v>68</v>
       </c>
       <c r="E120" s="2">
         <f t="shared" si="4"/>
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="F120" s="2">
         <f t="shared" si="5"/>
-        <v>2019</v>
+        <v>2018</v>
       </c>
     </row>
     <row r="121">
@@ -3409,25 +3409,25 @@
         <f t="shared" si="2"/>
         <v>120</v>
       </c>
-      <c r="B121" s="3" t="str">
+      <c r="B121" s="3">
         <f t="shared" ref="B121:D121" si="123">IF(RAND()&lt;0.2,"NA",RANDBETWEEN(60,80))</f>
-        <v>NA</v>
+        <v>70</v>
       </c>
       <c r="C121" s="3">
         <f t="shared" si="123"/>
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="D121" s="3">
         <f t="shared" si="123"/>
-        <v>77</v>
+        <v>64</v>
       </c>
       <c r="E121" s="2">
         <f t="shared" si="4"/>
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="F121" s="2">
         <f t="shared" si="5"/>
-        <v>2021</v>
+        <v>2019</v>
       </c>
     </row>
     <row r="122">
@@ -3437,23 +3437,23 @@
       </c>
       <c r="B122" s="3">
         <f t="shared" ref="B122:D122" si="124">IF(RAND()&lt;0.2,"NA",RANDBETWEEN(60,80))</f>
-        <v>61</v>
+        <v>71</v>
       </c>
       <c r="C122" s="3">
         <f t="shared" si="124"/>
-        <v>73</v>
+        <v>63</v>
       </c>
       <c r="D122" s="3">
         <f t="shared" si="124"/>
-        <v>69</v>
+        <v>77</v>
       </c>
       <c r="E122" s="2">
         <f t="shared" si="4"/>
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="F122" s="2">
         <f t="shared" si="5"/>
-        <v>2021</v>
+        <v>2019</v>
       </c>
     </row>
     <row r="123">
@@ -3463,23 +3463,23 @@
       </c>
       <c r="B123" s="3">
         <f t="shared" ref="B123:D123" si="125">IF(RAND()&lt;0.2,"NA",RANDBETWEEN(60,80))</f>
-        <v>72</v>
-      </c>
-      <c r="C123" s="3">
+        <v>69</v>
+      </c>
+      <c r="C123" s="3" t="str">
         <f t="shared" si="125"/>
-        <v>61</v>
+        <v>NA</v>
       </c>
       <c r="D123" s="3">
         <f t="shared" si="125"/>
+        <v>79</v>
+      </c>
+      <c r="E123" s="2">
+        <f t="shared" si="4"/>
         <v>76</v>
       </c>
-      <c r="E123" s="2">
-        <f t="shared" si="4"/>
-        <v>77</v>
-      </c>
       <c r="F123" s="2">
         <f t="shared" si="5"/>
-        <v>2020</v>
+        <v>2021</v>
       </c>
     </row>
     <row r="124">
@@ -3489,19 +3489,19 @@
       </c>
       <c r="B124" s="3">
         <f t="shared" ref="B124:D124" si="126">IF(RAND()&lt;0.2,"NA",RANDBETWEEN(60,80))</f>
-        <v>61</v>
+        <v>69</v>
       </c>
       <c r="C124" s="3">
         <f t="shared" si="126"/>
-        <v>67</v>
+        <v>76</v>
       </c>
       <c r="D124" s="3">
         <f t="shared" si="126"/>
-        <v>63</v>
+        <v>69</v>
       </c>
       <c r="E124" s="2">
         <f t="shared" si="4"/>
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="F124" s="2">
         <f t="shared" si="5"/>
@@ -3515,23 +3515,23 @@
       </c>
       <c r="B125" s="3">
         <f t="shared" ref="B125:D125" si="127">IF(RAND()&lt;0.2,"NA",RANDBETWEEN(60,80))</f>
-        <v>74</v>
+        <v>66</v>
       </c>
       <c r="C125" s="3">
         <f t="shared" si="127"/>
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="D125" s="3">
         <f t="shared" si="127"/>
-        <v>78</v>
+        <v>71</v>
       </c>
       <c r="E125" s="2">
         <f t="shared" si="4"/>
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="F125" s="2">
         <f t="shared" si="5"/>
-        <v>2018</v>
+        <v>2020</v>
       </c>
     </row>
     <row r="126">
@@ -3541,19 +3541,19 @@
       </c>
       <c r="B126" s="3">
         <f t="shared" ref="B126:D126" si="128">IF(RAND()&lt;0.2,"NA",RANDBETWEEN(60,80))</f>
-        <v>69</v>
+        <v>80</v>
       </c>
       <c r="C126" s="3">
         <f t="shared" si="128"/>
-        <v>63</v>
+        <v>74</v>
       </c>
       <c r="D126" s="3">
         <f t="shared" si="128"/>
+        <v>69</v>
+      </c>
+      <c r="E126" s="2">
+        <f t="shared" si="4"/>
         <v>80</v>
-      </c>
-      <c r="E126" s="2">
-        <f t="shared" si="4"/>
-        <v>89</v>
       </c>
       <c r="F126" s="2">
         <f t="shared" si="5"/>
@@ -3567,19 +3567,19 @@
       </c>
       <c r="B127" s="3">
         <f t="shared" ref="B127:D127" si="129">IF(RAND()&lt;0.2,"NA",RANDBETWEEN(60,80))</f>
-        <v>60</v>
-      </c>
-      <c r="C127" s="3">
+        <v>72</v>
+      </c>
+      <c r="C127" s="3" t="str">
         <f t="shared" si="129"/>
-        <v>80</v>
+        <v>NA</v>
       </c>
       <c r="D127" s="3">
         <f t="shared" si="129"/>
-        <v>60</v>
+        <v>79</v>
       </c>
       <c r="E127" s="2">
         <f t="shared" si="4"/>
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F127" s="2">
         <f t="shared" si="5"/>
@@ -3593,19 +3593,19 @@
       </c>
       <c r="B128" s="3">
         <f t="shared" ref="B128:D128" si="130">IF(RAND()&lt;0.2,"NA",RANDBETWEEN(60,80))</f>
-        <v>77</v>
+        <v>64</v>
       </c>
       <c r="C128" s="3">
         <f t="shared" si="130"/>
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="D128" s="3">
         <f t="shared" si="130"/>
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="E128" s="2">
         <f t="shared" si="4"/>
-        <v>75</v>
+        <v>89</v>
       </c>
       <c r="F128" s="2">
         <f t="shared" si="5"/>
@@ -3625,17 +3625,17 @@
         <f t="shared" si="131"/>
         <v>68</v>
       </c>
-      <c r="D129" s="3" t="str">
+      <c r="D129" s="3">
         <f t="shared" si="131"/>
-        <v>NA</v>
+        <v>60</v>
       </c>
       <c r="E129" s="2">
         <f t="shared" si="4"/>
-        <v>75</v>
+        <v>500</v>
       </c>
       <c r="F129" s="2">
         <f t="shared" si="5"/>
-        <v>2020</v>
+        <v>2021</v>
       </c>
     </row>
     <row r="130">
@@ -3643,25 +3643,25 @@
         <f t="shared" si="2"/>
         <v>129</v>
       </c>
-      <c r="B130" s="3">
+      <c r="B130" s="3" t="str">
         <f t="shared" ref="B130:D130" si="132">IF(RAND()&lt;0.2,"NA",RANDBETWEEN(60,80))</f>
-        <v>75</v>
+        <v>NA</v>
       </c>
       <c r="C130" s="3">
         <f t="shared" si="132"/>
-        <v>79</v>
-      </c>
-      <c r="D130" s="3">
+        <v>73</v>
+      </c>
+      <c r="D130" s="3" t="str">
         <f t="shared" si="132"/>
-        <v>67</v>
+        <v>NA</v>
       </c>
       <c r="E130" s="2">
         <f t="shared" si="4"/>
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="F130" s="2">
         <f t="shared" si="5"/>
-        <v>2020</v>
+        <v>2019</v>
       </c>
     </row>
     <row r="131">
@@ -3671,23 +3671,23 @@
       </c>
       <c r="B131" s="3">
         <f t="shared" ref="B131:D131" si="133">IF(RAND()&lt;0.2,"NA",RANDBETWEEN(60,80))</f>
-        <v>63</v>
+        <v>72</v>
       </c>
       <c r="C131" s="3">
         <f t="shared" si="133"/>
-        <v>63</v>
-      </c>
-      <c r="D131" s="3" t="str">
+        <v>73</v>
+      </c>
+      <c r="D131" s="3">
         <f t="shared" si="133"/>
-        <v>NA</v>
+        <v>77</v>
       </c>
       <c r="E131" s="2">
         <f t="shared" si="4"/>
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="F131" s="2">
         <f t="shared" si="5"/>
-        <v>2018</v>
+        <v>2019</v>
       </c>
     </row>
     <row r="132">
@@ -3699,21 +3699,21 @@
         <f t="shared" ref="B132:D132" si="134">IF(RAND()&lt;0.2,"NA",RANDBETWEEN(60,80))</f>
         <v>NA</v>
       </c>
-      <c r="C132" s="3" t="str">
+      <c r="C132" s="3">
         <f t="shared" si="134"/>
-        <v>NA</v>
+        <v>72</v>
       </c>
       <c r="D132" s="3">
         <f t="shared" si="134"/>
-        <v>80</v>
+        <v>74</v>
       </c>
       <c r="E132" s="2">
         <f t="shared" si="4"/>
-        <v>80</v>
+        <v>5</v>
       </c>
       <c r="F132" s="2">
         <f t="shared" si="5"/>
-        <v>2018</v>
+        <v>2019</v>
       </c>
     </row>
     <row r="133">
@@ -3723,23 +3723,23 @@
       </c>
       <c r="B133" s="3">
         <f t="shared" ref="B133:D133" si="135">IF(RAND()&lt;0.2,"NA",RANDBETWEEN(60,80))</f>
-        <v>70</v>
+        <v>62</v>
       </c>
       <c r="C133" s="3">
         <f t="shared" si="135"/>
-        <v>71</v>
+        <v>60</v>
       </c>
       <c r="D133" s="3">
         <f t="shared" si="135"/>
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="E133" s="2">
         <f t="shared" si="4"/>
-        <v>86</v>
+        <v>75</v>
       </c>
       <c r="F133" s="2">
         <f t="shared" si="5"/>
-        <v>2019</v>
+        <v>2021</v>
       </c>
     </row>
     <row r="134">
@@ -3747,25 +3747,25 @@
         <f t="shared" si="2"/>
         <v>133</v>
       </c>
-      <c r="B134" s="3">
+      <c r="B134" s="3" t="str">
         <f t="shared" ref="B134:D134" si="136">IF(RAND()&lt;0.2,"NA",RANDBETWEEN(60,80))</f>
-        <v>70</v>
+        <v>NA</v>
       </c>
       <c r="C134" s="3" t="str">
         <f t="shared" si="136"/>
         <v>NA</v>
       </c>
-      <c r="D134" s="3" t="str">
+      <c r="D134" s="3">
         <f t="shared" si="136"/>
-        <v>NA</v>
+        <v>75</v>
       </c>
       <c r="E134" s="2">
         <f t="shared" si="4"/>
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="F134" s="2">
         <f t="shared" si="5"/>
-        <v>2019</v>
+        <v>2021</v>
       </c>
     </row>
     <row r="135">
@@ -3775,23 +3775,23 @@
       </c>
       <c r="B135" s="3">
         <f t="shared" ref="B135:D135" si="137">IF(RAND()&lt;0.2,"NA",RANDBETWEEN(60,80))</f>
-        <v>77</v>
+        <v>66</v>
       </c>
       <c r="C135" s="3">
         <f t="shared" si="137"/>
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D135" s="3">
         <f t="shared" si="137"/>
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="E135" s="2">
         <f t="shared" si="4"/>
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="F135" s="2">
         <f t="shared" si="5"/>
-        <v>2018</v>
+        <v>2020</v>
       </c>
     </row>
     <row r="136">
@@ -3801,19 +3801,19 @@
       </c>
       <c r="B136" s="3">
         <f t="shared" ref="B136:D136" si="138">IF(RAND()&lt;0.2,"NA",RANDBETWEEN(60,80))</f>
-        <v>79</v>
-      </c>
-      <c r="C136" s="3">
+        <v>60</v>
+      </c>
+      <c r="C136" s="3" t="str">
         <f t="shared" si="138"/>
-        <v>66</v>
+        <v>NA</v>
       </c>
       <c r="D136" s="3">
         <f t="shared" si="138"/>
-        <v>68</v>
+        <v>75</v>
       </c>
       <c r="E136" s="2">
         <f t="shared" si="4"/>
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="F136" s="2">
         <f t="shared" si="5"/>
@@ -3825,25 +3825,25 @@
         <f t="shared" si="2"/>
         <v>136</v>
       </c>
-      <c r="B137" s="3">
+      <c r="B137" s="3" t="str">
         <f t="shared" ref="B137:D137" si="139">IF(RAND()&lt;0.2,"NA",RANDBETWEEN(60,80))</f>
-        <v>77</v>
+        <v>NA</v>
       </c>
       <c r="C137" s="3">
         <f t="shared" si="139"/>
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="D137" s="3">
         <f t="shared" si="139"/>
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E137" s="2">
         <f t="shared" si="4"/>
-        <v>90</v>
+        <v>75</v>
       </c>
       <c r="F137" s="2">
         <f t="shared" si="5"/>
-        <v>2018</v>
+        <v>2020</v>
       </c>
     </row>
     <row r="138">
@@ -3853,7 +3853,7 @@
       </c>
       <c r="B138" s="3">
         <f t="shared" ref="B138:D138" si="140">IF(RAND()&lt;0.2,"NA",RANDBETWEEN(60,80))</f>
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="C138" s="3">
         <f t="shared" si="140"/>
@@ -3861,15 +3861,15 @@
       </c>
       <c r="D138" s="3">
         <f t="shared" si="140"/>
+        <v>74</v>
+      </c>
+      <c r="E138" s="2">
+        <f t="shared" si="4"/>
         <v>79</v>
       </c>
-      <c r="E138" s="2">
-        <f t="shared" si="4"/>
-        <v>84</v>
-      </c>
       <c r="F138" s="2">
         <f t="shared" si="5"/>
-        <v>2018</v>
+        <v>2019</v>
       </c>
     </row>
     <row r="139">
@@ -3877,13 +3877,13 @@
         <f t="shared" si="2"/>
         <v>138</v>
       </c>
-      <c r="B139" s="3">
+      <c r="B139" s="3" t="str">
         <f t="shared" ref="B139:D139" si="141">IF(RAND()&lt;0.2,"NA",RANDBETWEEN(60,80))</f>
-        <v>71</v>
+        <v>NA</v>
       </c>
       <c r="C139" s="3">
         <f t="shared" si="141"/>
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="D139" s="3" t="str">
         <f t="shared" si="141"/>
@@ -3891,11 +3891,11 @@
       </c>
       <c r="E139" s="2">
         <f t="shared" si="4"/>
-        <v>77</v>
+        <v>90</v>
       </c>
       <c r="F139" s="2">
         <f t="shared" si="5"/>
-        <v>2021</v>
+        <v>2020</v>
       </c>
     </row>
   </sheetData>
